--- a/Comparison_linear_RMEP.xlsx
+++ b/Comparison_linear_RMEP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\MEP\RMEP_homotopy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AFCD8C-DC77-4F5C-8BA9-6442BBA3F318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79BD728-A493-450D-B8F1-C8E3E0E2AACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16200" yWindow="1416" windowWidth="23124" windowHeight="15936" activeTab="2" xr2:uid="{A4011660-FB7A-4DB9-A678-D73B0BBE67FE}"/>
+    <workbookView xWindow="240" yWindow="276" windowWidth="30312" windowHeight="17028" xr2:uid="{A4011660-FB7A-4DB9-A678-D73B0BBE67FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Times" sheetId="1" r:id="rId1"/>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="11" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B11">
         <v>36</v>

--- a/Comparison_linear_RMEP.xlsx
+++ b/Comparison_linear_RMEP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\MEP\RMEP_homotopy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2022A6D2-B1CA-432E-ABFD-FE219AA4FD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE7F549-60FB-4829-84D3-5D2D08827377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23400" yWindow="864" windowWidth="22176" windowHeight="17028" xr2:uid="{A4011660-FB7A-4DB9-A678-D73B0BBE67FE}"/>
+    <workbookView xWindow="612" yWindow="696" windowWidth="30384" windowHeight="17028" xr2:uid="{A4011660-FB7A-4DB9-A678-D73B0BBE67FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Times" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="66">
   <si>
     <t>n</t>
   </si>
@@ -225,6 +225,18 @@
   <si>
     <t>k=9</t>
   </si>
+  <si>
+    <t>homo sequential</t>
+  </si>
+  <si>
+    <t>speedup</t>
+  </si>
+  <si>
+    <t>Homo seq init</t>
+  </si>
+  <si>
+    <t>Out of mem</t>
+  </si>
 </sst>
 </file>
 
@@ -236,7 +248,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,8 +298,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,6 +368,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -376,13 +402,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -465,8 +492,19 @@
     <xf numFmtId="11" fontId="6" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="6" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="3" xr:uid="{37814D57-3646-4219-A278-D0D57E9A6287}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A00CCC5E-6F95-42E5-B9FB-CD86513E728C}"/>
@@ -788,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D26378D0-B3BB-4455-B056-646B4297C753}">
-  <dimension ref="A1:BD67"/>
+  <dimension ref="A1:BF67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -811,15 +849,16 @@
     <col min="26" max="26" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:56" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -847,32 +886,32 @@
       <c r="AD3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AH3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AL3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AO3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AR3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AS3" s="2" t="s">
+      <c r="AU3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AV3" s="2" t="s">
+      <c r="AX3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AY3" s="2" t="s">
+      <c r="BA3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="BB3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BD3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>14</v>
       </c>
@@ -964,82 +1003,88 @@
         <v>8</v>
       </c>
       <c r="AF4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG4" t="s">
         <v>9</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>14</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK4" t="s">
         <v>9</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AL4" t="s">
         <v>14</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AM4" t="s">
         <v>8</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AN4" t="s">
         <v>9</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AO4" t="s">
         <v>14</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AP4" t="s">
         <v>8</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AQ4" t="s">
         <v>9</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AR4" t="s">
         <v>14</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AS4" t="s">
         <v>8</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AT4" t="s">
         <v>9</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AU4" t="s">
         <v>14</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AV4" t="s">
         <v>8</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AW4" t="s">
         <v>9</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AX4" t="s">
         <v>14</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AY4" t="s">
         <v>8</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AZ4" t="s">
         <v>9</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="BA4" t="s">
         <v>14</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BB4" t="s">
         <v>8</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BC4" t="s">
         <v>9</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BD4" t="s">
         <v>14</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BE4" t="s">
         <v>8</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BF4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1053,7 +1098,7 @@
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="E5" s="7">
-        <v>1.9099999999999999E-2</v>
+        <v>1.985483E-2</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1065,7 +1110,7 @@
         <v>1.9401849999999999E-3</v>
       </c>
       <c r="I5" s="7">
-        <v>2.2146405000000001E-2</v>
+        <v>2.5156580000000001E-2</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -1077,7 +1122,7 @@
         <v>6.2774200000000014E-3</v>
       </c>
       <c r="M5" s="7">
-        <v>3.0309265000000002E-2</v>
+        <v>3.4954354999999993E-2</v>
       </c>
       <c r="N5">
         <v>6</v>
@@ -1089,7 +1134,7 @@
         <v>3.6216889999999995E-2</v>
       </c>
       <c r="Q5" s="7">
-        <v>3.852970499999999E-2</v>
+        <v>3.3204734999999999E-2</v>
       </c>
       <c r="R5">
         <v>7</v>
@@ -1101,7 +1146,7 @@
         <v>0.26154030500000003</v>
       </c>
       <c r="U5" s="10">
-        <v>4.8915764999999986E-2</v>
+        <v>4.5036955000000004E-2</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1113,7 +1158,7 @@
         <v>2.28116596</v>
       </c>
       <c r="Y5" s="5">
-        <v>5.9506694999999984E-2</v>
+        <v>7.5730779999999998E-2</v>
       </c>
       <c r="Z5">
         <v>9</v>
@@ -1125,7 +1170,7 @@
         <v>23.6435791</v>
       </c>
       <c r="AC5" s="5">
-        <v>8.3039160000000001E-2</v>
+        <v>6.2447779999999987E-2</v>
       </c>
       <c r="AD5">
         <v>10</v>
@@ -1133,80 +1178,86 @@
       <c r="AE5" s="6">
         <v>2.1355899999999997E-2</v>
       </c>
-      <c r="AF5" s="5">
-        <v>8.9840065000000024E-2</v>
-      </c>
-      <c r="AG5">
+      <c r="AF5" s="7">
+        <v>262.76</v>
+      </c>
+      <c r="AG5" s="5">
+        <v>6.709292E-2</v>
+      </c>
+      <c r="AH5">
         <v>11</v>
       </c>
-      <c r="AH5" s="6">
+      <c r="AI5" s="6">
         <v>2.8817240000000001E-2</v>
       </c>
-      <c r="AI5" s="5">
-        <v>0.10475287500000001</v>
-      </c>
-      <c r="AJ5">
+      <c r="AJ5" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK5" s="5">
+        <v>7.6054860000000002E-2</v>
+      </c>
+      <c r="AL5">
         <v>16</v>
       </c>
-      <c r="AK5" s="6">
+      <c r="AM5" s="6">
         <v>7.4035059999999986E-2</v>
       </c>
-      <c r="AL5" s="5">
-        <v>0.18416717500000002</v>
-      </c>
-      <c r="AM5">
+      <c r="AN5" s="5">
+        <v>0.15153119000000001</v>
+      </c>
+      <c r="AO5">
         <v>21</v>
       </c>
-      <c r="AN5" s="6">
+      <c r="AP5" s="6">
         <v>0.18962910499999996</v>
       </c>
-      <c r="AO5" s="5">
-        <v>0.37274005999999998</v>
-      </c>
-      <c r="AP5">
+      <c r="AQ5" s="5">
+        <v>0.31227701999999996</v>
+      </c>
+      <c r="AR5">
         <v>31</v>
       </c>
-      <c r="AQ5" s="6">
+      <c r="AS5" s="63">
         <v>1.2790287900000001</v>
       </c>
-      <c r="AR5" s="5">
-        <v>1.30644432</v>
-      </c>
-      <c r="AS5">
+      <c r="AT5" s="6">
+        <v>1.2597854550000001</v>
+      </c>
+      <c r="AU5">
         <v>41</v>
       </c>
-      <c r="AT5" s="5">
+      <c r="AV5" s="5">
         <v>6.3138266199999995</v>
       </c>
-      <c r="AU5" s="6">
-        <v>3.02475366</v>
-      </c>
-      <c r="AV5">
+      <c r="AW5" s="6">
+        <v>2.8433841800000001</v>
+      </c>
+      <c r="AX5">
         <v>51</v>
       </c>
-      <c r="AW5" s="5">
+      <c r="AY5" s="5">
         <v>21.992981719999996</v>
       </c>
-      <c r="AX5" s="6">
-        <v>5.5251610400000004</v>
-      </c>
-      <c r="AY5">
+      <c r="AZ5" s="6">
+        <v>5.1876860799999998</v>
+      </c>
+      <c r="BA5">
         <v>61</v>
       </c>
-      <c r="AZ5" s="5">
+      <c r="BB5" s="5">
         <v>64.626304340000004</v>
       </c>
-      <c r="BA5" s="6">
-        <v>11.96833852</v>
-      </c>
-      <c r="BB5">
+      <c r="BC5" s="6">
+        <v>8.5283140599999996</v>
+      </c>
+      <c r="BD5">
         <v>101</v>
       </c>
-      <c r="BD5" s="6">
-        <v>40.335313300000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BF5" s="6">
+        <v>38.690378299999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1220,7 +1271,7 @@
         <v>1.0246000000000001E-3</v>
       </c>
       <c r="E6" s="7">
-        <v>2.3864E-2</v>
+        <v>3.0805554999999998E-2</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -1232,7 +1283,7 @@
         <v>3.6057249999999997E-3</v>
       </c>
       <c r="I6" s="7">
-        <v>5.2197960000000009E-2</v>
+        <v>4.0466015000000008E-2</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -1244,7 +1295,7 @@
         <v>1.560634E-2</v>
       </c>
       <c r="M6" s="7">
-        <v>5.8947825000000009E-2</v>
+        <v>6.0674574999999994E-2</v>
       </c>
       <c r="N6">
         <v>21</v>
@@ -1256,7 +1307,7 @@
         <v>0.12438753000000002</v>
       </c>
       <c r="Q6" s="5">
-        <v>9.8172665000000006E-2</v>
+        <v>7.6251975E-2</v>
       </c>
       <c r="R6">
         <v>28</v>
@@ -1268,7 +1319,7 @@
         <v>1.0297562250000001</v>
       </c>
       <c r="U6" s="10">
-        <v>0.14700240000000003</v>
+        <v>0.11473232000000003</v>
       </c>
       <c r="V6">
         <v>36</v>
@@ -1280,7 +1331,7 @@
         <v>10.338131199999999</v>
       </c>
       <c r="Y6" s="5">
-        <v>0.197268425</v>
+        <v>0.15315430000000002</v>
       </c>
       <c r="Z6">
         <v>55</v>
@@ -1292,7 +1343,7 @@
         <v>118.63456050000001</v>
       </c>
       <c r="AC6" s="5">
-        <v>0.30986244499999999</v>
+        <v>0.20677629</v>
       </c>
       <c r="AD6">
         <v>55</v>
@@ -1300,38 +1351,40 @@
       <c r="AE6" s="6">
         <v>0.11367843</v>
       </c>
-      <c r="AF6" s="5">
-        <v>0.39305564000000004</v>
-      </c>
-      <c r="AG6">
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="5">
+        <v>0.26641277499999994</v>
+      </c>
+      <c r="AH6">
         <v>66</v>
       </c>
-      <c r="AH6" s="6">
+      <c r="AI6" s="6">
         <v>0.15541465500000001</v>
       </c>
-      <c r="AI6" s="5">
-        <v>0.50383889000000004</v>
-      </c>
-      <c r="AJ6">
+      <c r="AJ6" s="71"/>
+      <c r="AK6" s="5">
+        <v>0.34924788499999998</v>
+      </c>
+      <c r="AL6">
         <v>136</v>
       </c>
-      <c r="AK6" s="6">
+      <c r="AM6" s="63">
         <v>1.9413491549999999</v>
       </c>
-      <c r="AL6" s="5">
-        <v>2.2030135900000003</v>
-      </c>
-      <c r="AM6">
+      <c r="AN6" s="6">
+        <v>1.9267980650000003</v>
+      </c>
+      <c r="AO6">
         <v>231</v>
       </c>
-      <c r="AN6" s="5">
+      <c r="AP6" s="5">
         <v>13.794577720000001</v>
       </c>
-      <c r="AO6" s="6">
-        <v>6.0817013200000005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="AQ6" s="6">
+        <v>5.5634209600000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1345,7 +1398,7 @@
         <v>1.58939E-3</v>
       </c>
       <c r="E7" s="7">
-        <v>4.2245940000000003E-2</v>
+        <v>4.3799095000000003E-2</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -1357,7 +1410,7 @@
         <v>5.6873749999999997E-3</v>
       </c>
       <c r="I7" s="7">
-        <v>7.2745569999999982E-2</v>
+        <v>6.4804409999999993E-2</v>
       </c>
       <c r="J7">
         <v>35</v>
@@ -1369,7 +1422,7 @@
         <v>3.6510745000000004E-2</v>
       </c>
       <c r="M7" s="7">
-        <v>0.12679227000000001</v>
+        <v>9.542328500000001E-2</v>
       </c>
       <c r="N7">
         <v>56</v>
@@ -1381,7 +1434,7 @@
         <v>0.31682692000000007</v>
       </c>
       <c r="Q7" s="5">
-        <v>0.23720457499999997</v>
+        <v>0.14323133999999998</v>
       </c>
       <c r="R7">
         <v>84</v>
@@ -1393,7 +1446,7 @@
         <v>3.0857070799999997</v>
       </c>
       <c r="U7" s="10">
-        <v>0.41721945499999996</v>
+        <v>0.27964221500000008</v>
       </c>
       <c r="V7">
         <v>120</v>
@@ -1405,7 +1458,7 @@
         <v>35.421332300000003</v>
       </c>
       <c r="Y7" s="5">
-        <v>0.69836495499999995</v>
+        <v>0.44925526999999993</v>
       </c>
       <c r="Z7">
         <v>165</v>
@@ -1417,7 +1470,7 @@
         <v>448.86</v>
       </c>
       <c r="AC7" s="5">
-        <v>0.99736371500000021</v>
+        <v>0.68351704000000002</v>
       </c>
       <c r="AD7">
         <v>220</v>
@@ -1425,38 +1478,40 @@
       <c r="AE7" s="5">
         <v>1.8763886000000003</v>
       </c>
-      <c r="AF7" s="6">
-        <v>1.5480788649999997</v>
-      </c>
-      <c r="AG7">
+      <c r="AF7" s="71"/>
+      <c r="AG7" s="6">
+        <v>1.1054329600000004</v>
+      </c>
+      <c r="AH7">
         <v>286</v>
       </c>
-      <c r="AH7" s="5">
+      <c r="AI7" s="5">
         <v>5.3976198599999998</v>
       </c>
-      <c r="AI7" s="6">
-        <v>2.6376466600000001</v>
-      </c>
-      <c r="AJ7">
+      <c r="AJ7" s="71"/>
+      <c r="AK7" s="6">
+        <v>1.73802514</v>
+      </c>
+      <c r="AL7">
         <v>816</v>
       </c>
-      <c r="AK7" s="5">
+      <c r="AM7" s="5">
         <v>169.7973776</v>
       </c>
-      <c r="AL7" s="6">
-        <v>12.815375419999999</v>
-      </c>
-      <c r="AM7">
+      <c r="AN7" s="6">
+        <v>10.755881666666667</v>
+      </c>
+      <c r="AO7">
         <v>1771</v>
       </c>
-      <c r="AN7" s="4" t="s">
+      <c r="AP7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AO7" s="6">
-        <v>52.909996999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="AQ7" s="6">
+        <v>45.140964266666664</v>
+      </c>
+    </row>
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1470,7 +1525,7 @@
         <v>2.0284500000000002E-3</v>
       </c>
       <c r="E8" s="7">
-        <v>5.2596234999999991E-2</v>
+        <v>5.2675250000000007E-2</v>
       </c>
       <c r="F8">
         <v>35</v>
@@ -1482,7 +1537,7 @@
         <v>1.0133079999999999E-2</v>
       </c>
       <c r="I8" s="7">
-        <v>0.12181928500000001</v>
+        <v>8.5524635000000016E-2</v>
       </c>
       <c r="J8">
         <v>70</v>
@@ -1494,7 +1549,7 @@
         <v>7.2288394999999991E-2</v>
       </c>
       <c r="M8" s="7">
-        <v>0.25006141499999995</v>
+        <v>0.17940265999999999</v>
       </c>
       <c r="N8">
         <v>126</v>
@@ -1506,7 +1561,7 @@
         <v>0.79143405000000011</v>
       </c>
       <c r="Q8" s="5">
-        <v>0.56560521499999994</v>
+        <v>0.26320189500000002</v>
       </c>
       <c r="R8">
         <v>210</v>
@@ -1518,7 +1573,7 @@
         <v>8.2807449000000002</v>
       </c>
       <c r="U8" s="10">
-        <v>0.97330201000000005</v>
+        <v>0.61794294500000002</v>
       </c>
       <c r="V8">
         <v>330</v>
@@ -1530,7 +1585,7 @@
         <v>104.9884751</v>
       </c>
       <c r="Y8" s="6">
-        <v>1.79893028</v>
+        <v>1.28136454</v>
       </c>
       <c r="Z8">
         <v>495</v>
@@ -1542,7 +1597,7 @@
         <v>1452.2390227000001</v>
       </c>
       <c r="AC8" s="6">
-        <v>3.3568599399999997</v>
+        <v>2.2601355399999998</v>
       </c>
       <c r="AD8">
         <v>715</v>
@@ -1550,26 +1605,28 @@
       <c r="AE8" s="5">
         <v>32.783000000000001</v>
       </c>
-      <c r="AF8" s="6">
-        <v>5.7869999999999999</v>
-      </c>
-      <c r="AG8">
+      <c r="AF8" s="71"/>
+      <c r="AG8" s="6">
+        <v>4.0314480000000001</v>
+      </c>
+      <c r="AH8">
         <v>1001</v>
       </c>
-      <c r="AH8" s="5">
+      <c r="AI8" s="5">
         <v>109.4554016</v>
       </c>
-      <c r="AI8" s="6">
-        <v>9.5998410000000014</v>
-      </c>
-      <c r="AJ8">
+      <c r="AJ8" s="71"/>
+      <c r="AK8" s="6">
+        <v>6.7989622000000001</v>
+      </c>
+      <c r="AL8">
         <v>3876</v>
       </c>
-      <c r="AL8" s="11">
-        <v>88.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="AN8" s="6">
+        <v>61.956499999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1583,7 +1640,7 @@
         <v>2.9149549999999995E-3</v>
       </c>
       <c r="E9" s="7">
-        <v>7.8147800000000003E-2</v>
+        <v>6.2096049999999979E-2</v>
       </c>
       <c r="F9">
         <v>56</v>
@@ -1595,7 +1652,7 @@
         <v>1.5546505000000002E-2</v>
       </c>
       <c r="I9" s="7">
-        <v>0.19857331999999997</v>
+        <v>0.11641928500000001</v>
       </c>
       <c r="J9">
         <v>126</v>
@@ -1607,19 +1664,19 @@
         <v>0.13498407000000001</v>
       </c>
       <c r="M9" s="7">
-        <v>0.43198910999999995</v>
+        <v>0.29394207500000002</v>
       </c>
       <c r="N9">
         <v>252</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="5">
         <v>0.77225319000000003</v>
       </c>
       <c r="P9" s="7">
         <v>1.5915183100000001</v>
       </c>
-      <c r="Q9" s="5">
-        <v>0.99320628499999997</v>
+      <c r="Q9" s="6">
+        <v>0.56998807499999993</v>
       </c>
       <c r="R9">
         <v>462</v>
@@ -1631,7 +1688,7 @@
         <v>19.46116374</v>
       </c>
       <c r="U9" s="6">
-        <v>2.0912460400000001</v>
+        <v>1.2429469200000001</v>
       </c>
       <c r="V9">
         <v>792</v>
@@ -1643,7 +1700,7 @@
         <v>305.77434690000001</v>
       </c>
       <c r="Y9" s="6">
-        <v>5.4922689200000008</v>
+        <v>3.1694037799999997</v>
       </c>
       <c r="Z9">
         <v>1287</v>
@@ -1655,7 +1712,7 @@
         <v>4870.7439999999997</v>
       </c>
       <c r="AC9" s="6">
-        <v>9.8802709400000008</v>
+        <v>6.4819743799999996</v>
       </c>
       <c r="AD9">
         <v>2002</v>
@@ -1663,20 +1720,22 @@
       <c r="AE9" s="5">
         <v>658.49058000000002</v>
       </c>
-      <c r="AF9" s="6">
-        <v>19.7408</v>
-      </c>
-      <c r="AG9">
+      <c r="AF9" s="71"/>
+      <c r="AG9" s="6">
+        <v>12.6557928</v>
+      </c>
+      <c r="AH9">
         <v>3003</v>
       </c>
-      <c r="AH9" s="5">
+      <c r="AI9" s="5">
         <v>2574.1812619000002</v>
       </c>
-      <c r="AI9" s="6">
-        <v>36.282285619999996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="AJ9" s="71"/>
+      <c r="AK9" s="6">
+        <v>22.921736533333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1690,7 +1749,7 @@
         <v>2.8811699999999997E-3</v>
       </c>
       <c r="E10" s="7">
-        <v>9.4563604999999995E-2</v>
+        <v>8.2486694999999999E-2</v>
       </c>
       <c r="F10">
         <v>84</v>
@@ -1702,7 +1761,7 @@
         <v>2.3653085000000001E-2</v>
       </c>
       <c r="I10" s="7">
-        <v>0.28786992999999994</v>
+        <v>0.18086283000000003</v>
       </c>
       <c r="J10">
         <v>210</v>
@@ -1714,7 +1773,7 @@
         <v>0.243723775</v>
       </c>
       <c r="M10" s="7">
-        <v>0.72719087000000004</v>
+        <v>0.46586473500000009</v>
       </c>
       <c r="N10">
         <v>462</v>
@@ -1726,7 +1785,7 @@
         <v>2.8065348999999999</v>
       </c>
       <c r="Q10" s="6">
-        <v>1.50936874</v>
+        <v>0.97101222000000009</v>
       </c>
       <c r="R10">
         <v>924</v>
@@ -1738,7 +1797,7 @@
         <v>43.666878280000006</v>
       </c>
       <c r="U10" s="6">
-        <v>4.3360461200000007</v>
+        <v>2.6888829599999999</v>
       </c>
       <c r="V10">
         <v>1716</v>
@@ -1750,7 +1809,7 @@
         <v>860.35919660000002</v>
       </c>
       <c r="Y10" s="6">
-        <v>12.902357200000001</v>
+        <v>7.5992268666666662</v>
       </c>
       <c r="Z10">
         <v>3003</v>
@@ -1759,19 +1818,20 @@
         <v>1508.3916630000001</v>
       </c>
       <c r="AC10" s="6">
-        <v>25.822244000000001</v>
+        <v>16.457347866666666</v>
       </c>
       <c r="AD10">
         <v>5005</v>
       </c>
-      <c r="AG10">
+      <c r="AH10">
         <v>8008</v>
       </c>
-      <c r="AI10" s="6">
-        <v>99.045699999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="AJ10" s="72"/>
+      <c r="AK10" s="6">
+        <v>67.346488899999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1785,7 +1845,7 @@
         <v>4.3376150000000013E-3</v>
       </c>
       <c r="E11" s="7">
-        <v>0.13076563499999999</v>
+        <v>0.10883477000000004</v>
       </c>
       <c r="F11">
         <v>120</v>
@@ -1797,19 +1857,19 @@
         <v>3.4414294999999998E-2</v>
       </c>
       <c r="I11" s="7">
-        <v>0.366772335</v>
+        <v>0.24312836999999998</v>
       </c>
       <c r="J11">
         <v>330</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="7">
         <v>1.175780225</v>
       </c>
       <c r="L11" s="6">
         <v>0.42528166999999995</v>
       </c>
-      <c r="M11" s="7">
-        <v>1.1408193700000002</v>
+      <c r="M11" s="5">
+        <v>0.70006993500000014</v>
       </c>
       <c r="N11">
         <v>792</v>
@@ -1821,7 +1881,7 @@
         <v>5.9555392600000001</v>
       </c>
       <c r="Q11" s="6">
-        <v>2.7873993399999999</v>
+        <v>1.7259364399999999</v>
       </c>
       <c r="R11">
         <v>1716</v>
@@ -1833,7 +1893,7 @@
         <v>118.44355419999999</v>
       </c>
       <c r="U11" s="6">
-        <v>9.2199360400000003</v>
+        <v>5.3917490800000003</v>
       </c>
       <c r="V11">
         <v>3432</v>
@@ -1845,22 +1905,22 @@
         <v>3018</v>
       </c>
       <c r="Y11" s="6">
-        <v>25.822244000000001</v>
+        <v>16.7404893</v>
       </c>
       <c r="Z11">
         <v>6435</v>
       </c>
       <c r="AC11" s="6">
-        <v>60.166719000000001</v>
-      </c>
-      <c r="AG11">
+        <v>39.216944900000001</v>
+      </c>
+      <c r="AH11">
         <v>19448</v>
       </c>
-      <c r="AI11" s="6">
-        <v>330.77274190000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="AK11" s="6">
+        <v>184.7420821</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -1874,7 +1934,7 @@
         <v>4.9303649999999999E-3</v>
       </c>
       <c r="E12" s="7">
-        <v>0.16253485500000003</v>
+        <v>0.130007495</v>
       </c>
       <c r="F12">
         <v>165</v>
@@ -1886,7 +1946,7 @@
         <v>5.074608500000001E-2</v>
       </c>
       <c r="I12" s="7">
-        <v>0.53416845000000013</v>
+        <v>0.35455610500000001</v>
       </c>
       <c r="J12">
         <v>495</v>
@@ -1898,7 +1958,7 @@
         <v>0.63481323999999995</v>
       </c>
       <c r="M12" s="5">
-        <v>1.6256549799999997</v>
+        <v>1.1385132600000001</v>
       </c>
       <c r="N12">
         <v>1287</v>
@@ -1910,7 +1970,7 @@
         <v>10.79656404</v>
       </c>
       <c r="Q12" s="6">
-        <v>5.1298590599999994</v>
+        <v>3.1348834800000001</v>
       </c>
       <c r="R12">
         <v>3003</v>
@@ -1922,16 +1982,16 @@
         <v>302.59518709999998</v>
       </c>
       <c r="U12" s="6">
-        <v>16.972541159999999</v>
+        <v>11.015139166666666</v>
       </c>
       <c r="V12">
         <v>6435</v>
       </c>
       <c r="Y12" s="6">
-        <v>52.916882999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:56" x14ac:dyDescent="0.3">
+        <v>34.003315099999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -1945,7 +2005,7 @@
         <v>6.4831199999999993E-3</v>
       </c>
       <c r="E13" s="7">
-        <v>0.19085728999999999</v>
+        <v>0.14224112000000003</v>
       </c>
       <c r="F13">
         <v>220</v>
@@ -1957,7 +2017,7 @@
         <v>7.2403085000000006E-2</v>
       </c>
       <c r="I13" s="7">
-        <v>0.72586963000000015</v>
+        <v>0.50099266499999984</v>
       </c>
       <c r="J13">
         <v>715</v>
@@ -1969,7 +2029,7 @@
         <v>1.0409039400000002</v>
       </c>
       <c r="M13" s="5">
-        <v>2.3917373</v>
+        <v>1.69885522</v>
       </c>
       <c r="N13">
         <v>2002</v>
@@ -1981,7 +2041,7 @@
         <v>20.229128060000001</v>
       </c>
       <c r="Q13" s="6">
-        <v>8.05378814</v>
+        <v>5.3174288199999999</v>
       </c>
       <c r="R13">
         <v>5005</v>
@@ -1991,22 +2051,22 @@
         <v>742.08734189999996</v>
       </c>
       <c r="U13" s="6">
-        <v>33.834060720000004</v>
+        <v>21.323356200000003</v>
       </c>
       <c r="V13">
         <v>11440</v>
       </c>
       <c r="Y13" s="6">
-        <v>106.03</v>
-      </c>
-      <c r="AG13">
+        <v>65.172876599999995</v>
+      </c>
+      <c r="AH13">
         <v>92378</v>
       </c>
-      <c r="AI13" s="52">
-        <v>3187.55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="AK13" s="52">
+        <v>1116.2019324999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2020,7 +2080,7 @@
         <v>7.9231799999999984E-3</v>
       </c>
       <c r="E14" s="7">
-        <v>0.21668550000000003</v>
+        <v>0.15834911500000001</v>
       </c>
       <c r="F14">
         <v>286</v>
@@ -2032,7 +2092,7 @@
         <v>0.10487514000000001</v>
       </c>
       <c r="I14" s="7">
-        <v>1.0885678799999998</v>
+        <v>0.64965617999999992</v>
       </c>
       <c r="J14">
         <v>1001</v>
@@ -2044,7 +2104,7 @@
         <v>1.6349814599999999</v>
       </c>
       <c r="M14" s="5">
-        <v>3.7372063799999999</v>
+        <v>2.3266192000000006</v>
       </c>
       <c r="N14">
         <v>3003</v>
@@ -2056,7 +2116,7 @@
         <v>66.047500400000004</v>
       </c>
       <c r="Q14" s="6">
-        <v>14.221233339999998</v>
+        <v>9.0094639000000001</v>
       </c>
       <c r="R14">
         <v>8008</v>
@@ -2066,16 +2126,16 @@
         <v>2312.4965281999998</v>
       </c>
       <c r="U14" s="6">
-        <v>66.541065099999997</v>
+        <v>40.379703499999998</v>
       </c>
       <c r="V14">
         <v>19448</v>
       </c>
       <c r="Y14" s="6">
-        <v>215.22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:56" x14ac:dyDescent="0.3">
+        <v>121.9182672</v>
+      </c>
+    </row>
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2089,7 +2149,7 @@
         <v>9.9332399999999994E-3</v>
       </c>
       <c r="E15" s="7">
-        <v>0.25790239999999998</v>
+        <v>0.19490289500000002</v>
       </c>
       <c r="F15">
         <v>364</v>
@@ -2101,7 +2161,7 @@
         <v>0.14052732000000001</v>
       </c>
       <c r="I15" s="5">
-        <v>1.31935706</v>
+        <v>0.85651955999999996</v>
       </c>
       <c r="J15">
         <v>1365</v>
@@ -2113,7 +2173,7 @@
         <v>2.9392954199999997</v>
       </c>
       <c r="M15" s="5">
-        <v>5.4098433200000002</v>
+        <v>3.5770991199999997</v>
       </c>
       <c r="N15">
         <v>4368</v>
@@ -2125,16 +2185,16 @@
         <v>119.5974179</v>
       </c>
       <c r="Q15" s="6">
-        <v>22.382495080000002</v>
+        <v>14.310228033333333</v>
       </c>
       <c r="V15">
         <v>31824</v>
       </c>
       <c r="Y15" s="6">
-        <v>407.31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:56" x14ac:dyDescent="0.3">
+        <v>216.4531848</v>
+      </c>
+    </row>
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -2148,7 +2208,7 @@
         <v>1.151434E-2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.31560336</v>
+        <v>0.23170724500000003</v>
       </c>
       <c r="F16">
         <v>455</v>
@@ -2160,7 +2220,7 @@
         <v>0.20229919999999998</v>
       </c>
       <c r="I16" s="5">
-        <v>1.9567906799999999</v>
+        <v>1.1217998200000001</v>
       </c>
       <c r="J16">
         <v>1820</v>
@@ -2172,7 +2232,7 @@
         <v>4.7792429199999997</v>
       </c>
       <c r="M16" s="5">
-        <v>7.5230298800000002</v>
+        <v>5.3300209399999998</v>
       </c>
       <c r="N16">
         <v>6188</v>
@@ -2181,7 +2241,7 @@
         <v>267.15335240000002</v>
       </c>
       <c r="Q16" s="6">
-        <v>40.196838199999995</v>
+        <v>21.312664000000002</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
@@ -2198,7 +2258,7 @@
         <v>1.62122E-2</v>
       </c>
       <c r="E17" s="7">
-        <v>0.38776778000000001</v>
+        <v>0.27117799999999997</v>
       </c>
       <c r="F17">
         <v>560</v>
@@ -2210,7 +2270,7 @@
         <v>0.30381140000000001</v>
       </c>
       <c r="I17" s="5">
-        <v>2.3736570399999999</v>
+        <v>1.4490373999999999</v>
       </c>
       <c r="J17">
         <v>2380</v>
@@ -2218,11 +2278,11 @@
       <c r="K17" s="7">
         <v>313.41755699999999</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="5">
         <v>8.3362589800000002</v>
       </c>
-      <c r="M17" s="5">
-        <v>10.44317684</v>
+      <c r="M17" s="6">
+        <v>7.400859333333333</v>
       </c>
       <c r="N17">
         <v>8568</v>
@@ -2231,7 +2291,7 @@
         <v>537.66359539999996</v>
       </c>
       <c r="Q17" s="6">
-        <v>56.411471800000001</v>
+        <v>32.910109399999996</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -2248,7 +2308,7 @@
         <v>1.9705760000000003E-2</v>
       </c>
       <c r="E18" s="7">
-        <v>0.51535036000000001</v>
+        <v>0.32632619000000007</v>
       </c>
       <c r="F18">
         <v>680</v>
@@ -2260,7 +2320,7 @@
         <v>0.39482010000000001</v>
       </c>
       <c r="I18" s="5">
-        <v>3.0902487199999999</v>
+        <v>1.8809741200000001</v>
       </c>
       <c r="J18">
         <v>3060</v>
@@ -2268,11 +2328,11 @@
       <c r="K18" s="7">
         <v>636.95748519999995</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>14.44136638</v>
       </c>
-      <c r="M18" s="5">
-        <v>15.071869660000001</v>
+      <c r="M18" s="6">
+        <v>11.133719133333335</v>
       </c>
       <c r="N18">
         <v>11628</v>
@@ -2281,7 +2341,7 @@
         <v>1097.6545295999999</v>
       </c>
       <c r="Q18" s="6">
-        <v>86.555000000000007</v>
+        <v>54.297702599999994</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -2298,7 +2358,7 @@
         <v>2.3229080000000003E-2</v>
       </c>
       <c r="E19" s="7">
-        <v>0.66134314000000005</v>
+        <v>0.41870578999999991</v>
       </c>
       <c r="F19">
         <v>816</v>
@@ -2310,7 +2370,7 @@
         <v>0.54198486000000001</v>
       </c>
       <c r="I19" s="5">
-        <v>4.3281014800000008</v>
+        <v>2.6914631600000001</v>
       </c>
       <c r="J19">
         <v>3876</v>
@@ -2319,7 +2379,7 @@
         <v>25.02096762</v>
       </c>
       <c r="M19" s="6">
-        <v>20.578489879999999</v>
+        <v>15.777931366666666</v>
       </c>
       <c r="N19">
         <v>15504</v>
@@ -2328,7 +2388,7 @@
         <v>2305.13</v>
       </c>
       <c r="Q19" s="6">
-        <v>118.39</v>
+        <v>80.945590799999991</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -2345,7 +2405,7 @@
         <v>2.5294240000000003E-2</v>
       </c>
       <c r="E20" s="7">
-        <v>0.69582818000000013</v>
+        <v>0.4737934949999999</v>
       </c>
       <c r="F20">
         <v>969</v>
@@ -2357,7 +2417,7 @@
         <v>0.70671596000000003</v>
       </c>
       <c r="I20" s="5">
-        <v>4.7503033599999993</v>
+        <v>3.3767622600000005</v>
       </c>
       <c r="J20">
         <v>4845</v>
@@ -2366,13 +2426,13 @@
         <v>47.062229133333325</v>
       </c>
       <c r="M20" s="6">
-        <v>29.898959999999999</v>
+        <v>20.979158766666668</v>
       </c>
       <c r="N20">
         <v>20349</v>
       </c>
       <c r="Q20" s="6">
-        <v>176.19</v>
+        <v>117.491991</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
@@ -2389,7 +2449,7 @@
         <v>3.1552719999999999E-2</v>
       </c>
       <c r="E21" s="7">
-        <v>0.8702651400000001</v>
+        <v>0.52304658500000012</v>
       </c>
       <c r="F21">
         <v>1140</v>
@@ -2401,7 +2461,7 @@
         <v>0.92488938000000009</v>
       </c>
       <c r="I21" s="5">
-        <v>6.2207562800000007</v>
+        <v>4.3980127800000002</v>
       </c>
       <c r="J21">
         <v>5985</v>
@@ -2410,7 +2470,7 @@
         <v>82.009343533333336</v>
       </c>
       <c r="M21" s="6">
-        <v>40.761109433333338</v>
+        <v>28.033140100000001</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -2427,7 +2487,7 @@
         <v>3.531658E-2</v>
       </c>
       <c r="E22" s="7">
-        <v>0.90906603999999991</v>
+        <v>0.58412838499999997</v>
       </c>
       <c r="F22">
         <v>1330</v>
@@ -2439,7 +2499,7 @@
         <v>1.2547853400000002</v>
       </c>
       <c r="I22" s="5">
-        <v>7.5400198200000004</v>
+        <v>5.2699050600000001</v>
       </c>
       <c r="J22">
         <v>7315</v>
@@ -2448,7 +2508,7 @@
         <v>143.72249239999999</v>
       </c>
       <c r="M22" s="6">
-        <v>53.679607900000001</v>
+        <v>36.964761099999997</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -2465,7 +2525,7 @@
         <v>4.0417000000000002E-2</v>
       </c>
       <c r="E23" s="7">
-        <v>0.99607999999999997</v>
+        <v>0.69107876499999998</v>
       </c>
       <c r="F23">
         <v>1540</v>
@@ -2477,7 +2537,7 @@
         <v>1.6707743799999999</v>
       </c>
       <c r="I23" s="5">
-        <v>9.2921912000000013</v>
+        <v>6.5965324399999998</v>
       </c>
       <c r="J23">
         <v>8855</v>
@@ -2486,7 +2546,7 @@
         <v>284.22466589999999</v>
       </c>
       <c r="M23" s="6">
-        <v>70.480605499999996</v>
+        <v>47.428557900000001</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -2503,11 +2563,16 @@
         <v>5.5109740000000004E-2</v>
       </c>
       <c r="E24" s="7">
-        <v>1.24023306</v>
+        <v>0.79010034500000004</v>
+      </c>
+      <c r="F24">
+        <v>1771</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="6"/>
-      <c r="I24" s="5"/>
+      <c r="I24" s="5">
+        <v>8.1195292333333331</v>
+      </c>
       <c r="L24" s="5"/>
       <c r="M24" s="6"/>
     </row>
@@ -2518,18 +2583,23 @@
       <c r="B25">
         <v>253</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="7">
         <v>0.89569849999999995</v>
       </c>
       <c r="D25" s="6">
         <v>5.9378299999999995E-2</v>
       </c>
-      <c r="E25" s="7">
-        <v>1.27388452</v>
+      <c r="E25" s="5">
+        <v>0.9149621950000002</v>
+      </c>
+      <c r="F25">
+        <v>2024</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="6"/>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5">
+        <v>9.989284266666667</v>
+      </c>
       <c r="L25" s="5"/>
       <c r="M25" s="6"/>
     </row>
@@ -2540,18 +2610,23 @@
       <c r="B26">
         <v>276</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="7">
         <v>1.08964112</v>
       </c>
       <c r="D26" s="6">
         <v>6.9736980000000018E-2</v>
       </c>
-      <c r="E26" s="7">
-        <v>1.5986215399999999</v>
+      <c r="E26" s="5">
+        <v>1.0752771999999997</v>
+      </c>
+      <c r="F26">
+        <v>2300</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="6"/>
-      <c r="I26" s="5"/>
+      <c r="I26" s="5">
+        <v>12.581238600000001</v>
+      </c>
       <c r="L26" s="5"/>
       <c r="M26" s="6"/>
     </row>
@@ -2562,18 +2637,23 @@
       <c r="B27">
         <v>300</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="7">
         <v>1.3699703200000002</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="6">
         <v>7.5921020000000006E-2</v>
       </c>
-      <c r="E27" s="9">
-        <v>1.7043411799999997</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
+      <c r="E27" s="5">
+        <v>1.2560447750000001</v>
+      </c>
+      <c r="F27">
+        <v>2600</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="5">
+        <v>14.702419566666668</v>
+      </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
@@ -2582,14 +2662,14 @@
       <c r="B28">
         <v>325</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="7">
         <v>1.69150998</v>
       </c>
       <c r="D28" s="6">
         <v>9.1298459999999998E-2</v>
       </c>
-      <c r="E28" s="7">
-        <v>2.0182782599999998</v>
+      <c r="E28" s="5">
+        <v>1.4090005600000002</v>
       </c>
       <c r="F28">
         <v>2925</v>
@@ -2601,7 +2681,7 @@
         <v>8.908031059999999</v>
       </c>
       <c r="I28" s="5">
-        <v>22.9</v>
+        <v>18.113736433333333</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
@@ -2611,18 +2691,23 @@
       <c r="B29">
         <v>351</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="7">
         <v>1.98505942</v>
       </c>
       <c r="D29" s="6">
         <v>0.10076236000000001</v>
       </c>
-      <c r="E29" s="7">
-        <v>2.1781020400000002</v>
+      <c r="E29" s="5">
+        <v>1.5488192250000004</v>
+      </c>
+      <c r="F29">
+        <v>3276</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="6"/>
-      <c r="I29" s="5"/>
+      <c r="I29" s="5">
+        <v>21.148166566666671</v>
+      </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
@@ -2631,18 +2716,23 @@
       <c r="B30">
         <v>378</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="7">
         <v>2.3568667400000001</v>
       </c>
       <c r="D30" s="6">
         <v>0.11699650000000002</v>
       </c>
-      <c r="E30" s="7">
-        <v>2.5533071000000001</v>
+      <c r="E30" s="5">
+        <v>1.75114831</v>
+      </c>
+      <c r="F30">
+        <v>3654</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="6"/>
-      <c r="I30" s="5"/>
+      <c r="I30" s="5">
+        <v>24.842484366666667</v>
+      </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
@@ -2658,11 +2748,16 @@
         <v>0.12802649999999999</v>
       </c>
       <c r="E31" s="63">
-        <v>2.8400937000000002</v>
+        <v>1.942846665</v>
+      </c>
+      <c r="F31">
+        <v>4060</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="6"/>
-      <c r="I31" s="5"/>
+      <c r="I31" s="5">
+        <v>28.946058966666669</v>
+      </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
@@ -2678,11 +2773,16 @@
         <v>0.14873066000000001</v>
       </c>
       <c r="E32" s="63">
-        <v>3.0378674799999996</v>
+        <v>2.1799970800000001</v>
+      </c>
+      <c r="F32">
+        <v>4495</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="5"/>
+      <c r="I32" s="5">
+        <v>35.305066600000004</v>
+      </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
@@ -2698,7 +2798,7 @@
         <v>0.16683683999999999</v>
       </c>
       <c r="E33" s="5">
-        <v>3.4178486399999999</v>
+        <v>2.5384637550000004</v>
       </c>
       <c r="F33">
         <v>4960</v>
@@ -2710,7 +2810,7 @@
         <v>38.040107039999995</v>
       </c>
       <c r="I33" s="5">
-        <v>50.43</v>
+        <v>42.129151199999995</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -2727,7 +2827,7 @@
         <v>0.30069123999999997</v>
       </c>
       <c r="E34" s="5">
-        <v>5.8926999999999996</v>
+        <v>4.17852026</v>
       </c>
       <c r="F34">
         <v>7770</v>
@@ -2737,7 +2837,7 @@
         <v>125.1647718</v>
       </c>
       <c r="I34" s="6">
-        <v>108.44</v>
+        <v>95.136749099999989</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -2754,7 +2854,7 @@
         <v>0.49568519999999994</v>
       </c>
       <c r="E35" s="5">
-        <v>10.06</v>
+        <v>6.3664312000000001</v>
       </c>
       <c r="F35">
         <v>11480</v>
@@ -2764,7 +2864,7 @@
         <v>370.39367979999997</v>
       </c>
       <c r="I35" s="6">
-        <v>192.76</v>
+        <v>175.14812790000002</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -2781,7 +2881,7 @@
         <v>0.80555524000000001</v>
       </c>
       <c r="E36" s="5">
-        <v>14.856</v>
+        <v>9.8831791400000011</v>
       </c>
       <c r="F36">
         <v>16215</v>
@@ -2790,7 +2890,7 @@
         <v>1086.0201896999999</v>
       </c>
       <c r="I36" s="51">
-        <v>397.25</v>
+        <v>332.94932940000001</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -2807,10 +2907,13 @@
         <v>1.3144702333333333</v>
       </c>
       <c r="E37" s="5">
-        <v>22.384</v>
+        <v>15.868211633333333</v>
+      </c>
+      <c r="F37">
+        <v>22100</v>
       </c>
       <c r="I37" s="52">
-        <v>701.53599999999994</v>
+        <v>594.58825760000002</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -2833,7 +2936,7 @@
         <v>2.800247933333333</v>
       </c>
       <c r="E39" s="5">
-        <v>47.697000000000003</v>
+        <v>31.2651982</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
@@ -2850,7 +2953,7 @@
         <v>6.2341727999999996</v>
       </c>
       <c r="E40" s="5">
-        <v>93.001000000000005</v>
+        <v>55.996203399999999</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
@@ -2864,7 +2967,7 @@
         <v>12.487203200000002</v>
       </c>
       <c r="E41" s="5">
-        <v>158.82</v>
+        <v>110.90585229999999</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
@@ -2878,7 +2981,7 @@
         <v>23.887301400000002</v>
       </c>
       <c r="E42" s="5">
-        <v>266.63</v>
+        <v>168.2752265</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
@@ -2892,7 +2995,7 @@
         <v>40.637031233333332</v>
       </c>
       <c r="E43" s="5">
-        <v>450.76</v>
+        <v>282.60610249999996</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -2911,7 +3014,7 @@
         <v>381.6920283</v>
       </c>
       <c r="E45" s="50">
-        <v>2941.06</v>
+        <v>2115.6538992000001</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -3214,7 +3317,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78DD4B41-E54D-4E4B-A641-06B53D0464D3}">
-  <dimension ref="A1:R160"/>
+  <dimension ref="A1:V161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="4" style="16" bestFit="1" customWidth="1"/>
@@ -3232,10 +3335,13 @@
     <col min="14" max="15" width="12" style="19" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.6640625" style="18" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="12" style="19" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="16"/>
+    <col min="19" max="19" width="16" style="69" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.6640625" style="69" customWidth="1"/>
+    <col min="21" max="22" width="8.88671875" style="67"/>
+    <col min="23" max="16384" width="8.88671875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
         <v>23</v>
       </c>
@@ -3290,8 +3396,17 @@
       <c r="R1" s="44" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S1" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="T1" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="U1" s="66" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -3314,19 +3429,19 @@
         <v>0</v>
       </c>
       <c r="H2" s="22">
-        <v>37.416666666666671</v>
+        <v>17.249999999999996</v>
       </c>
       <c r="I2" s="22">
-        <v>5.1902000000000003E-4</v>
+        <v>6.6805000000000098E-4</v>
       </c>
       <c r="J2" s="22">
-        <v>1.9029000000000001E-2</v>
+        <v>1.985483E-2</v>
       </c>
       <c r="K2" s="23">
-        <v>3.6085022794943392E-16</v>
+        <v>6.6476105091071594E-16</v>
       </c>
       <c r="L2" s="27">
-        <v>1.0549862847332312E-16</v>
+        <v>1.4871270873652407E-16</v>
       </c>
       <c r="M2" s="30">
         <v>7.3952999999999996E-4</v>
@@ -3347,7 +3462,7 @@
         <v>5.9272017089337676E-16</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="20">
         <v>2</v>
       </c>
@@ -3370,19 +3485,19 @@
         <v>0</v>
       </c>
       <c r="H3" s="22">
-        <v>37.949999999999996</v>
+        <v>18.358333333333331</v>
       </c>
       <c r="I3" s="22">
-        <v>7.0985000000000004E-4</v>
+        <v>8.8916999999999902E-4</v>
       </c>
       <c r="J3" s="22">
-        <v>2.3864E-2</v>
+        <v>3.0805554999999998E-2</v>
       </c>
       <c r="K3" s="23">
-        <v>5.3428629991318204E-16</v>
+        <v>1.0251605734416759E-15</v>
       </c>
       <c r="L3" s="27">
-        <v>1.0384519022631201E-16</v>
+        <v>1.0741390525641387E-16</v>
       </c>
       <c r="M3" s="30">
         <v>1.0246000000000001E-3</v>
@@ -3403,7 +3518,7 @@
         <v>5.2996279196627281E-16</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="20">
         <v>2</v>
       </c>
@@ -3426,19 +3541,19 @@
         <v>0</v>
       </c>
       <c r="H4" s="22">
-        <v>38.43</v>
+        <v>18.164999999999999</v>
       </c>
       <c r="I4" s="22">
-        <v>1.1516450000000002E-3</v>
+        <v>1.14091E-3</v>
       </c>
       <c r="J4" s="22">
-        <v>4.2245940000000003E-2</v>
+        <v>4.3799095000000003E-2</v>
       </c>
       <c r="K4" s="23">
-        <v>6.3549705202802216E-16</v>
+        <v>6.3820629949653316E-15</v>
       </c>
       <c r="L4" s="27">
-        <v>9.269485813104065E-17</v>
+        <v>9.2660390478903813E-17</v>
       </c>
       <c r="M4" s="30">
         <v>1.58939E-3</v>
@@ -3459,7 +3574,7 @@
         <v>3.4933669516830488E-16</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="20">
         <v>2</v>
       </c>
@@ -3482,19 +3597,19 @@
         <v>6.6666666666666671E-3</v>
       </c>
       <c r="H5" s="22">
-        <v>40.836666666666673</v>
+        <v>20.786666666666669</v>
       </c>
       <c r="I5" s="22">
-        <v>1.376185E-3</v>
+        <v>1.637E-3</v>
       </c>
       <c r="J5" s="22">
-        <v>5.2596234999999991E-2</v>
+        <v>5.2675250000000007E-2</v>
       </c>
       <c r="K5" s="23">
-        <v>7.8186122880255118E-16</v>
+        <v>2.0065368475387842E-15</v>
       </c>
       <c r="L5" s="27">
-        <v>9.1289347339606071E-17</v>
+        <v>9.7450602314897623E-17</v>
       </c>
       <c r="M5" s="30">
         <v>2.0284500000000002E-3</v>
@@ -3515,7 +3630,7 @@
         <v>4.4142888835188977E-16</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="20">
         <v>2</v>
       </c>
@@ -3535,22 +3650,22 @@
         <v>21</v>
       </c>
       <c r="G6" s="21">
-        <v>4.7619047619047623E-3</v>
+        <v>0</v>
       </c>
       <c r="H6" s="22">
-        <v>42.295238095238098</v>
+        <v>21.464285714285712</v>
       </c>
       <c r="I6" s="22">
-        <v>1.7841500000000004E-3</v>
+        <v>2.2006999999999999E-3</v>
       </c>
       <c r="J6" s="22">
-        <v>7.8147800000000003E-2</v>
+        <v>6.2096049999999979E-2</v>
       </c>
       <c r="K6" s="23">
-        <v>1.0607315651283371E-15</v>
+        <v>1.7911300476473016E-15</v>
       </c>
       <c r="L6" s="27">
-        <v>9.4924669931457535E-17</v>
+        <v>9.4642885895182265E-17</v>
       </c>
       <c r="M6" s="30">
         <v>2.9149549999999995E-3</v>
@@ -3571,7 +3686,7 @@
         <v>6.1218422523590752E-16</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="20">
         <v>2</v>
       </c>
@@ -3591,22 +3706,22 @@
         <v>28</v>
       </c>
       <c r="G7" s="21">
-        <v>3.5714285714285718E-3</v>
+        <v>0</v>
       </c>
       <c r="H7" s="22">
-        <v>43.35535714285713</v>
+        <v>22.783928571428568</v>
       </c>
       <c r="I7" s="22">
-        <v>2.2427299999999992E-3</v>
+        <v>2.8816650000000007E-3</v>
       </c>
       <c r="J7" s="22">
-        <v>9.4563604999999995E-2</v>
+        <v>8.2486694999999999E-2</v>
       </c>
       <c r="K7" s="23">
-        <v>1.2184187240062708E-15</v>
+        <v>2.4003620004368138E-15</v>
       </c>
       <c r="L7" s="27">
-        <v>9.5395735656211058E-17</v>
+        <v>9.460744161122868E-17</v>
       </c>
       <c r="M7" s="30">
         <v>2.8811699999999997E-3</v>
@@ -3627,7 +3742,7 @@
         <v>5.9834603778956113E-16</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="20">
         <v>2</v>
       </c>
@@ -3647,22 +3762,22 @@
         <v>36</v>
       </c>
       <c r="G8" s="21">
-        <v>8.3333333333333332E-3</v>
+        <v>5.5555555555555558E-3</v>
       </c>
       <c r="H8" s="22">
-        <v>44.311111111111117</v>
+        <v>24.6</v>
       </c>
       <c r="I8" s="22">
-        <v>3.0042799999999998E-3</v>
+        <v>4.5765500000000004E-3</v>
       </c>
       <c r="J8" s="22">
-        <v>0.13076563499999999</v>
+        <v>0.10883477000000004</v>
       </c>
       <c r="K8" s="23">
-        <v>1.1049044974897303E-15</v>
+        <v>4.388090394311456E-15</v>
       </c>
       <c r="L8" s="27">
-        <v>9.3450569558283478E-17</v>
+        <v>9.6926112942468842E-17</v>
       </c>
       <c r="M8" s="30">
         <v>4.3376150000000013E-3</v>
@@ -3683,7 +3798,7 @@
         <v>6.6948757332753836E-16</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="20">
         <v>2</v>
       </c>
@@ -3703,22 +3818,22 @@
         <v>45</v>
       </c>
       <c r="G9" s="21">
-        <v>1.1111111111111112E-2</v>
+        <v>6.6666666666666662E-3</v>
       </c>
       <c r="H9" s="22">
-        <v>45.994444444444447</v>
+        <v>26.690000000000005</v>
       </c>
       <c r="I9" s="22">
-        <v>3.2727049999999999E-3</v>
+        <v>4.3009249999999997E-3</v>
       </c>
       <c r="J9" s="22">
-        <v>0.16253485500000003</v>
+        <v>0.130007495</v>
       </c>
       <c r="K9" s="23">
-        <v>1.1594579113393595E-15</v>
+        <v>2.3683051687901541E-15</v>
       </c>
       <c r="L9" s="27">
-        <v>9.6302353422905139E-17</v>
+        <v>9.7490299950827517E-17</v>
       </c>
       <c r="M9" s="30">
         <v>4.9303649999999999E-3</v>
@@ -3739,7 +3854,7 @@
         <v>1.4250195290242512E-15</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="20">
         <v>2</v>
       </c>
@@ -3759,22 +3874,22 @@
         <v>55</v>
       </c>
       <c r="G10" s="21">
-        <v>7.2727272727272727E-3</v>
+        <v>9.0909090909090905E-3</v>
       </c>
       <c r="H10" s="22">
-        <v>46.943636363636365</v>
+        <v>27.421818181818178</v>
       </c>
       <c r="I10" s="22">
-        <v>4.1480800000000002E-3</v>
+        <v>4.3764499999999996E-3</v>
       </c>
       <c r="J10" s="22">
-        <v>0.19085728999999999</v>
+        <v>0.14224112000000003</v>
       </c>
       <c r="K10" s="23">
-        <v>1.4509786350843225E-15</v>
+        <v>3.4552741402881735E-15</v>
       </c>
       <c r="L10" s="27">
-        <v>9.5967879171709235E-17</v>
+        <v>9.8450170249782374E-17</v>
       </c>
       <c r="M10" s="30">
         <v>6.4831199999999993E-3</v>
@@ -3795,7 +3910,7 @@
         <v>1.7643512804122316E-15</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="20">
         <v>2</v>
       </c>
@@ -3803,7 +3918,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D11" s="34">
         <v>5</v>
@@ -3815,22 +3930,22 @@
         <v>66</v>
       </c>
       <c r="G11" s="21">
-        <v>0</v>
+        <v>4.5454545454545452E-3</v>
       </c>
       <c r="H11" s="22">
-        <v>47.903030303030306</v>
+        <v>28.695454545454545</v>
       </c>
       <c r="I11" s="22">
-        <v>4.6990000000000001E-3</v>
+        <v>5.1829900000000002E-3</v>
       </c>
       <c r="J11" s="22">
-        <v>0.21668550000000003</v>
+        <v>0.15834911500000001</v>
       </c>
       <c r="K11" s="23">
-        <v>1.7123829575852314E-15</v>
+        <v>3.0293475691483342E-15</v>
       </c>
       <c r="L11" s="27">
-        <v>9.8925796937170564E-17</v>
+        <v>9.8473024182128511E-17</v>
       </c>
       <c r="M11" s="30">
         <v>7.9231799999999984E-3</v>
@@ -3851,7 +3966,7 @@
         <v>1.5888123130548142E-15</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="20">
         <v>2</v>
       </c>
@@ -3859,7 +3974,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D12" s="34">
         <v>5</v>
@@ -3871,22 +3986,22 @@
         <v>78</v>
       </c>
       <c r="G12" s="21">
-        <v>5.1282051282051282E-3</v>
+        <v>1.3461538461538462E-2</v>
       </c>
       <c r="H12" s="22">
-        <v>48.035897435897439</v>
+        <v>30.328205128205127</v>
       </c>
       <c r="I12" s="22">
-        <v>5.9587999999999993E-3</v>
+        <v>5.2430050000000002E-3</v>
       </c>
       <c r="J12" s="22">
-        <v>0.25790239999999998</v>
+        <v>0.19490289500000002</v>
       </c>
       <c r="K12" s="23">
-        <v>1.4253917453114702E-15</v>
+        <v>4.0897654333766215E-15</v>
       </c>
       <c r="L12" s="27">
-        <v>9.678915953398272E-17</v>
+        <v>1.0070488883126816E-16</v>
       </c>
       <c r="M12" s="30">
         <v>9.9332399999999994E-3</v>
@@ -3907,7 +4022,7 @@
         <v>2.3356029560573503E-15</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="20">
         <v>2</v>
       </c>
@@ -3915,7 +4030,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D13" s="34">
         <v>5</v>
@@ -3927,22 +4042,22 @@
         <v>91</v>
       </c>
       <c r="G13" s="21">
-        <v>4.3956043956043956E-3</v>
+        <v>9.8901098901098897E-3</v>
       </c>
       <c r="H13" s="22">
-        <v>49.795604395604393</v>
+        <v>31.519230769230774</v>
       </c>
       <c r="I13" s="22">
-        <v>6.461800000000001E-3</v>
+        <v>6.3392850000000001E-3</v>
       </c>
       <c r="J13" s="22">
-        <v>0.31560336</v>
+        <v>0.23170724500000003</v>
       </c>
       <c r="K13" s="23">
-        <v>1.4667725853332236E-15</v>
+        <v>3.5643724070393367E-15</v>
       </c>
       <c r="L13" s="27">
-        <v>1.0086875847266312E-16</v>
+        <v>1.0041707028599198E-16</v>
       </c>
       <c r="M13" s="30">
         <v>1.151434E-2</v>
@@ -3963,7 +4078,7 @@
         <v>3.6181620657799192E-15</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
         <v>2</v>
       </c>
@@ -3971,7 +4086,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D14" s="34">
         <v>5</v>
@@ -3983,22 +4098,22 @@
         <v>105</v>
       </c>
       <c r="G14" s="21">
-        <v>7.619047619047619E-3</v>
+        <v>1.0476190476190477E-2</v>
       </c>
       <c r="H14" s="22">
-        <v>50.161904761904758</v>
+        <v>32.881904761904764</v>
       </c>
       <c r="I14" s="22">
-        <v>8.3471599999999993E-3</v>
+        <v>7.4810100000000006E-3</v>
       </c>
       <c r="J14" s="22">
-        <v>0.38776778000000001</v>
+        <v>0.27117799999999997</v>
       </c>
       <c r="K14" s="23">
-        <v>1.451996640218956E-15</v>
+        <v>3.8799261807797476E-14</v>
       </c>
       <c r="L14" s="27">
-        <v>1.0012773699733318E-16</v>
+        <v>1.0189212509884523E-16</v>
       </c>
       <c r="M14" s="30">
         <v>1.62122E-2</v>
@@ -4019,7 +4134,7 @@
         <v>2.7838264868631072E-15</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="20">
         <v>2</v>
       </c>
@@ -4027,7 +4142,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D15" s="34">
         <v>5</v>
@@ -4039,22 +4154,22 @@
         <v>120</v>
       </c>
       <c r="G15" s="21">
-        <v>6.6666666666666671E-3</v>
+        <v>1.0833333333333334E-2</v>
       </c>
       <c r="H15" s="22">
-        <v>53.04</v>
+        <v>33.717916666666682</v>
       </c>
       <c r="I15" s="22">
-        <v>8.29476E-3</v>
+        <v>8.1833949999999996E-3</v>
       </c>
       <c r="J15" s="22">
-        <v>0.51535036000000001</v>
+        <v>0.32632619000000007</v>
       </c>
       <c r="K15" s="23">
-        <v>3.5676156156611688E-14</v>
+        <v>2.0962637031720853E-14</v>
       </c>
       <c r="L15" s="27">
-        <v>1.0177778270133074E-16</v>
+        <v>1.0358229404531319E-16</v>
       </c>
       <c r="M15" s="30">
         <v>1.9705760000000003E-2</v>
@@ -4075,7 +4190,7 @@
         <v>7.3576942600163309E-15</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="20">
         <v>2</v>
       </c>
@@ -4083,7 +4198,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D16" s="34">
         <v>5</v>
@@ -4095,22 +4210,22 @@
         <v>136</v>
       </c>
       <c r="G16" s="21">
-        <v>1.1764705882352941E-2</v>
+        <v>1.4338235294117646E-2</v>
       </c>
       <c r="H16" s="22">
-        <v>53.510294117647064</v>
+        <v>35.930882352941182</v>
       </c>
       <c r="I16" s="22">
-        <v>8.7395600000000004E-3</v>
+        <v>9.6065099999999987E-3</v>
       </c>
       <c r="J16" s="22">
-        <v>0.66134314000000005</v>
+        <v>0.41870578999999991</v>
       </c>
       <c r="K16" s="23">
-        <v>1.5115708687693088E-15</v>
+        <v>6.9524829709115067E-15</v>
       </c>
       <c r="L16" s="27">
-        <v>1.026061610572041E-16</v>
+        <v>1.0519104559057617E-16</v>
       </c>
       <c r="M16" s="30">
         <v>2.3229080000000003E-2</v>
@@ -4131,7 +4246,7 @@
         <v>4.0227697672686556E-15</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="20">
         <v>2</v>
       </c>
@@ -4139,7 +4254,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D17" s="34">
         <v>5</v>
@@ -4151,22 +4266,22 @@
         <v>153</v>
       </c>
       <c r="G17" s="21">
-        <v>1.3071895424836602E-2</v>
+        <v>1.4379084967320262E-2</v>
       </c>
       <c r="H17" s="22">
-        <v>54.665359477124184</v>
+        <v>36.586928104575179</v>
       </c>
       <c r="I17" s="22">
-        <v>1.0559200000000001E-2</v>
+        <v>1.0477994999999999E-2</v>
       </c>
       <c r="J17" s="22">
-        <v>0.69582818000000013</v>
+        <v>0.4737934949999999</v>
       </c>
       <c r="K17" s="23">
-        <v>1.3911416918388427E-15</v>
+        <v>4.7457015638136598E-14</v>
       </c>
       <c r="L17" s="27">
-        <v>1.0238517299890162E-16</v>
+        <v>1.0500785949504587E-16</v>
       </c>
       <c r="M17" s="30">
         <v>2.5294240000000003E-2</v>
@@ -4187,7 +4302,7 @@
         <v>8.7552025679730782E-14</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="20">
         <v>2</v>
       </c>
@@ -4195,7 +4310,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D18" s="34">
         <v>5</v>
@@ -4210,19 +4325,19 @@
         <v>1.4035087719298246E-2</v>
       </c>
       <c r="H18" s="22">
-        <v>55.886549707602342</v>
+        <v>37.657309941520467</v>
       </c>
       <c r="I18" s="22">
-        <v>1.1049659999999999E-2</v>
+        <v>1.2134030000000001E-2</v>
       </c>
       <c r="J18" s="22">
-        <v>0.8702651400000001</v>
+        <v>0.52304658500000012</v>
       </c>
       <c r="K18" s="23">
-        <v>1.6258729870068966E-15</v>
+        <v>3.9985903938676434E-14</v>
       </c>
       <c r="L18" s="27">
-        <v>1.0441513158341605E-16</v>
+        <v>1.0616823006634725E-16</v>
       </c>
       <c r="M18" s="30">
         <v>3.1552719999999999E-2</v>
@@ -4243,7 +4358,7 @@
         <v>4.5350729665076063E-14</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="20">
         <v>2</v>
       </c>
@@ -4251,7 +4366,7 @@
         <v>19</v>
       </c>
       <c r="C19" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D19" s="34">
         <v>5</v>
@@ -4263,22 +4378,22 @@
         <v>190</v>
       </c>
       <c r="G19" s="21">
-        <v>6.3157894736842104E-3</v>
+        <v>1.2105263157894735E-2</v>
       </c>
       <c r="H19" s="22">
-        <v>56.397894736842112</v>
+        <v>38.788157894736841</v>
       </c>
       <c r="I19" s="22">
-        <v>1.180688E-2</v>
+        <v>1.2900415000000002E-2</v>
       </c>
       <c r="J19" s="22">
-        <v>0.90906603999999991</v>
+        <v>0.58412838499999997</v>
       </c>
       <c r="K19" s="23">
-        <v>1.5533597758784119E-15</v>
+        <v>1.6340526627852346E-14</v>
       </c>
       <c r="L19" s="27">
-        <v>1.0750700466541568E-16</v>
+        <v>1.0768966235382596E-16</v>
       </c>
       <c r="M19" s="30">
         <v>3.531658E-2</v>
@@ -4299,7 +4414,7 @@
         <v>1.7931018418150177E-14</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
         <v>2</v>
       </c>
@@ -4307,7 +4422,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D20" s="34">
         <v>5</v>
@@ -4319,22 +4434,22 @@
         <v>210</v>
       </c>
       <c r="G20" s="59">
-        <v>7.619047619047619E-3</v>
+        <v>1.7142857142857144E-2</v>
       </c>
       <c r="H20" s="60">
-        <v>55.771999999999998</v>
+        <v>40.341904761904757</v>
       </c>
       <c r="I20" s="60">
-        <v>1.389E-2</v>
+        <v>1.4739435000000004E-2</v>
       </c>
       <c r="J20" s="60">
-        <v>0.99607999999999997</v>
+        <v>0.69107876499999998</v>
       </c>
       <c r="K20" s="61">
-        <v>1.6067936220055009E-15</v>
+        <v>2.7392339443222676E-14</v>
       </c>
       <c r="L20" s="62">
-        <v>1.0617863916342263E-16</v>
+        <v>1.0857447766926479E-16</v>
       </c>
       <c r="M20" s="30">
         <v>4.0417000000000002E-2</v>
@@ -4355,7 +4470,7 @@
         <v>3.7378083601096163E-13</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
         <v>2</v>
       </c>
@@ -4363,7 +4478,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D21" s="34">
         <v>0</v>
@@ -4375,22 +4490,22 @@
         <v>231</v>
       </c>
       <c r="G21" s="59">
-        <v>1.2121212121212121E-2</v>
+        <v>1.6883116883116882E-2</v>
       </c>
       <c r="H21" s="60">
-        <v>57.031168831168827</v>
+        <v>41.462554112554109</v>
       </c>
       <c r="I21" s="60">
-        <v>1.5743879999999998E-2</v>
+        <v>1.5864969999999999E-2</v>
       </c>
       <c r="J21" s="60">
-        <v>1.24023306</v>
+        <v>0.79010034500000004</v>
       </c>
       <c r="K21" s="61">
-        <v>7.619843099287671E-15</v>
+        <v>2.8778156041185635E-14</v>
       </c>
       <c r="L21" s="62">
-        <v>1.0757862500528673E-16</v>
+        <v>1.0878871946916689E-16</v>
       </c>
       <c r="M21" s="30">
         <v>5.5109740000000004E-2</v>
@@ -4411,7 +4526,7 @@
         <v>4.6699618554977332E-13</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="20">
         <v>2</v>
       </c>
@@ -4419,7 +4534,7 @@
         <v>22</v>
       </c>
       <c r="C22" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D22" s="34">
         <v>0</v>
@@ -4431,22 +4546,22 @@
         <v>253</v>
       </c>
       <c r="G22" s="59">
-        <v>4.7430830039525687E-3</v>
+        <v>1.6996047430830039E-2</v>
       </c>
       <c r="H22" s="60">
-        <v>56.976284584980235</v>
+        <v>42.713043478260872</v>
       </c>
       <c r="I22" s="60">
-        <v>1.9343599999999999E-2</v>
+        <v>1.7344240000000004E-2</v>
       </c>
       <c r="J22" s="60">
-        <v>1.27388452</v>
+        <v>0.9149621950000002</v>
       </c>
       <c r="K22" s="61">
-        <v>1.6689333900618801E-15</v>
+        <v>3.3281802461311868E-14</v>
       </c>
       <c r="L22" s="62">
-        <v>1.0846447186479793E-16</v>
+        <v>1.0944128676858523E-16</v>
       </c>
       <c r="M22" s="30">
         <v>5.9378299999999995E-2</v>
@@ -4467,7 +4582,7 @@
         <v>1.2234113210397602E-13</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="20">
         <v>2</v>
       </c>
@@ -4475,7 +4590,7 @@
         <v>23</v>
       </c>
       <c r="C23" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D23" s="34">
         <v>0</v>
@@ -4487,22 +4602,22 @@
         <v>276</v>
       </c>
       <c r="G23" s="59">
-        <v>8.6956521739130436E-3</v>
+        <v>2.2463768115942029E-2</v>
       </c>
       <c r="H23" s="60">
-        <v>57.833333333333329</v>
+        <v>44.563768115942032</v>
       </c>
       <c r="I23" s="60">
-        <v>1.937678E-2</v>
+        <v>1.8125044999999999E-2</v>
       </c>
       <c r="J23" s="60">
-        <v>1.5986215399999999</v>
+        <v>1.0752771999999997</v>
       </c>
       <c r="K23" s="61">
-        <v>1.5722940425134174E-15</v>
+        <v>1.6152340165538887E-14</v>
       </c>
       <c r="L23" s="62">
-        <v>1.0905085374816065E-16</v>
+        <v>1.1140951351500981E-16</v>
       </c>
       <c r="M23" s="30">
         <v>6.9736980000000018E-2</v>
@@ -4523,7 +4638,7 @@
         <v>6.5073742330760481E-14</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="20">
         <v>2</v>
       </c>
@@ -4531,7 +4646,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D24" s="34">
         <v>0</v>
@@ -4543,22 +4658,22 @@
         <v>300</v>
       </c>
       <c r="G24" s="59">
-        <v>6.6666666666666671E-3</v>
+        <v>2.8833333333333336E-2</v>
       </c>
       <c r="H24" s="60">
-        <v>59.364666666666665</v>
+        <v>46.669000000000004</v>
       </c>
       <c r="I24" s="60">
-        <v>2.1626300000000001E-2</v>
+        <v>2.0395825000000003E-2</v>
       </c>
       <c r="J24" s="60">
-        <v>1.7043411799999997</v>
+        <v>1.2560447750000001</v>
       </c>
       <c r="K24" s="61">
-        <v>1.5916498305626947E-15</v>
+        <v>4.1937345141823692E-14</v>
       </c>
       <c r="L24" s="62">
-        <v>1.0986601719526259E-16</v>
+        <v>1.1265408644105274E-16</v>
       </c>
       <c r="M24" s="30">
         <v>7.5921020000000006E-2</v>
@@ -4579,7 +4694,7 @@
         <v>1.6485923791846004E-13</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="20">
         <v>2</v>
       </c>
@@ -4587,7 +4702,7 @@
         <v>25</v>
       </c>
       <c r="C25" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D25" s="34">
         <v>5</v>
@@ -4599,22 +4714,22 @@
         <v>325</v>
       </c>
       <c r="G25" s="59">
-        <v>1.5384615384615385E-2</v>
+        <v>3.2615384615384616E-2</v>
       </c>
       <c r="H25" s="60">
-        <v>61.105846153846166</v>
+        <v>47.982615384615386</v>
       </c>
       <c r="I25" s="60">
-        <v>2.0853660000000003E-2</v>
+        <v>2.2346830000000005E-2</v>
       </c>
       <c r="J25" s="60">
-        <v>2.0182782599999998</v>
+        <v>1.4090005600000002</v>
       </c>
       <c r="K25" s="61">
-        <v>1.6190073608290576E-15</v>
+        <v>4.8017049350330334E-14</v>
       </c>
       <c r="L25" s="62">
-        <v>1.103250804821175E-16</v>
+        <v>1.1261140175910624E-16</v>
       </c>
       <c r="M25" s="30">
         <v>9.1298459999999998E-2</v>
@@ -4634,8 +4749,22 @@
       <c r="R25" s="27">
         <v>2.4340357086863738E-12</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S25" s="69">
+        <v>7.2060000000000004</v>
+      </c>
+      <c r="T25" s="69">
+        <v>2.1820200000000001E-2</v>
+      </c>
+      <c r="U25" s="67">
+        <f>S25/J25</f>
+        <v>5.1142634038413721</v>
+      </c>
+      <c r="V25" s="67">
+        <f>(S25-T25)/(J25-I25)</f>
+        <v>5.1809472289812399</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="20">
         <v>2</v>
       </c>
@@ -4643,7 +4772,7 @@
         <v>26</v>
       </c>
       <c r="C26" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D26" s="34">
         <v>0</v>
@@ -4655,22 +4784,22 @@
         <v>351</v>
       </c>
       <c r="G26" s="59">
-        <v>1.0256410256410256E-2</v>
+        <v>2.6638176638176636E-2</v>
       </c>
       <c r="H26" s="60">
-        <v>61.393732193732191</v>
+        <v>48.510113960113969</v>
       </c>
       <c r="I26" s="60">
-        <v>2.97281E-2</v>
+        <v>2.3491724999999998E-2</v>
       </c>
       <c r="J26" s="60">
-        <v>2.1781020400000002</v>
+        <v>1.5488192250000004</v>
       </c>
       <c r="K26" s="61">
-        <v>1.7543192283689806E-15</v>
+        <v>9.5474811052637423E-15</v>
       </c>
       <c r="L26" s="62">
-        <v>1.1137116337889736E-16</v>
+        <v>1.1353206722203085E-16</v>
       </c>
       <c r="M26" s="30">
         <v>0.10076236000000001</v>
@@ -4691,7 +4820,7 @@
         <v>2.9724838784035458E-12</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="20">
         <v>2</v>
       </c>
@@ -4699,7 +4828,7 @@
         <v>27</v>
       </c>
       <c r="C27" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D27" s="34">
         <v>0</v>
@@ -4711,22 +4840,22 @@
         <v>378</v>
       </c>
       <c r="G27" s="59">
-        <v>1.3756613756613757E-2</v>
+        <v>3.0555555555555558E-2</v>
       </c>
       <c r="H27" s="60">
-        <v>62.403703703703698</v>
+        <v>49.616402116402114</v>
       </c>
       <c r="I27" s="60">
-        <v>2.5685920000000001E-2</v>
+        <v>2.4796125000000002E-2</v>
       </c>
       <c r="J27" s="60">
-        <v>2.5533071000000001</v>
+        <v>1.75114831</v>
       </c>
       <c r="K27" s="61">
-        <v>1.7257488314888615E-15</v>
+        <v>2.5778818783788179E-14</v>
       </c>
       <c r="L27" s="62">
-        <v>1.1183416191383584E-16</v>
+        <v>1.1354055921293978E-16</v>
       </c>
       <c r="M27" s="30">
         <v>0.11699650000000002</v>
@@ -4747,7 +4876,7 @@
         <v>1.4202209278090491E-12</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="20">
         <v>2</v>
       </c>
@@ -4755,7 +4884,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D28" s="34">
         <v>0</v>
@@ -4767,22 +4896,22 @@
         <v>406</v>
       </c>
       <c r="G28" s="59">
-        <v>9.852216748768473E-3</v>
+        <v>2.5738916256157634E-2</v>
       </c>
       <c r="H28" s="60">
-        <v>62.487684729064043</v>
+        <v>50.393842364532027</v>
       </c>
       <c r="I28" s="60">
-        <v>2.8239400000000005E-2</v>
+        <v>2.7020064999999999E-2</v>
       </c>
       <c r="J28" s="60">
-        <v>2.8400937000000002</v>
+        <v>1.942846665</v>
       </c>
       <c r="K28" s="61">
-        <v>1.6766947859729709E-15</v>
+        <v>1.3761007491756398E-14</v>
       </c>
       <c r="L28" s="62">
-        <v>1.1357907908948645E-16</v>
+        <v>1.1546506487495039E-16</v>
       </c>
       <c r="M28" s="30">
         <v>0.12802649999999999</v>
@@ -4803,7 +4932,7 @@
         <v>1.1422870420980384E-12</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="20">
         <v>2</v>
       </c>
@@ -4811,7 +4940,7 @@
         <v>29</v>
       </c>
       <c r="C29" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D29" s="34">
         <v>0</v>
@@ -4823,22 +4952,22 @@
         <v>435</v>
       </c>
       <c r="G29" s="59">
-        <v>9.1954022988505746E-3</v>
+        <v>3.1839080459770117E-2</v>
       </c>
       <c r="H29" s="60">
-        <v>63.611954022988506</v>
+        <v>52.089195402298841</v>
       </c>
       <c r="I29" s="60">
-        <v>2.861818E-2</v>
+        <v>2.9689365000000002E-2</v>
       </c>
       <c r="J29" s="60">
-        <v>3.0378674799999996</v>
+        <v>2.1799970800000001</v>
       </c>
       <c r="K29" s="61">
-        <v>1.7007793619427858E-15</v>
+        <v>1.8979789579368411E-14</v>
       </c>
       <c r="L29" s="62">
-        <v>1.1416914567724068E-16</v>
+        <v>1.1576647108819763E-16</v>
       </c>
       <c r="M29" s="30">
         <v>0.14873066000000001</v>
@@ -4859,7 +4988,7 @@
         <v>1.9269365271593541E-12</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="20">
         <v>2</v>
       </c>
@@ -4867,7 +4996,7 @@
         <v>30</v>
       </c>
       <c r="C30" s="33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D30" s="34">
         <v>5</v>
@@ -4879,22 +5008,22 @@
         <v>465</v>
       </c>
       <c r="G30" s="59">
-        <v>9.4623655913978495E-3</v>
+        <v>2.7096774193548386E-2</v>
       </c>
       <c r="H30" s="60">
-        <v>63.498494623655915</v>
+        <v>52.679677419354846</v>
       </c>
       <c r="I30" s="60">
-        <v>2.6155019999999994E-2</v>
+        <v>3.0870744999999995E-2</v>
       </c>
       <c r="J30" s="60">
-        <v>3.4178486399999999</v>
+        <v>2.5384637550000004</v>
       </c>
       <c r="K30" s="61">
-        <v>1.6717981636799012E-15</v>
+        <v>5.9839943010842651E-14</v>
       </c>
       <c r="L30" s="62">
-        <v>1.1602379808792252E-16</v>
+        <v>1.1574397875685501E-16</v>
       </c>
       <c r="M30" s="30">
         <v>0.16683683999999999</v>
@@ -4915,7 +5044,7 @@
         <v>4.7186430279132278E-12</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
         <v>2</v>
       </c>
@@ -4935,22 +5064,22 @@
         <v>630</v>
       </c>
       <c r="G31" s="21">
-        <v>1.2698412698412698E-2</v>
+        <v>3.3650793650793646E-2</v>
       </c>
       <c r="H31" s="22">
-        <v>68.92603174603174</v>
+        <v>57.499365079365077</v>
       </c>
       <c r="I31" s="22">
-        <v>3.8365959999999998E-2</v>
+        <v>4.0244800000000004E-2</v>
       </c>
       <c r="J31" s="22">
-        <v>6.4157302200000004</v>
+        <v>4.17852026</v>
       </c>
       <c r="K31" s="23">
-        <v>1.6895040079773959E-15</v>
+        <v>9.4920688551920749E-15</v>
       </c>
       <c r="L31" s="27">
-        <v>1.2033289590550148E-16</v>
+        <v>1.2177334783233279E-16</v>
       </c>
       <c r="M31" s="30">
         <v>0.30069123999999997</v>
@@ -4971,7 +5100,7 @@
         <v>3.4351269132525695E-10</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="20">
         <v>2</v>
       </c>
@@ -4991,22 +5120,22 @@
         <v>820</v>
       </c>
       <c r="G32" s="21">
-        <v>1.804878048780488E-2</v>
+        <v>3.3658536585365856E-2</v>
       </c>
       <c r="H32" s="22">
-        <v>73.898048780487812</v>
+        <v>61.383414634146348</v>
       </c>
       <c r="I32" s="22">
-        <v>5.561294E-2</v>
+        <v>5.0895939999999994E-2</v>
       </c>
       <c r="J32" s="22">
-        <v>10.25907248</v>
+        <v>6.3664312000000001</v>
       </c>
       <c r="K32" s="23">
-        <v>1.7005071762529194E-15</v>
+        <v>5.9873963495898767E-14</v>
       </c>
       <c r="L32" s="27">
-        <v>1.2233317635439223E-16</v>
+        <v>1.2389222667373658E-16</v>
       </c>
       <c r="M32" s="30">
         <v>0.49568519999999994</v>
@@ -5027,7 +5156,7 @@
         <v>4.6334124649263625E-9</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="20">
         <v>2</v>
       </c>
@@ -5047,22 +5176,22 @@
         <v>1035</v>
       </c>
       <c r="G33" s="21">
-        <v>2.1256038647342997E-2</v>
+        <v>4.4057971014492756E-2</v>
       </c>
       <c r="H33" s="22">
-        <v>77.230724637681163</v>
+        <v>67.037681159420302</v>
       </c>
       <c r="I33" s="22">
-        <v>6.802003999999999E-2</v>
+        <v>6.8991459999999991E-2</v>
       </c>
       <c r="J33" s="22">
-        <v>15.21545688</v>
+        <v>9.8831791400000011</v>
       </c>
       <c r="K33" s="23">
-        <v>9.3062557763510882E-15</v>
+        <v>6.4734862282219622E-14</v>
       </c>
       <c r="L33" s="27">
-        <v>1.2690834411971978E-16</v>
+        <v>1.2788068478916227E-16</v>
       </c>
       <c r="M33" s="30">
         <v>0.80555524000000001</v>
@@ -5083,7 +5212,7 @@
         <v>7.4246832903633801E-9</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="20">
         <v>2</v>
       </c>
@@ -5103,22 +5232,22 @@
         <v>1275</v>
       </c>
       <c r="G34" s="21">
-        <v>1.7254901960784313E-2</v>
+        <v>5.0980392156862744E-2</v>
       </c>
       <c r="H34" s="22">
-        <v>79.779869281045748</v>
+        <v>71.818300653594761</v>
       </c>
       <c r="I34" s="22">
-        <v>8.5954799999999998E-2</v>
+        <v>9.1101500000000002E-2</v>
       </c>
       <c r="J34" s="22">
-        <v>23.393247933333338</v>
+        <v>15.868211633333333</v>
       </c>
       <c r="K34" s="23">
-        <v>1.5074984744968749E-14</v>
+        <v>3.2304592674180124E-14</v>
       </c>
       <c r="L34" s="27">
-        <v>1.310104929684305E-16</v>
+        <v>1.3183193442487803E-16</v>
       </c>
       <c r="M34" s="30">
         <v>1.3144702333333333</v>
@@ -5138,8 +5267,22 @@
       <c r="R34" s="27">
         <v>6.442172439304426E-7</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S34" s="69">
+        <v>104.61</v>
+      </c>
+      <c r="T34" s="69">
+        <v>0.119522</v>
+      </c>
+      <c r="U34" s="67">
+        <f>S34/J34</f>
+        <v>6.5924253102506203</v>
+      </c>
+      <c r="V34" s="67">
+        <f>(S34-T34)/(J34-I34)</f>
+        <v>6.6229161815405044</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="20">
         <v>2</v>
       </c>
@@ -5159,22 +5302,22 @@
         <v>1830</v>
       </c>
       <c r="G35" s="21">
-        <v>2.222222222222222E-2</v>
+        <v>3.9344262295081971E-2</v>
       </c>
       <c r="H35" s="22">
-        <v>87.347176684881603</v>
+        <v>77.313661202185799</v>
       </c>
       <c r="I35" s="22">
-        <v>0.13172706666666667</v>
+        <v>0.1308067</v>
       </c>
       <c r="J35" s="22">
-        <v>47.697023233333333</v>
+        <v>31.2651982</v>
       </c>
       <c r="K35" s="23">
-        <v>1.7508332407106472E-15</v>
+        <v>3.8892216422202066E-15</v>
       </c>
       <c r="L35" s="27">
-        <v>1.3793345777927318E-16</v>
+        <v>1.381700791554997E-16</v>
       </c>
       <c r="M35" s="30">
         <v>2.800247933333333</v>
@@ -5195,7 +5338,7 @@
         <v>1.0073677694000527E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="20">
         <v>2</v>
       </c>
@@ -5215,22 +5358,22 @@
         <v>2485</v>
       </c>
       <c r="G36" s="21">
-        <v>2.9107981220657275E-2</v>
+        <v>4.1448692152917507E-2</v>
       </c>
       <c r="H36" s="22">
-        <v>94.904493628437294</v>
+        <v>82.989134808853123</v>
       </c>
       <c r="I36" s="22">
-        <v>0.18128160000000001</v>
+        <v>0.2229844</v>
       </c>
       <c r="J36" s="22">
-        <v>93.000638766666668</v>
+        <v>55.996203399999999</v>
       </c>
       <c r="K36" s="23">
-        <v>3.6847161346397225E-14</v>
+        <v>5.6646440431938585E-15</v>
       </c>
       <c r="L36" s="27">
-        <v>1.4406298353887348E-16</v>
+        <v>1.4537046240614609E-16</v>
       </c>
       <c r="M36" s="30">
         <v>6.2341727999999996</v>
@@ -5247,7 +5390,7 @@
       <c r="Q36" s="23"/>
       <c r="R36" s="27"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="20">
         <v>2</v>
       </c>
@@ -5267,22 +5410,22 @@
         <v>3240</v>
       </c>
       <c r="G37" s="21">
-        <v>2.6499999999999999E-2</v>
+        <v>7.098765432098765E-2</v>
       </c>
       <c r="H37" s="22">
-        <v>93.54</v>
+        <v>100.51018518518518</v>
       </c>
       <c r="I37" s="22">
-        <v>0.24102670000000001</v>
+        <v>0.33151960000000003</v>
       </c>
       <c r="J37" s="22">
-        <v>146.54</v>
+        <v>110.90585229999999</v>
       </c>
       <c r="K37" s="23">
-        <v>1.7319995116485418E-15</v>
+        <v>3.8677091728740458E-13</v>
       </c>
       <c r="L37" s="27">
-        <v>1.5265413854932524E-16</v>
+        <v>1.5410995223273906E-16</v>
       </c>
       <c r="M37" s="30">
         <v>12.487203200000002</v>
@@ -5299,7 +5442,7 @@
       <c r="Q37" s="23"/>
       <c r="R37" s="27"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="20">
         <v>2</v>
       </c>
@@ -5319,22 +5462,22 @@
         <v>4095</v>
       </c>
       <c r="G38" s="21">
-        <v>2.3699999999999999E-2</v>
+        <v>7.0818070818070816E-2</v>
       </c>
       <c r="H38" s="22">
-        <v>98.64</v>
+        <v>104.26202686202686</v>
       </c>
       <c r="I38" s="22">
-        <v>0.34195170000000003</v>
+        <v>0.41936560000000001</v>
       </c>
       <c r="J38" s="22">
-        <v>242.09</v>
+        <v>168.2752265</v>
       </c>
       <c r="K38" s="23">
-        <v>2.76E-14</v>
+        <v>3.1471110156093829E-13</v>
       </c>
       <c r="L38" s="27">
-        <v>1.5758781614617004E-16</v>
+        <v>1.5969692082746394E-16</v>
       </c>
       <c r="M38" s="30">
         <v>23.887301400000002</v>
@@ -5351,7 +5494,7 @@
       <c r="Q38" s="23"/>
       <c r="R38" s="27"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="20">
         <v>2</v>
       </c>
@@ -5371,22 +5514,22 @@
         <v>5050</v>
       </c>
       <c r="G39" s="59">
-        <v>3.9E-2</v>
+        <v>6.8316831683168322E-2</v>
       </c>
       <c r="H39" s="60">
-        <v>103.93</v>
+        <v>109.89940594059406</v>
       </c>
       <c r="I39" s="60">
-        <v>0.49730000000000002</v>
+        <v>0.62602760000000002</v>
       </c>
       <c r="J39" s="60">
-        <v>375.41</v>
+        <v>282.60610249999996</v>
       </c>
       <c r="K39" s="61">
-        <v>1.7400000000000001E-15</v>
+        <v>3.2560848751661369E-13</v>
       </c>
       <c r="L39" s="62">
-        <v>1.6351429256298836E-16</v>
+        <v>1.6453689389224409E-16</v>
       </c>
       <c r="M39" s="30">
         <v>40.637031233333332</v>
@@ -5403,7 +5546,7 @@
       <c r="Q39" s="23"/>
       <c r="R39" s="27"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="20">
         <v>2</v>
       </c>
@@ -5423,22 +5566,22 @@
         <v>11325</v>
       </c>
       <c r="G40" s="59">
-        <v>5.6899999999999999E-2</v>
+        <v>8.4503311258278146E-2</v>
       </c>
       <c r="H40" s="60">
-        <v>131.41999999999999</v>
+        <v>151.5119646799117</v>
       </c>
       <c r="I40" s="60">
-        <v>1.2569999999999999</v>
+        <v>1.6805964</v>
       </c>
       <c r="J40" s="60">
-        <v>2770.03</v>
+        <v>2115.6538992000001</v>
       </c>
       <c r="K40" s="61">
-        <v>1.3299999999999999E-13</v>
+        <v>1.5338465174447838E-13</v>
       </c>
       <c r="L40" s="62">
-        <v>1.9128432146246522E-16</v>
+        <v>1.9184618820497844E-16</v>
       </c>
       <c r="M40" s="30">
         <v>381.6920283</v>
@@ -5455,7 +5598,7 @@
       <c r="Q40" s="23"/>
       <c r="R40" s="27"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="12">
         <v>3</v>
       </c>
@@ -5478,19 +5621,19 @@
         <v>0</v>
       </c>
       <c r="H41" s="26">
-        <v>37.462499999999999</v>
+        <v>19.875</v>
       </c>
       <c r="I41" s="26">
-        <v>1.774865E-3</v>
+        <v>2.3421150000000001E-3</v>
       </c>
       <c r="J41" s="26">
-        <v>2.2146405000000001E-2</v>
+        <v>2.5156580000000001E-2</v>
       </c>
       <c r="K41" s="19">
-        <v>8.3722130256265905E-15</v>
+        <v>1.7590317955905083E-15</v>
       </c>
       <c r="L41" s="29">
-        <v>1.2852655003258614E-16</v>
+        <v>1.4359751717977171E-16</v>
       </c>
       <c r="M41" s="31">
         <v>1.9401849999999999E-3</v>
@@ -5511,7 +5654,7 @@
         <v>6.6044462663449849E-16</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="12">
         <v>3</v>
       </c>
@@ -5531,22 +5674,22 @@
         <v>10</v>
       </c>
       <c r="G42" s="25">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H42" s="26">
-        <v>41.105000000000004</v>
+        <v>18.920000000000002</v>
       </c>
       <c r="I42" s="26">
-        <v>1.8646749999999997E-3</v>
+        <v>1.5870300000000001E-3</v>
       </c>
       <c r="J42" s="26">
-        <v>5.2197960000000009E-2</v>
+        <v>4.0466015000000008E-2</v>
       </c>
       <c r="K42" s="19">
-        <v>9.3994857518821815E-16</v>
+        <v>2.2416634029586792E-15</v>
       </c>
       <c r="L42" s="29">
-        <v>1.0904855484302551E-16</v>
+        <v>1.2413147067564898E-16</v>
       </c>
       <c r="M42" s="31">
         <v>3.6057249999999997E-3</v>
@@ -5567,7 +5710,7 @@
         <v>1.3016753449785429E-15</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="12">
         <v>3</v>
       </c>
@@ -5590,19 +5733,19 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H43" s="26">
-        <v>41.012500000000003</v>
+        <v>20.669999999999998</v>
       </c>
       <c r="I43" s="26">
-        <v>2.781295E-3</v>
+        <v>2.6409900000000002E-3</v>
       </c>
       <c r="J43" s="26">
-        <v>7.2745569999999982E-2</v>
+        <v>6.4804409999999993E-2</v>
       </c>
       <c r="K43" s="19">
-        <v>9.2490731434348941E-16</v>
+        <v>3.0370768147202678E-15</v>
       </c>
       <c r="L43" s="29">
-        <v>1.0610631648774711E-16</v>
+        <v>1.1060085603168663E-16</v>
       </c>
       <c r="M43" s="31">
         <v>5.6873749999999997E-3</v>
@@ -5623,7 +5766,7 @@
         <v>1.6939215566782756E-15</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="12">
         <v>3</v>
       </c>
@@ -5643,22 +5786,22 @@
         <v>35</v>
       </c>
       <c r="G44" s="25">
-        <v>1.1428571428571429E-2</v>
+        <v>8.5714285714285719E-3</v>
       </c>
       <c r="H44" s="26">
-        <v>41.715714285714284</v>
+        <v>21.511428571428571</v>
       </c>
       <c r="I44" s="26">
-        <v>4.6255100000000011E-3</v>
+        <v>4.4745999999999996E-3</v>
       </c>
       <c r="J44" s="26">
-        <v>0.12181928500000001</v>
+        <v>8.5524635000000016E-2</v>
       </c>
       <c r="K44" s="19">
-        <v>1.3312620489181795E-15</v>
+        <v>2.910756363600462E-15</v>
       </c>
       <c r="L44" s="29">
-        <v>1.0353327901786183E-16</v>
+        <v>1.1024479720834339E-16</v>
       </c>
       <c r="M44" s="31">
         <v>1.0133079999999999E-2</v>
@@ -5679,7 +5822,7 @@
         <v>1.4442483163689786E-15</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="12">
         <v>3</v>
       </c>
@@ -5699,22 +5842,22 @@
         <v>56</v>
       </c>
       <c r="G45" s="25">
-        <v>1.9642857142857146E-2</v>
+        <v>1.0714285714285714E-2</v>
       </c>
       <c r="H45" s="26">
-        <v>43.482142857142854</v>
+        <v>23.303571428571423</v>
       </c>
       <c r="I45" s="26">
-        <v>6.4352549999999982E-3</v>
+        <v>6.31461E-3</v>
       </c>
       <c r="J45" s="26">
-        <v>0.19857331999999997</v>
+        <v>0.11641928500000001</v>
       </c>
       <c r="K45" s="19">
-        <v>1.5179211669340866E-15</v>
+        <v>3.6137746712829608E-14</v>
       </c>
       <c r="L45" s="29">
-        <v>1.0602036358505885E-16</v>
+        <v>1.0689983468947442E-16</v>
       </c>
       <c r="M45" s="31">
         <v>1.5546505000000002E-2</v>
@@ -5735,7 +5878,7 @@
         <v>3.7120339541155763E-15</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
         <v>3</v>
       </c>
@@ -5755,22 +5898,22 @@
         <v>84</v>
       </c>
       <c r="G46" s="25">
-        <v>2.0238095238095239E-2</v>
+        <v>1.1904761904761904E-2</v>
       </c>
       <c r="H46" s="26">
-        <v>44.220833333333339</v>
+        <v>25.141666666666662</v>
       </c>
       <c r="I46" s="26">
-        <v>9.8520149999999987E-3</v>
+        <v>9.9704849999999994E-3</v>
       </c>
       <c r="J46" s="26">
-        <v>0.28786992999999994</v>
+        <v>0.18086283000000003</v>
       </c>
       <c r="K46" s="19">
-        <v>1.9732332719897574E-15</v>
+        <v>1.2485429742509005E-14</v>
       </c>
       <c r="L46" s="29">
-        <v>1.0565574437908516E-16</v>
+        <v>1.0730826365935549E-16</v>
       </c>
       <c r="M46" s="31">
         <v>2.3653085000000001E-2</v>
@@ -5791,7 +5934,7 @@
         <v>2.5311975964215702E-15</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="12">
         <v>3</v>
       </c>
@@ -5811,22 +5954,22 @@
         <v>120</v>
       </c>
       <c r="G47" s="25">
-        <v>8.3333333333333332E-3</v>
+        <v>0.01</v>
       </c>
       <c r="H47" s="26">
-        <v>45.308749999999996</v>
+        <v>26.921249999999997</v>
       </c>
       <c r="I47" s="26">
-        <v>1.2987579999999999E-2</v>
+        <v>1.2709695000000002E-2</v>
       </c>
       <c r="J47" s="26">
-        <v>0.366772335</v>
+        <v>0.24312836999999998</v>
       </c>
       <c r="K47" s="19">
-        <v>5.0474477023079649E-15</v>
+        <v>2.2701282288638033E-14</v>
       </c>
       <c r="L47" s="29">
-        <v>1.0458135953006495E-16</v>
+        <v>1.0617746438035777E-16</v>
       </c>
       <c r="M47" s="31">
         <v>3.4414294999999998E-2</v>
@@ -5847,7 +5990,7 @@
         <v>4.3865309428092218E-15</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="12">
         <v>3</v>
       </c>
@@ -5867,22 +6010,22 @@
         <v>165</v>
       </c>
       <c r="G48" s="25">
-        <v>2.0606060606060607E-2</v>
+        <v>1.6969696969696968E-2</v>
       </c>
       <c r="H48" s="26">
-        <v>46.855454545454542</v>
+        <v>28.760909090909088</v>
       </c>
       <c r="I48" s="26">
-        <v>1.675488E-2</v>
+        <v>1.8585224999999997E-2</v>
       </c>
       <c r="J48" s="26">
-        <v>0.53416845000000013</v>
+        <v>0.35455610500000001</v>
       </c>
       <c r="K48" s="19">
-        <v>5.6942689226392804E-15</v>
+        <v>8.0505106468104198E-15</v>
       </c>
       <c r="L48" s="29">
-        <v>1.0625812742895307E-16</v>
+        <v>1.0840127854605948E-16</v>
       </c>
       <c r="M48" s="31">
         <v>5.074608500000001E-2</v>
@@ -5903,7 +6046,7 @@
         <v>1.7453365496978689E-14</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="12">
         <v>3</v>
       </c>
@@ -5923,22 +6066,22 @@
         <v>220</v>
       </c>
       <c r="G49" s="25">
-        <v>1.7272727272727273E-2</v>
+        <v>2.0454545454545454E-2</v>
       </c>
       <c r="H49" s="26">
-        <v>48.306363636363628</v>
+        <v>31.07090909090909</v>
       </c>
       <c r="I49" s="26">
-        <v>2.3017935E-2</v>
+        <v>2.3237874999999998E-2</v>
       </c>
       <c r="J49" s="26">
-        <v>0.72586963000000015</v>
+        <v>0.50099266499999984</v>
       </c>
       <c r="K49" s="19">
-        <v>4.4729781196235689E-15</v>
+        <v>4.3532669413489904E-15</v>
       </c>
       <c r="L49" s="29">
-        <v>1.055488568015661E-16</v>
+        <v>1.0803222490211642E-16</v>
       </c>
       <c r="M49" s="31">
         <v>7.2403085000000006E-2</v>
@@ -5959,7 +6102,7 @@
         <v>6.2485623154199843E-15</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="12">
         <v>3</v>
       </c>
@@ -5979,22 +6122,22 @@
         <v>286</v>
       </c>
       <c r="G50" s="25">
-        <v>1.8181818181818181E-2</v>
+        <v>1.9580419580419579E-2</v>
       </c>
       <c r="H50" s="26">
-        <v>50.01328671328671</v>
+        <v>32.466433566433565</v>
       </c>
       <c r="I50" s="26">
-        <v>3.1125259999999998E-2</v>
+        <v>3.0076479999999999E-2</v>
       </c>
       <c r="J50" s="26">
-        <v>1.0885678799999998</v>
+        <v>0.64965617999999992</v>
       </c>
       <c r="K50" s="19">
-        <v>7.3148907073688365E-14</v>
+        <v>5.5318165304084287E-15</v>
       </c>
       <c r="L50" s="29">
-        <v>1.0726862492715321E-16</v>
+        <v>1.0839363440172011E-16</v>
       </c>
       <c r="M50" s="31">
         <v>0.10487514000000001</v>
@@ -6015,7 +6158,7 @@
         <v>1.5510442256234427E-14</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="12">
         <v>3</v>
       </c>
@@ -6035,22 +6178,22 @@
         <v>364</v>
       </c>
       <c r="G51" s="25">
-        <v>1.7582417582417582E-2</v>
+        <v>3.2967032967032968E-2</v>
       </c>
       <c r="H51" s="26">
-        <v>50.065384615384609</v>
+        <v>36.325274725274724</v>
       </c>
       <c r="I51" s="26">
-        <v>4.1544440000000002E-2</v>
+        <v>3.9777820000000005E-2</v>
       </c>
       <c r="J51" s="26">
-        <v>1.31935706</v>
+        <v>0.85651955999999996</v>
       </c>
       <c r="K51" s="19">
-        <v>7.5613566674009782E-14</v>
+        <v>4.9044620377337687E-15</v>
       </c>
       <c r="L51" s="29">
-        <v>1.0531248382938062E-16</v>
+        <v>1.0868652454028221E-16</v>
       </c>
       <c r="M51" s="31">
         <v>0.14052732000000001</v>
@@ -6071,7 +6214,7 @@
         <v>1.4730134171795829E-14</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="12">
         <v>3</v>
       </c>
@@ -6094,19 +6237,19 @@
         <v>2.7252747252747254E-2</v>
       </c>
       <c r="H52" s="26">
-        <v>52.058901098901103</v>
+        <v>37.519999999999996</v>
       </c>
       <c r="I52" s="26">
-        <v>5.0244259999999999E-2</v>
+        <v>5.0065780000000004E-2</v>
       </c>
       <c r="J52" s="26">
-        <v>1.9567906799999999</v>
+        <v>1.1217998200000001</v>
       </c>
       <c r="K52" s="19">
-        <v>1.9813440086444814E-15</v>
+        <v>1.8722212361204548E-13</v>
       </c>
       <c r="L52" s="29">
-        <v>1.0831607398495275E-16</v>
+        <v>1.0971972341957951E-16</v>
       </c>
       <c r="M52" s="31">
         <v>0.20229919999999998</v>
@@ -6127,7 +6270,7 @@
         <v>1.942575056088023E-14</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="12">
         <v>3</v>
       </c>
@@ -6147,22 +6290,22 @@
         <v>560</v>
       </c>
       <c r="G53" s="25">
-        <v>1.7857142857142856E-2</v>
+        <v>3.0714285714285711E-2</v>
       </c>
       <c r="H53" s="26">
-        <v>52.746428571428567</v>
+        <v>39.363571428571426</v>
       </c>
       <c r="I53" s="26">
-        <v>6.2632959999999988E-2</v>
+        <v>6.2795600000000007E-2</v>
       </c>
       <c r="J53" s="26">
-        <v>2.3736570399999999</v>
+        <v>1.4490373999999999</v>
       </c>
       <c r="K53" s="19">
-        <v>2.0767297247357917E-14</v>
+        <v>2.3261163447349027E-14</v>
       </c>
       <c r="L53" s="29">
-        <v>1.0870693762828835E-16</v>
+        <v>1.106842856133458E-16</v>
       </c>
       <c r="M53" s="31">
         <v>0.30381140000000001</v>
@@ -6183,7 +6326,7 @@
         <v>7.0326428790844721E-14</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="12">
         <v>3</v>
       </c>
@@ -6203,22 +6346,22 @@
         <v>680</v>
       </c>
       <c r="G54" s="25">
-        <v>2.2058823529411766E-2</v>
+        <v>3.8235294117647062E-2</v>
       </c>
       <c r="H54" s="26">
-        <v>53.809705882352944</v>
+        <v>41.503529411764703</v>
       </c>
       <c r="I54" s="26">
-        <v>7.4149659999999992E-2</v>
+        <v>7.3424239999999988E-2</v>
       </c>
       <c r="J54" s="26">
-        <v>3.0902487199999999</v>
+        <v>1.8809741200000001</v>
       </c>
       <c r="K54" s="19">
-        <v>2.0280978170041934E-15</v>
+        <v>4.5958117797863951E-15</v>
       </c>
       <c r="L54" s="29">
-        <v>1.1028803237851775E-16</v>
+        <v>1.115072807516643E-16</v>
       </c>
       <c r="M54" s="31">
         <v>0.39482010000000001</v>
@@ -6239,7 +6382,7 @@
         <v>5.9750780002089569E-14</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="12">
         <v>3</v>
       </c>
@@ -6259,22 +6402,22 @@
         <v>816</v>
       </c>
       <c r="G55" s="25">
-        <v>1.8137254901960786E-2</v>
+        <v>4.4117647058823532E-2</v>
       </c>
       <c r="H55" s="26">
-        <v>55.506862745098047</v>
+        <v>44.441421568627447</v>
       </c>
       <c r="I55" s="26">
-        <v>9.0795719999999996E-2</v>
+        <v>9.0207780000000001E-2</v>
       </c>
       <c r="J55" s="26">
-        <v>4.3281014800000008</v>
+        <v>2.6914631600000001</v>
       </c>
       <c r="K55" s="19">
-        <v>2.106832340189237E-15</v>
+        <v>9.073751827443964E-14</v>
       </c>
       <c r="L55" s="29">
-        <v>1.1091287872753665E-16</v>
+        <v>1.1271542848625927E-16</v>
       </c>
       <c r="M55" s="31">
         <v>0.54198486000000001</v>
@@ -6295,7 +6438,7 @@
         <v>7.8842543563651667E-14</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="12">
         <v>3</v>
       </c>
@@ -6315,22 +6458,22 @@
         <v>969</v>
       </c>
       <c r="G56" s="25">
-        <v>1.6924664602683177E-2</v>
+        <v>5.1805985552115588E-2</v>
       </c>
       <c r="H56" s="26">
-        <v>54.750257997936025</v>
+        <v>46.909391124870993</v>
       </c>
       <c r="I56" s="26">
-        <v>0.1073916</v>
+        <v>0.10606660000000001</v>
       </c>
       <c r="J56" s="26">
-        <v>4.7503033599999993</v>
+        <v>3.3767622600000005</v>
       </c>
       <c r="K56" s="19">
-        <v>9.5686409563961372E-14</v>
+        <v>3.7948812987184378E-14</v>
       </c>
       <c r="L56" s="29">
-        <v>1.1162098495689669E-16</v>
+        <v>1.1314365046236184E-16</v>
       </c>
       <c r="M56" s="31">
         <v>0.70671596000000003</v>
@@ -6351,7 +6494,7 @@
         <v>4.9900728133169959E-13</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="12">
         <v>3</v>
       </c>
@@ -6371,22 +6514,22 @@
         <v>1140</v>
       </c>
       <c r="G57" s="25">
-        <v>2.2456140350877195E-2</v>
+        <v>5.3508771929824561E-2</v>
       </c>
       <c r="H57" s="26">
-        <v>57.009649122807012</v>
+        <v>50.010877192982456</v>
       </c>
       <c r="I57" s="26">
-        <v>0.12106208</v>
+        <v>0.13572754000000001</v>
       </c>
       <c r="J57" s="26">
-        <v>6.2207562800000007</v>
+        <v>4.3980127800000002</v>
       </c>
       <c r="K57" s="19">
-        <v>1.5457728550117078E-14</v>
+        <v>3.1189355922691095E-14</v>
       </c>
       <c r="L57" s="29">
-        <v>1.1255024824495587E-16</v>
+        <v>1.1426437872097752E-16</v>
       </c>
       <c r="M57" s="31">
         <v>0.92488938000000009</v>
@@ -6407,7 +6550,7 @@
         <v>6.4074278166628339E-12</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="12">
         <v>3</v>
       </c>
@@ -6427,22 +6570,22 @@
         <v>1330</v>
       </c>
       <c r="G58" s="25">
-        <v>2.3007518796992484E-2</v>
+        <v>5.0225563909774437E-2</v>
       </c>
       <c r="H58" s="26">
-        <v>58.468721804511276</v>
+        <v>50.74977443609022</v>
       </c>
       <c r="I58" s="26">
-        <v>0.14625664000000002</v>
+        <v>0.14674185999999997</v>
       </c>
       <c r="J58" s="26">
-        <v>7.5400198200000004</v>
+        <v>5.2699050600000001</v>
       </c>
       <c r="K58" s="19">
-        <v>4.4479721344561478E-14</v>
+        <v>9.8729791457307506E-14</v>
       </c>
       <c r="L58" s="29">
-        <v>1.121368691710749E-16</v>
+        <v>1.1408040038943511E-16</v>
       </c>
       <c r="M58" s="31">
         <v>1.2547853400000002</v>
@@ -6463,7 +6606,7 @@
         <v>2.3707600027125359E-12</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
         <v>3</v>
       </c>
@@ -6483,22 +6626,22 @@
         <v>1540</v>
       </c>
       <c r="G59" s="57">
-        <v>2.181818181818182E-2</v>
+        <v>5.9740259740259739E-2</v>
       </c>
       <c r="H59" s="58">
-        <v>58.3</v>
+        <v>53.8774025974026</v>
       </c>
       <c r="I59" s="58">
-        <v>0.17575637999999999</v>
+        <v>0.17292921999999999</v>
       </c>
       <c r="J59" s="58">
-        <v>9.1372198600000001</v>
+        <v>6.5965324399999998</v>
       </c>
       <c r="K59" s="55">
-        <v>3.7648467009044892E-15</v>
+        <v>2.1793281835964784E-13</v>
       </c>
       <c r="L59" s="56">
-        <v>1.1342504186850679E-16</v>
+        <v>1.1468885479212613E-16</v>
       </c>
       <c r="M59" s="31">
         <v>1.6707743799999999</v>
@@ -6519,7 +6662,7 @@
         <v>4.4571130327287062E-12</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="12">
         <v>3</v>
       </c>
@@ -6539,29 +6682,29 @@
         <v>1771</v>
       </c>
       <c r="G60" s="57">
-        <v>2.1118012422360246E-2</v>
+        <v>6.0606060606060601E-2</v>
       </c>
       <c r="H60" s="58">
-        <v>58.632523997741387</v>
+        <v>56.038584603802001</v>
       </c>
       <c r="I60" s="58">
-        <v>0.20392157999999999</v>
+        <v>0.20777886666666667</v>
       </c>
       <c r="J60" s="58">
-        <v>11.423609819999999</v>
+        <v>8.1195292333333331</v>
       </c>
       <c r="K60" s="55">
-        <v>1.8124732952343464E-14</v>
+        <v>1.3139619585956635E-13</v>
       </c>
       <c r="L60" s="56">
-        <v>1.1540886731859975E-16</v>
+        <v>1.171858783500853E-16</v>
       </c>
       <c r="M60" s="31"/>
       <c r="O60" s="29"/>
       <c r="P60" s="31"/>
       <c r="R60" s="29"/>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" s="12">
         <v>3</v>
       </c>
@@ -6581,29 +6724,29 @@
         <v>2024</v>
       </c>
       <c r="G61" s="57">
-        <v>1.9762845849802372E-2</v>
+        <v>6.3899868247694336E-2</v>
       </c>
       <c r="H61" s="58">
-        <v>59.528952569169959</v>
+        <v>57.802371541501977</v>
       </c>
       <c r="I61" s="58">
-        <v>0.23648253999999999</v>
+        <v>0.22991966666666666</v>
       </c>
       <c r="J61" s="58">
-        <v>13.83586188</v>
+        <v>9.989284266666667</v>
       </c>
       <c r="K61" s="55">
-        <v>2.1114239291851844E-15</v>
+        <v>1.1130333479064356E-13</v>
       </c>
       <c r="L61" s="56">
-        <v>1.1547486566506067E-16</v>
+        <v>1.1649493666303677E-16</v>
       </c>
       <c r="M61" s="31"/>
       <c r="O61" s="29"/>
       <c r="P61" s="31"/>
       <c r="R61" s="29"/>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" s="12">
         <v>3</v>
       </c>
@@ -6623,29 +6766,29 @@
         <v>2300</v>
       </c>
       <c r="G62" s="57">
-        <v>2.2434782608695653E-2</v>
+        <v>6.7391304347826086E-2</v>
       </c>
       <c r="H62" s="58">
-        <v>60.696434782608698</v>
+        <v>60.052898550724642</v>
       </c>
       <c r="I62" s="58">
-        <v>0.27565203999999993</v>
+        <v>0.27988303333333336</v>
       </c>
       <c r="J62" s="58">
-        <v>16.86771624</v>
+        <v>12.581238600000001</v>
       </c>
       <c r="K62" s="55">
-        <v>1.1651484474962234E-14</v>
+        <v>1.4281253678169888E-13</v>
       </c>
       <c r="L62" s="56">
-        <v>1.1745016588532044E-16</v>
+        <v>1.1932747750634078E-16</v>
       </c>
       <c r="M62" s="31"/>
       <c r="O62" s="29"/>
       <c r="P62" s="31"/>
       <c r="R62" s="29"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" s="12">
         <v>3</v>
       </c>
@@ -6665,29 +6808,29 @@
         <v>2600</v>
       </c>
       <c r="G63" s="57">
-        <v>2.5923076923076924E-2</v>
+        <v>7.0512820512820512E-2</v>
       </c>
       <c r="H63" s="58">
-        <v>62.932000000000002</v>
+        <v>61.918717948717948</v>
       </c>
       <c r="I63" s="58">
-        <v>0.32044097999999999</v>
+        <v>0.32866136666666668</v>
       </c>
       <c r="J63" s="58">
-        <v>20.861996319999999</v>
+        <v>14.702419566666668</v>
       </c>
       <c r="K63" s="55">
-        <v>2.3548337235709475E-15</v>
+        <v>2.0012565009545321E-14</v>
       </c>
       <c r="L63" s="56">
-        <v>1.1606479035226939E-16</v>
+        <v>1.1695193361084058E-16</v>
       </c>
       <c r="M63" s="31"/>
       <c r="O63" s="29"/>
       <c r="P63" s="31"/>
       <c r="R63" s="29"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" s="12">
         <v>3</v>
       </c>
@@ -6707,22 +6850,22 @@
         <v>2925</v>
       </c>
       <c r="G64" s="57">
-        <v>2.858119658119658E-2</v>
+        <v>7.4529914529914532E-2</v>
       </c>
       <c r="H64" s="58">
-        <v>62.602256410256416</v>
+        <v>65.887863247863251</v>
       </c>
       <c r="I64" s="58">
-        <v>0.35743199999999997</v>
+        <v>0.35918383333333331</v>
       </c>
       <c r="J64" s="58">
-        <v>23.86704026</v>
+        <v>18.113736433333333</v>
       </c>
       <c r="K64" s="55">
-        <v>3.9934199917884667E-14</v>
+        <v>1.8137255770682601E-13</v>
       </c>
       <c r="L64" s="56">
-        <v>1.1984019893522346E-16</v>
+        <v>1.2119584638053238E-16</v>
       </c>
       <c r="M64" s="31">
         <v>8.908031059999999</v>
@@ -6742,8 +6885,22 @@
       <c r="R64" s="29">
         <v>3.4739232563227599E-9</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S64" s="70">
+        <v>109.9</v>
+      </c>
+      <c r="T64" s="70">
+        <v>0.43365900000000002</v>
+      </c>
+      <c r="U64" s="67">
+        <f>S64/J64</f>
+        <v>6.0672186770786496</v>
+      </c>
+      <c r="V64" s="67">
+        <f>(S64-T64)/(J64-I64)</f>
+        <v>6.1655364382428877</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" s="12">
         <v>3</v>
       </c>
@@ -6763,29 +6920,29 @@
         <v>3276</v>
       </c>
       <c r="G65" s="57">
-        <v>2.8205128205128206E-2</v>
+        <v>7.1225071225071226E-2</v>
       </c>
       <c r="H65" s="58">
-        <v>63.818986568986567</v>
+        <v>66.481990231990224</v>
       </c>
       <c r="I65" s="58">
-        <v>0.41221880000000005</v>
+        <v>0.42810476666666669</v>
       </c>
       <c r="J65" s="58">
-        <v>28.29822266</v>
+        <v>21.148166566666671</v>
       </c>
       <c r="K65" s="55">
-        <v>2.1338979960717368E-15</v>
+        <v>1.7998114913827903E-13</v>
       </c>
       <c r="L65" s="56">
-        <v>1.1765866824795947E-16</v>
+        <v>1.1940977734724117E-16</v>
       </c>
       <c r="M65" s="31"/>
       <c r="O65" s="29"/>
       <c r="P65" s="31"/>
       <c r="R65" s="29"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" s="12">
         <v>3</v>
       </c>
@@ -6805,29 +6962,29 @@
         <v>3654</v>
       </c>
       <c r="G66" s="57">
-        <v>3.2129173508483856E-2</v>
+        <v>7.7175697865353041E-2</v>
       </c>
       <c r="H66" s="58">
-        <v>65.407389162561572</v>
+        <v>68.451468710089401</v>
       </c>
       <c r="I66" s="58">
-        <v>0.46456357999999998</v>
+        <v>0.46049063333333334</v>
       </c>
       <c r="J66" s="58">
-        <v>33.505723119999999</v>
+        <v>24.842484366666667</v>
       </c>
       <c r="K66" s="55">
-        <v>1.1350056282946783E-13</v>
+        <v>2.6113332015293676E-13</v>
       </c>
       <c r="L66" s="56">
-        <v>1.2013975308780423E-16</v>
+        <v>1.1993259269597337E-16</v>
       </c>
       <c r="M66" s="31"/>
       <c r="O66" s="29"/>
       <c r="P66" s="31"/>
       <c r="R66" s="29"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" s="12">
         <v>3</v>
       </c>
@@ -6847,29 +7004,29 @@
         <v>4060</v>
       </c>
       <c r="G67" s="57">
-        <v>3.413793103448276E-2</v>
+        <v>7.4876847290640397E-2</v>
       </c>
       <c r="H67" s="58">
-        <v>66.39004926108376</v>
+        <v>70.274548440065686</v>
       </c>
       <c r="I67" s="58">
-        <v>0.52866955999999998</v>
+        <v>0.55710026666666668</v>
       </c>
       <c r="J67" s="58">
-        <v>39.278509620000001</v>
+        <v>28.946058966666669</v>
       </c>
       <c r="K67" s="55">
-        <v>1.695344892246094E-13</v>
+        <v>3.1867505171696011E-13</v>
       </c>
       <c r="L67" s="56">
-        <v>1.1985467140980435E-16</v>
+        <v>1.2128685257833857E-16</v>
       </c>
       <c r="M67" s="31"/>
       <c r="O67" s="29"/>
       <c r="P67" s="31"/>
       <c r="R67" s="29"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
         <v>3</v>
       </c>
@@ -6889,29 +7046,29 @@
         <v>4495</v>
       </c>
       <c r="G68" s="57">
-        <v>3.6974416017797551E-2</v>
+        <v>8.4093437152391551E-2</v>
       </c>
       <c r="H68" s="58">
-        <v>67.936507230255842</v>
+        <v>73.635150166852057</v>
       </c>
       <c r="I68" s="58">
-        <v>0.59688160000000001</v>
+        <v>0.71057219999999999</v>
       </c>
       <c r="J68" s="58">
-        <v>47.437452319999998</v>
+        <v>35.305066600000004</v>
       </c>
       <c r="K68" s="55">
-        <v>1.0858471070382208E-13</v>
+        <v>3.198353048055673E-13</v>
       </c>
       <c r="L68" s="56">
-        <v>1.2013840692907677E-16</v>
+        <v>1.2161303731200556E-16</v>
       </c>
       <c r="M68" s="31"/>
       <c r="O68" s="29"/>
       <c r="P68" s="31"/>
       <c r="R68" s="29"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" s="12">
         <v>3</v>
       </c>
@@ -6931,22 +7088,22 @@
         <v>4960</v>
       </c>
       <c r="G69" s="57">
-        <v>3.850806451612903E-2</v>
+        <v>8.1451612903225806E-2</v>
       </c>
       <c r="H69" s="58">
-        <v>68.694879032258058</v>
+        <v>75.680846774193554</v>
       </c>
       <c r="I69" s="58">
-        <v>0.6989223200000001</v>
+        <v>0.89683080000000004</v>
       </c>
       <c r="J69" s="58">
-        <v>54.376531759999999</v>
+        <v>42.129151199999995</v>
       </c>
       <c r="K69" s="55">
-        <v>1.3354832437089293E-13</v>
+        <v>3.5962940669649715E-14</v>
       </c>
       <c r="L69" s="56">
-        <v>1.2151285357041188E-16</v>
+        <v>1.2122310917559599E-16</v>
       </c>
       <c r="M69" s="31">
         <v>38.040107039999995</v>
@@ -6967,7 +7124,7 @@
         <v>1.8001816932431437E-9</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" s="12">
         <v>3</v>
       </c>
@@ -6987,22 +7144,22 @@
         <v>7770</v>
       </c>
       <c r="G70" s="57">
-        <v>5.2600000000000001E-2</v>
+        <v>9.2406692406692401E-2</v>
       </c>
       <c r="H70" s="58">
-        <v>74.945999999999998</v>
+        <v>86.462419562419569</v>
       </c>
       <c r="I70" s="58">
-        <v>1.1020000000000001</v>
+        <v>1.4917809</v>
       </c>
       <c r="J70" s="58">
-        <v>113.56</v>
+        <v>95.136749099999989</v>
       </c>
       <c r="K70" s="55">
-        <v>1.1E-14</v>
+        <v>4.4357857712054773E-13</v>
       </c>
       <c r="L70" s="56">
-        <v>1.2500000000000001E-16</v>
+        <v>1.2749142776101935E-16</v>
       </c>
       <c r="M70" s="31">
         <v>139.30000000000001</v>
@@ -7016,7 +7173,7 @@
       <c r="P70" s="31"/>
       <c r="R70" s="29"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
         <v>3</v>
       </c>
@@ -7036,22 +7193,22 @@
         <v>11480</v>
       </c>
       <c r="G71" s="25">
-        <v>5.4616724738675959E-2</v>
+        <v>0.10261324041811846</v>
       </c>
       <c r="H71" s="26">
-        <v>82.133623693379789</v>
+        <v>97.029355400696858</v>
       </c>
       <c r="I71" s="26">
-        <v>1.5539052</v>
+        <v>2.6192115</v>
       </c>
       <c r="J71" s="26">
-        <v>192.76115590000001</v>
+        <v>175.14812790000002</v>
       </c>
       <c r="K71" s="19">
-        <v>2.152138320993483E-15</v>
+        <v>3.236040810148015E-13</v>
       </c>
       <c r="L71" s="29">
-        <v>1.2981727364576096E-16</v>
+        <v>1.3130444722608819E-16</v>
       </c>
       <c r="M71" s="31">
         <v>370.39367979999997</v>
@@ -7066,8 +7223,22 @@
         <v>0</v>
       </c>
       <c r="R71" s="29"/>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S71" s="69">
+        <v>1119.4000000000001</v>
+      </c>
+      <c r="T71" s="69">
+        <v>2.3519000000000001</v>
+      </c>
+      <c r="U71" s="67">
+        <f>S71/J71</f>
+        <v>6.3911616608264072</v>
+      </c>
+      <c r="V71" s="67">
+        <f>(S71-T71)/(J71-I71)</f>
+        <v>6.4745558211829124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" s="12">
         <v>3</v>
       </c>
@@ -7087,22 +7258,22 @@
         <v>16215</v>
       </c>
       <c r="G72" s="53">
-        <v>8.8059999999999999E-2</v>
+        <v>0.11575701510946654</v>
       </c>
       <c r="H72" s="54">
-        <v>91.105000000000004</v>
+        <v>109.28874498920753</v>
       </c>
       <c r="I72" s="54">
-        <v>3.1669999999999998</v>
+        <v>4.2480339999999996</v>
       </c>
       <c r="J72" s="54">
-        <v>396.36</v>
+        <v>332.94932940000001</v>
       </c>
       <c r="K72" s="55">
-        <v>1.8200000000000001E-13</v>
+        <v>3.4703951790655293E-13</v>
       </c>
       <c r="L72" s="56">
-        <v>1.3269999999999999E-16</v>
+        <v>1.3492237304629769E-16</v>
       </c>
       <c r="M72" s="31">
         <v>1086.0201896999999</v>
@@ -7118,7 +7289,7 @@
       </c>
       <c r="R72" s="29"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" s="12">
         <v>3</v>
       </c>
@@ -7138,29 +7309,29 @@
         <v>22100</v>
       </c>
       <c r="G73" s="53">
-        <v>0.10539999999999999</v>
+        <v>0.12470588235294118</v>
       </c>
       <c r="H73" s="54">
-        <v>98.218000000000004</v>
+        <v>120.94615384615385</v>
       </c>
       <c r="I73" s="54">
-        <v>4.8780000000000001</v>
+        <v>6.503323</v>
       </c>
       <c r="J73" s="54">
-        <v>708.46799999999996</v>
+        <v>594.58825760000002</v>
       </c>
       <c r="K73" s="55">
-        <v>2.8400000000000001E-14</v>
+        <v>4.4174361193271037E-13</v>
       </c>
       <c r="L73" s="56">
-        <v>1.347229054177294E-16</v>
+        <v>1.3602582199598565E-16</v>
       </c>
       <c r="M73" s="31"/>
       <c r="O73" s="29"/>
       <c r="P73" s="31"/>
       <c r="R73" s="29"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" s="20">
         <v>4</v>
       </c>
@@ -7183,19 +7354,19 @@
         <v>0</v>
       </c>
       <c r="H74" s="22">
-        <v>40.019999999999996</v>
+        <v>20.330000000000002</v>
       </c>
       <c r="I74" s="22">
-        <v>2.0652999999999999E-3</v>
+        <v>9.137855000000002E-3</v>
       </c>
       <c r="J74" s="22">
-        <v>2.6754E-2</v>
+        <v>3.4954354999999993E-2</v>
       </c>
       <c r="K74" s="23">
-        <v>1.0690144010666058E-15</v>
+        <v>1.0983004986093658E-15</v>
       </c>
       <c r="L74" s="27">
-        <v>1.6087454082354521E-16</v>
+        <v>1.3257961225358292E-16</v>
       </c>
       <c r="M74" s="30">
         <v>5.875E-3</v>
@@ -7216,7 +7387,7 @@
         <v>1.0512096698219458E-15</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" s="20">
         <v>4</v>
       </c>
@@ -7236,22 +7407,22 @@
         <v>15</v>
       </c>
       <c r="G75" s="21">
-        <v>0</v>
+        <v>6.6666666666666671E-3</v>
       </c>
       <c r="H75" s="22">
-        <v>40.900000000000006</v>
+        <v>21.486666666666668</v>
       </c>
       <c r="I75" s="22">
-        <v>5.8943300000000014E-3</v>
+        <v>5.5112450000000006E-3</v>
       </c>
       <c r="J75" s="22">
-        <v>5.8947825000000009E-2</v>
+        <v>6.0674574999999994E-2</v>
       </c>
       <c r="K75" s="23">
-        <v>1.1117240167145039E-15</v>
+        <v>4.480195995153041E-15</v>
       </c>
       <c r="L75" s="27">
-        <v>1.1392542878554944E-16</v>
+        <v>1.2762604879758112E-16</v>
       </c>
       <c r="M75" s="30">
         <v>1.560634E-2</v>
@@ -7272,7 +7443,7 @@
         <v>1.4339104354569855E-15</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" s="20">
         <v>4</v>
       </c>
@@ -7292,22 +7463,22 @@
         <v>35</v>
       </c>
       <c r="G76" s="21">
-        <v>1.4285714285714285E-2</v>
+        <v>5.7142857142857143E-3</v>
       </c>
       <c r="H76" s="22">
-        <v>41.72571428571429</v>
+        <v>21.895714285714284</v>
       </c>
       <c r="I76" s="22">
-        <v>1.1611869999999998E-2</v>
+        <v>1.0473195000000001E-2</v>
       </c>
       <c r="J76" s="22">
-        <v>0.12679227000000001</v>
+        <v>9.542328500000001E-2</v>
       </c>
       <c r="K76" s="23">
-        <v>1.1570319595604635E-14</v>
+        <v>7.5578889631988401E-15</v>
       </c>
       <c r="L76" s="27">
-        <v>1.1449924186409742E-16</v>
+        <v>1.1502531428663804E-16</v>
       </c>
       <c r="M76" s="30">
         <v>3.6510745000000004E-2</v>
@@ -7328,7 +7499,7 @@
         <v>2.579752468698647E-15</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" s="20">
         <v>4</v>
       </c>
@@ -7348,22 +7519,22 @@
         <v>70</v>
       </c>
       <c r="G77" s="21">
-        <v>2.1428571428571429E-2</v>
+        <v>1.2857142857142857E-2</v>
       </c>
       <c r="H77" s="22">
-        <v>43.276428571428568</v>
+        <v>23.298571428571435</v>
       </c>
       <c r="I77" s="22">
-        <v>1.9794359999999997E-2</v>
+        <v>1.8140739999999999E-2</v>
       </c>
       <c r="J77" s="22">
-        <v>0.25006141499999995</v>
+        <v>0.17940265999999999</v>
       </c>
       <c r="K77" s="23">
-        <v>1.8516607572879195E-15</v>
+        <v>4.041214319934914E-14</v>
       </c>
       <c r="L77" s="27">
-        <v>1.1478347075390335E-16</v>
+        <v>1.1801743404306337E-16</v>
       </c>
       <c r="M77" s="30">
         <v>7.2288394999999991E-2</v>
@@ -7384,7 +7555,7 @@
         <v>3.0929534425831649E-15</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="20">
         <v>4</v>
       </c>
@@ -7404,22 +7575,22 @@
         <v>126</v>
       </c>
       <c r="G78" s="21">
-        <v>1.6666666666666666E-2</v>
+        <v>1.3492063492063491E-2</v>
       </c>
       <c r="H78" s="22">
-        <v>44.130158730158726</v>
+        <v>24.808730158730157</v>
       </c>
       <c r="I78" s="22">
-        <v>3.7547160000000003E-2</v>
+        <v>3.2196504999999993E-2</v>
       </c>
       <c r="J78" s="22">
-        <v>0.43198910999999995</v>
+        <v>0.29394207500000002</v>
       </c>
       <c r="K78" s="23">
-        <v>3.2592395130234304E-14</v>
+        <v>8.5529906449556539E-14</v>
       </c>
       <c r="L78" s="27">
-        <v>1.1468614432485226E-16</v>
+        <v>1.163817486016718E-16</v>
       </c>
       <c r="M78" s="30">
         <v>0.13498407000000001</v>
@@ -7440,7 +7611,7 @@
         <v>5.8210515051116458E-15</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" s="20">
         <v>4</v>
       </c>
@@ -7460,22 +7631,22 @@
         <v>210</v>
       </c>
       <c r="G79" s="21">
-        <v>1.7142857142857144E-2</v>
+        <v>1.6190476190476189E-2</v>
       </c>
       <c r="H79" s="22">
-        <v>44.783333333333331</v>
+        <v>26.170714285714286</v>
       </c>
       <c r="I79" s="22">
-        <v>6.0879950000000002E-2</v>
+        <v>5.1908255E-2</v>
       </c>
       <c r="J79" s="22">
-        <v>0.72719087000000004</v>
+        <v>0.46586473500000009</v>
       </c>
       <c r="K79" s="23">
-        <v>2.2395722743180501E-15</v>
+        <v>6.0022900426234662E-14</v>
       </c>
       <c r="L79" s="27">
-        <v>1.1340080195979656E-16</v>
+        <v>1.1543568817180195E-16</v>
       </c>
       <c r="M79" s="30">
         <v>0.243723775</v>
@@ -7496,7 +7667,7 @@
         <v>7.7475147871904035E-15</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" s="20">
         <v>4</v>
       </c>
@@ -7516,22 +7687,22 @@
         <v>330</v>
       </c>
       <c r="G80" s="21">
-        <v>2.0303030303030302E-2</v>
+        <v>1.9090909090909089E-2</v>
       </c>
       <c r="H80" s="22">
-        <v>46.284696969696974</v>
+        <v>28.240151515151517</v>
       </c>
       <c r="I80" s="22">
-        <v>9.072996500000001E-2</v>
+        <v>7.9923529999999993E-2</v>
       </c>
       <c r="J80" s="22">
-        <v>1.1408193700000002</v>
+        <v>0.70006993500000014</v>
       </c>
       <c r="K80" s="23">
-        <v>2.7927354417051986E-14</v>
+        <v>9.8779004470342054E-15</v>
       </c>
       <c r="L80" s="27">
-        <v>1.1399929219741382E-16</v>
+        <v>1.1486076678321669E-16</v>
       </c>
       <c r="M80" s="30">
         <v>0.42528166999999995</v>
@@ -7552,7 +7723,7 @@
         <v>1.1158079985928919E-14</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" s="20">
         <v>4</v>
       </c>
@@ -7572,22 +7743,22 @@
         <v>495</v>
       </c>
       <c r="G81" s="21">
-        <v>2.8686868686868684E-2</v>
+        <v>3.5151515151515149E-2</v>
       </c>
       <c r="H81" s="22">
-        <v>48.097777777777779</v>
+        <v>31.677171717171724</v>
       </c>
       <c r="I81" s="22">
-        <v>0.12514518000000002</v>
+        <v>0.12756457999999998</v>
       </c>
       <c r="J81" s="22">
-        <v>1.6256549799999997</v>
+        <v>1.1385132600000001</v>
       </c>
       <c r="K81" s="23">
-        <v>2.5376966748084449E-15</v>
+        <v>1.4576451946246432E-14</v>
       </c>
       <c r="L81" s="27">
-        <v>1.1154266322974579E-16</v>
+        <v>1.131445946719595E-16</v>
       </c>
       <c r="M81" s="30">
         <v>0.63481323999999995</v>
@@ -7608,7 +7779,7 @@
         <v>7.842842029990741E-15</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" s="20">
         <v>4</v>
       </c>
@@ -7628,22 +7799,22 @@
         <v>715</v>
       </c>
       <c r="G82" s="21">
-        <v>2.097902097902098E-2</v>
+        <v>4.5594405594405599E-2</v>
       </c>
       <c r="H82" s="22">
-        <v>49.061818181818182</v>
+        <v>35.218741258741261</v>
       </c>
       <c r="I82" s="22">
-        <v>0.18500096000000002</v>
+        <v>0.17729632000000001</v>
       </c>
       <c r="J82" s="22">
-        <v>2.3917373</v>
+        <v>1.69885522</v>
       </c>
       <c r="K82" s="23">
-        <v>1.5562649893619303E-14</v>
+        <v>1.6317209500467239E-13</v>
       </c>
       <c r="L82" s="27">
-        <v>1.1292426874962972E-16</v>
+        <v>1.1483547889003847E-16</v>
       </c>
       <c r="M82" s="30">
         <v>1.0409039400000002</v>
@@ -7664,7 +7835,7 @@
         <v>1.7656021792978649E-13</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" s="20">
         <v>4</v>
       </c>
@@ -7684,22 +7855,22 @@
         <v>1001</v>
       </c>
       <c r="G83" s="21">
-        <v>2.7572427572427574E-2</v>
+        <v>3.6563436563436566E-2</v>
       </c>
       <c r="H83" s="22">
-        <v>50.934065934065927</v>
+        <v>36.208591408591403</v>
       </c>
       <c r="I83" s="22">
-        <v>0.26725438000000001</v>
+        <v>0.25459546</v>
       </c>
       <c r="J83" s="22">
-        <v>3.7372063799999999</v>
+        <v>2.3266192000000006</v>
       </c>
       <c r="K83" s="23">
-        <v>2.3372691347063264E-15</v>
+        <v>3.6303725330656767E-13</v>
       </c>
       <c r="L83" s="27">
-        <v>1.1205632848280079E-16</v>
+        <v>1.1395480974110111E-16</v>
       </c>
       <c r="M83" s="30">
         <v>1.6349814599999999</v>
@@ -7720,7 +7891,7 @@
         <v>3.3118663384917392E-14</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" s="20">
         <v>4</v>
       </c>
@@ -7740,22 +7911,22 @@
         <v>1365</v>
       </c>
       <c r="G84" s="21">
-        <v>2.8864468864468862E-2</v>
+        <v>4.5567765567765567E-2</v>
       </c>
       <c r="H84" s="22">
-        <v>51.22871794871795</v>
+        <v>38.271355311355315</v>
       </c>
       <c r="I84" s="22">
-        <v>0.35178973999999996</v>
+        <v>0.35783355999999999</v>
       </c>
       <c r="J84" s="22">
-        <v>5.4098433200000002</v>
+        <v>3.5770991199999997</v>
       </c>
       <c r="K84" s="23">
-        <v>2.4121449246535292E-15</v>
+        <v>1.8253168615212489E-13</v>
       </c>
       <c r="L84" s="27">
-        <v>1.1525408615845469E-16</v>
+        <v>1.167438615254113E-16</v>
       </c>
       <c r="M84" s="30">
         <v>2.9392954199999997</v>
@@ -7776,7 +7947,7 @@
         <v>5.4309566727962712E-14</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" s="20">
         <v>4</v>
       </c>
@@ -7796,22 +7967,22 @@
         <v>1820</v>
       </c>
       <c r="G85" s="21">
-        <v>2.736263736263736E-2</v>
+        <v>5.3186813186813182E-2</v>
       </c>
       <c r="H85" s="22">
-        <v>52.860769230769236</v>
+        <v>41.53164835164835</v>
       </c>
       <c r="I85" s="22">
-        <v>0.47380211999999994</v>
+        <v>0.49127464000000004</v>
       </c>
       <c r="J85" s="22">
-        <v>7.5230298800000002</v>
+        <v>5.3300209399999998</v>
       </c>
       <c r="K85" s="23">
-        <v>3.1427987823216139E-14</v>
+        <v>9.6905500987222835E-14</v>
       </c>
       <c r="L85" s="27">
-        <v>1.1495977109103944E-16</v>
+        <v>1.1614077384509436E-16</v>
       </c>
       <c r="M85" s="30">
         <v>4.7792429199999997</v>
@@ -7832,7 +8003,7 @@
         <v>2.1098061616563067E-13</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" s="20">
         <v>4</v>
       </c>
@@ -7852,22 +8023,22 @@
         <v>2380</v>
       </c>
       <c r="G86" s="21">
-        <v>3.3025210084033613E-2</v>
+        <v>4.5658263305322133E-2</v>
       </c>
       <c r="H86" s="22">
-        <v>54.088487394957973</v>
+        <v>43.447899159663869</v>
       </c>
       <c r="I86" s="22">
-        <v>0.62005795999999991</v>
+        <v>0.68477906666666666</v>
       </c>
       <c r="J86" s="22">
-        <v>10.44317684</v>
+        <v>7.400859333333333</v>
       </c>
       <c r="K86" s="23">
-        <v>8.5253053039311693E-14</v>
+        <v>4.9419892261991879E-13</v>
       </c>
       <c r="L86" s="27">
-        <v>1.1513669817816618E-16</v>
+        <v>1.164586238006375E-16</v>
       </c>
       <c r="M86" s="30">
         <v>8.3362589800000002</v>
@@ -7888,7 +8059,7 @@
         <v>6.35707785116052E-14</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" s="20">
         <v>4</v>
       </c>
@@ -7908,22 +8079,22 @@
         <v>3060</v>
       </c>
       <c r="G87" s="21">
-        <v>3.3137254901960789E-2</v>
+        <v>5.7298474945533771E-2</v>
       </c>
       <c r="H87" s="22">
-        <v>55.123660130718953</v>
+        <v>46.019063180827885</v>
       </c>
       <c r="I87" s="22">
-        <v>0.83278660000000004</v>
+        <v>0.88638263333333345</v>
       </c>
       <c r="J87" s="22">
-        <v>15.071869660000001</v>
+        <v>11.133719133333335</v>
       </c>
       <c r="K87" s="23">
-        <v>2.0589187701652911E-14</v>
+        <v>1.9317385277829409E-13</v>
       </c>
       <c r="L87" s="27">
-        <v>1.1605266464270717E-16</v>
+        <v>1.1827455273357717E-16</v>
       </c>
       <c r="M87" s="30">
         <v>14.44136638</v>
@@ -7943,8 +8114,22 @@
       <c r="R87" s="27">
         <v>4.5467606439694606E-13</v>
       </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S87" s="69">
+        <v>63.802</v>
+      </c>
+      <c r="T87" s="69">
+        <v>1.105</v>
+      </c>
+      <c r="U87" s="67">
+        <f>S87/J87</f>
+        <v>5.7305199849152526</v>
+      </c>
+      <c r="V87" s="67">
+        <f>(S87-T87)/(J87-I87)</f>
+        <v>6.1183703687294742</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" s="20">
         <v>4</v>
       </c>
@@ -7964,22 +8149,22 @@
         <v>3876</v>
       </c>
       <c r="G88" s="21">
-        <v>3.3126934984520122E-2</v>
+        <v>6.1833505331957341E-2</v>
       </c>
       <c r="H88" s="22">
-        <v>56.329411764705888</v>
+        <v>49.434554523563811</v>
       </c>
       <c r="I88" s="22">
-        <v>1.05540134</v>
+        <v>1.1506924333333333</v>
       </c>
       <c r="J88" s="22">
-        <v>20.578489879999999</v>
+        <v>15.777931366666666</v>
       </c>
       <c r="K88" s="23">
-        <v>1.157263597828843E-13</v>
+        <v>1.9189830423276945E-13</v>
       </c>
       <c r="L88" s="27">
-        <v>1.1689872761932068E-16</v>
+        <v>1.1808072234278666E-16</v>
       </c>
       <c r="M88" s="30">
         <v>25.02096762</v>
@@ -7996,7 +8181,7 @@
       <c r="Q88" s="23"/>
       <c r="R88" s="27"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" s="20">
         <v>4</v>
       </c>
@@ -8016,22 +8201,22 @@
         <v>4845</v>
       </c>
       <c r="G89" s="21">
-        <v>3.6463708290333678E-2</v>
+        <v>6.5290677674578593E-2</v>
       </c>
       <c r="H89" s="22">
-        <v>57.452975576195392</v>
+        <v>51.261988304093563</v>
       </c>
       <c r="I89" s="22">
-        <v>1.5319223</v>
+        <v>1.4620122666666664</v>
       </c>
       <c r="J89" s="22">
-        <v>29.898959999999999</v>
+        <v>20.979158766666668</v>
       </c>
       <c r="K89" s="23">
-        <v>7.7254564099145816E-14</v>
+        <v>3.2085760469667915E-13</v>
       </c>
       <c r="L89" s="27">
-        <v>1.1776574312420388E-16</v>
+        <v>1.1946152399984706E-16</v>
       </c>
       <c r="M89" s="30">
         <v>47.062229133333325</v>
@@ -8048,7 +8233,7 @@
       <c r="Q89" s="23"/>
       <c r="R89" s="27"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A90" s="20">
         <v>4</v>
       </c>
@@ -8068,22 +8253,22 @@
         <v>5985</v>
       </c>
       <c r="G90" s="21">
-        <v>3.5588972431077691E-2</v>
+        <v>6.6276803118908378E-2</v>
       </c>
       <c r="H90" s="22">
-        <v>58.78000556947925</v>
+        <v>54.764522417153991</v>
       </c>
       <c r="I90" s="22">
-        <v>1.8644255000000001</v>
+        <v>1.8767346</v>
       </c>
       <c r="J90" s="22">
-        <v>40.761109433333338</v>
+        <v>28.033140100000001</v>
       </c>
       <c r="K90" s="23">
-        <v>3.7943520296200498E-13</v>
+        <v>4.2929592680929307E-13</v>
       </c>
       <c r="L90" s="27">
-        <v>1.185149623689525E-16</v>
+        <v>1.2001547345980983E-16</v>
       </c>
       <c r="M90" s="30">
         <v>82.009343533333336</v>
@@ -8100,7 +8285,7 @@
       <c r="Q90" s="23"/>
       <c r="R90" s="27"/>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" s="20">
         <v>4</v>
       </c>
@@ -8120,22 +8305,22 @@
         <v>7315</v>
       </c>
       <c r="G91" s="21">
-        <v>4.0328092959671907E-2</v>
+        <v>7.4367737525632263E-2</v>
       </c>
       <c r="H91" s="22">
-        <v>60.714559125085444</v>
+        <v>56.366780587833219</v>
       </c>
       <c r="I91" s="22">
-        <v>2.5364664000000001</v>
+        <v>2.9357280000000001</v>
       </c>
       <c r="J91" s="22">
-        <v>53.679607900000001</v>
+        <v>36.964761099999997</v>
       </c>
       <c r="K91" s="23">
-        <v>1.0934099825046952E-13</v>
+        <v>3.5311073124841684E-13</v>
       </c>
       <c r="L91" s="27">
-        <v>1.1931042773440712E-16</v>
+        <v>1.210853488575235E-16</v>
       </c>
       <c r="M91" s="30">
         <v>143.72249239999999</v>
@@ -8152,7 +8337,7 @@
       <c r="Q91" s="23"/>
       <c r="R91" s="27"/>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" s="20">
         <v>4</v>
       </c>
@@ -8172,22 +8357,22 @@
         <v>8855</v>
       </c>
       <c r="G92" s="21">
-        <v>4.6188594014680971E-2</v>
+        <v>6.5386787125917556E-2</v>
       </c>
       <c r="H92" s="22">
-        <v>62.067532467532466</v>
+        <v>58.826086956521742</v>
       </c>
       <c r="I92" s="22">
-        <v>3.1253017999999999</v>
+        <v>3.8454337000000001</v>
       </c>
       <c r="J92" s="22">
-        <v>70.480605499999996</v>
+        <v>47.428557900000001</v>
       </c>
       <c r="K92" s="23">
-        <v>3.6888960994908602E-14</v>
+        <v>3.6238747631324489E-13</v>
       </c>
       <c r="L92" s="27">
-        <v>1.1808839098110602E-16</v>
+        <v>1.1945624082942715E-16</v>
       </c>
       <c r="M92" s="30">
         <v>284.22466589999999</v>
@@ -8204,7 +8389,7 @@
       <c r="Q92" s="23"/>
       <c r="R92" s="27"/>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A93" s="12">
         <v>5</v>
       </c>
@@ -8227,19 +8412,19 @@
         <v>0</v>
       </c>
       <c r="H93" s="26">
-        <v>41.06666666666667</v>
+        <v>21.024999999999999</v>
       </c>
       <c r="I93" s="26">
-        <v>4.3451350000000008E-3</v>
+        <v>4.0485599999999988E-3</v>
       </c>
       <c r="J93" s="26">
-        <v>3.852970499999999E-2</v>
+        <v>3.3204734999999999E-2</v>
       </c>
       <c r="K93" s="19">
-        <v>1.0111020330950408E-15</v>
+        <v>1.4726596319343203E-15</v>
       </c>
       <c r="L93" s="29">
-        <v>1.4134737104830064E-16</v>
+        <v>1.5883526653922439E-16</v>
       </c>
       <c r="M93" s="31">
         <v>3.6216889999999995E-2</v>
@@ -8260,7 +8445,7 @@
         <v>1.8508597092275008E-15</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A94" s="12">
         <v>5</v>
       </c>
@@ -8283,19 +8468,19 @@
         <v>4.7619047619047623E-3</v>
       </c>
       <c r="H94" s="26">
-        <v>41.021428571428579</v>
+        <v>22.540476190476191</v>
       </c>
       <c r="I94" s="26">
-        <v>1.2850474999999997E-2</v>
+        <v>9.2671399999999984E-3</v>
       </c>
       <c r="J94" s="26">
-        <v>9.8172665000000006E-2</v>
+        <v>7.6251975E-2</v>
       </c>
       <c r="K94" s="19">
-        <v>1.5016150040344402E-15</v>
+        <v>1.1343831338671864E-14</v>
       </c>
       <c r="L94" s="29">
-        <v>1.3168328400029662E-16</v>
+        <v>1.3481850005851606E-16</v>
       </c>
       <c r="M94" s="31">
         <v>0.12438753000000002</v>
@@ -8316,7 +8501,7 @@
         <v>1.641303113276523E-15</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" s="12">
         <v>5</v>
       </c>
@@ -8336,22 +8521,22 @@
         <v>56</v>
       </c>
       <c r="G95" s="25">
-        <v>1.7857142857142856E-2</v>
+        <v>8.9285714285714281E-3</v>
       </c>
       <c r="H95" s="26">
-        <v>43.362499999999997</v>
+        <v>22.9375</v>
       </c>
       <c r="I95" s="26">
-        <v>2.9452795000000004E-2</v>
+        <v>2.2691720000000005E-2</v>
       </c>
       <c r="J95" s="26">
-        <v>0.23720457499999997</v>
+        <v>0.14323133999999998</v>
       </c>
       <c r="K95" s="19">
-        <v>2.0578425953473661E-15</v>
+        <v>2.9316739767053971E-14</v>
       </c>
       <c r="L95" s="29">
-        <v>1.2264438691042977E-16</v>
+        <v>1.2753805978833556E-16</v>
       </c>
       <c r="M95" s="31">
         <v>0.31682692000000007</v>
@@ -8372,7 +8557,7 @@
         <v>4.5678968541089174E-15</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A96" s="12">
         <v>5</v>
       </c>
@@ -8392,22 +8577,22 @@
         <v>126</v>
       </c>
       <c r="G96" s="25">
-        <v>1.4285714285714285E-2</v>
+        <v>2.3809523809523807E-3</v>
       </c>
       <c r="H96" s="26">
-        <v>43.746825396825407</v>
+        <v>23.792857142857141</v>
       </c>
       <c r="I96" s="26">
-        <v>6.6734979999999985E-2</v>
+        <v>4.8373805000000006E-2</v>
       </c>
       <c r="J96" s="26">
-        <v>0.56560521499999994</v>
+        <v>0.26320189500000002</v>
       </c>
       <c r="K96" s="19">
-        <v>8.327493225826354E-15</v>
+        <v>1.6190019789062394E-14</v>
       </c>
       <c r="L96" s="29">
-        <v>1.2369988016671953E-16</v>
+        <v>1.255261327009809E-16</v>
       </c>
       <c r="M96" s="31">
         <v>0.79143405000000011</v>
@@ -8428,7 +8613,7 @@
         <v>5.2104212116125127E-15</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" s="12">
         <v>5</v>
       </c>
@@ -8448,22 +8633,22 @@
         <v>252</v>
       </c>
       <c r="G97" s="25">
-        <v>2.5396825396825397E-2</v>
+        <v>1.8452380952380953E-2</v>
       </c>
       <c r="H97" s="26">
-        <v>45.042658730158728</v>
+        <v>26.539087301587301</v>
       </c>
       <c r="I97" s="26">
-        <v>0.13532438999999999</v>
+        <v>9.2760460000000017E-2</v>
       </c>
       <c r="J97" s="26">
-        <v>0.99320628499999997</v>
+        <v>0.56998807499999993</v>
       </c>
       <c r="K97" s="19">
-        <v>2.6172940156042614E-14</v>
+        <v>7.7833531890587368E-14</v>
       </c>
       <c r="L97" s="29">
-        <v>1.2116469888421233E-16</v>
+        <v>1.2367373045101332E-16</v>
       </c>
       <c r="M97" s="31">
         <v>1.5915183100000001</v>
@@ -8484,7 +8669,7 @@
         <v>7.4488651787145559E-15</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A98" s="12">
         <v>5</v>
       </c>
@@ -8504,22 +8689,22 @@
         <v>462</v>
       </c>
       <c r="G98" s="25">
-        <v>2.1645021645021644E-2</v>
+        <v>1.1255411255411256E-2</v>
       </c>
       <c r="H98" s="26">
-        <v>45.003030303030307</v>
+        <v>26.957575757575757</v>
       </c>
       <c r="I98" s="26">
-        <v>0.22163472000000001</v>
+        <v>0.17871157999999998</v>
       </c>
       <c r="J98" s="26">
-        <v>1.50936874</v>
+        <v>0.97101222000000009</v>
       </c>
       <c r="K98" s="19">
-        <v>2.7711533514438997E-15</v>
+        <v>2.1684055356784678E-13</v>
       </c>
       <c r="L98" s="29">
-        <v>1.2132702133985043E-16</v>
+        <v>1.2435396102418885E-16</v>
       </c>
       <c r="M98" s="31">
         <v>2.8065348999999999</v>
@@ -8540,7 +8725,7 @@
         <v>1.1681932912735279E-14</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A99" s="12">
         <v>5</v>
       </c>
@@ -8560,22 +8745,22 @@
         <v>792</v>
       </c>
       <c r="G99" s="25">
-        <v>2.9545454545454545E-2</v>
+        <v>2.803030303030303E-2</v>
       </c>
       <c r="H99" s="26">
-        <v>47.18762626262626</v>
+        <v>29.622222222222224</v>
       </c>
       <c r="I99" s="26">
-        <v>0.40433444000000007</v>
+        <v>0.33457002000000002</v>
       </c>
       <c r="J99" s="26">
-        <v>2.7873993399999999</v>
+        <v>1.7259364399999999</v>
       </c>
       <c r="K99" s="19">
-        <v>2.7686345473108905E-15</v>
+        <v>1.686144447831692E-13</v>
       </c>
       <c r="L99" s="29">
-        <v>1.2098861890812174E-16</v>
+        <v>1.2341453415391171E-16</v>
       </c>
       <c r="M99" s="31">
         <v>5.9555392600000001</v>
@@ -8596,7 +8781,7 @@
         <v>1.7386600573385902E-14</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A100" s="12">
         <v>5</v>
       </c>
@@ -8616,22 +8801,22 @@
         <v>1287</v>
       </c>
       <c r="G100" s="25">
-        <v>3.9627039627039624E-2</v>
+        <v>3.822843822843823E-2</v>
       </c>
       <c r="H100" s="26">
-        <v>49.886557886557895</v>
+        <v>33.783216783216787</v>
       </c>
       <c r="I100" s="26">
-        <v>0.67022542000000007</v>
+        <v>0.5659322</v>
       </c>
       <c r="J100" s="26">
-        <v>5.1298590599999994</v>
+        <v>3.1348834800000001</v>
       </c>
       <c r="K100" s="19">
-        <v>4.2294484783412656E-14</v>
+        <v>6.2409832481825526E-14</v>
       </c>
       <c r="L100" s="29">
-        <v>1.2252333205730709E-16</v>
+        <v>1.2348076550384923E-16</v>
       </c>
       <c r="M100" s="31">
         <v>10.79656404</v>
@@ -8652,7 +8837,7 @@
         <v>2.0325013552458296E-14</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A101" s="12">
         <v>5</v>
       </c>
@@ -8672,22 +8857,22 @@
         <v>2002</v>
       </c>
       <c r="G101" s="25">
-        <v>3.3766233766233764E-2</v>
+        <v>4.4955044955044952E-2</v>
       </c>
       <c r="H101" s="26">
-        <v>49.959240759240757</v>
+        <v>36.016083916083915</v>
       </c>
       <c r="I101" s="26">
-        <v>1.09012354</v>
+        <v>0.96331532000000009</v>
       </c>
       <c r="J101" s="26">
-        <v>8.05378814</v>
+        <v>5.3174288199999999</v>
       </c>
       <c r="K101" s="19">
-        <v>1.6320985825224811E-14</v>
+        <v>2.0682766462553197E-13</v>
       </c>
       <c r="L101" s="29">
-        <v>1.1928792098704364E-16</v>
+        <v>1.2117968775034721E-16</v>
       </c>
       <c r="M101" s="31">
         <v>20.229128060000001</v>
@@ -8708,7 +8893,7 @@
         <v>4.0503504313146147E-14</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A102" s="12">
         <v>5</v>
       </c>
@@ -8728,22 +8913,22 @@
         <v>3003</v>
       </c>
       <c r="G102" s="25">
-        <v>4.4022644022644018E-2</v>
+        <v>5.3058053058053063E-2</v>
       </c>
       <c r="H102" s="26">
-        <v>52.050016650016644</v>
+        <v>39.181152181152179</v>
       </c>
       <c r="I102" s="26">
-        <v>1.7193194599999999</v>
+        <v>1.5279626333333332</v>
       </c>
       <c r="J102" s="26">
-        <v>14.221233339999998</v>
+        <v>9.0094639000000001</v>
       </c>
       <c r="K102" s="19">
-        <v>2.1674091566287858E-14</v>
+        <v>3.9971695378103606E-13</v>
       </c>
       <c r="L102" s="29">
-        <v>1.19697021298036E-16</v>
+        <v>1.2148143771941906E-16</v>
       </c>
       <c r="M102" s="31">
         <v>66.047500400000004</v>
@@ -8764,7 +8949,7 @@
         <v>6.3725624216579441E-14</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A103" s="12">
         <v>5</v>
       </c>
@@ -8784,22 +8969,22 @@
         <v>4368</v>
       </c>
       <c r="G103" s="25">
-        <v>4.716117216117216E-2</v>
+        <v>5.967643467643468E-2</v>
       </c>
       <c r="H103" s="26">
-        <v>53.460805860805863</v>
+        <v>41.855692918192915</v>
       </c>
       <c r="I103" s="26">
-        <v>2.6408645800000001</v>
+        <v>2.4413142000000003</v>
       </c>
       <c r="J103" s="26">
-        <v>22.382495080000002</v>
+        <v>14.310228033333333</v>
       </c>
       <c r="K103" s="19">
-        <v>1.9849585675117582E-13</v>
+        <v>4.1011328675153563E-13</v>
       </c>
       <c r="L103" s="29">
-        <v>1.2153242872410853E-16</v>
+        <v>1.2309243045992736E-16</v>
       </c>
       <c r="M103" s="31">
         <v>119.5974179</v>
@@ -8820,7 +9005,7 @@
         <v>8.916631099107902E-14</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A104" s="12">
         <v>5</v>
       </c>
@@ -8840,22 +9025,22 @@
         <v>6188</v>
       </c>
       <c r="G104" s="25">
-        <v>4.6380090497737558E-2</v>
+        <v>5.7530704589528116E-2</v>
       </c>
       <c r="H104" s="26">
-        <v>55.604072398190048</v>
+        <v>42.254686489980607</v>
       </c>
       <c r="I104" s="26">
-        <v>4.3651004999999996</v>
+        <v>4.0589202999999996</v>
       </c>
       <c r="J104" s="26">
-        <v>40.196838199999995</v>
+        <v>21.312664000000002</v>
       </c>
       <c r="K104" s="19">
-        <v>7.6220692133465515E-13</v>
+        <v>1.1053927024494505E-13</v>
       </c>
       <c r="L104" s="29">
-        <v>1.1957001009087114E-16</v>
+        <v>1.2091455341096432E-16</v>
       </c>
       <c r="M104" s="31">
         <v>267.15335240000002</v>
@@ -8871,7 +9056,7 @@
       </c>
       <c r="R104" s="29"/>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A105" s="12">
         <v>5</v>
       </c>
@@ -8891,22 +9076,22 @@
         <v>8568</v>
       </c>
       <c r="G105" s="25">
-        <v>5.0887021475256769E-2</v>
+        <v>6.8160597572362272E-2</v>
       </c>
       <c r="H105" s="26">
-        <v>55.548786181139121</v>
+        <v>45.746965452847803</v>
       </c>
       <c r="I105" s="26">
-        <v>6.5030210999999998</v>
+        <v>6.3668737999999996</v>
       </c>
       <c r="J105" s="26">
-        <v>56.411471800000001</v>
+        <v>32.910109399999996</v>
       </c>
       <c r="K105" s="19">
-        <v>3.5382780931788124E-13</v>
+        <v>5.6513930771883584E-13</v>
       </c>
       <c r="L105" s="29">
-        <v>1.2152060527248596E-16</v>
+        <v>1.2353662116605378E-16</v>
       </c>
       <c r="M105" s="31">
         <v>537.66359539999996</v>
@@ -8922,7 +9107,7 @@
       </c>
       <c r="R105" s="29"/>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A106" s="12">
         <v>5</v>
       </c>
@@ -8942,22 +9127,22 @@
         <v>11628</v>
       </c>
       <c r="G106" s="25">
-        <v>5.203E-2</v>
+        <v>6.6305469556243557E-2</v>
       </c>
       <c r="H106" s="26">
-        <v>58.2</v>
+        <v>48.850963192294465</v>
       </c>
       <c r="I106" s="26">
-        <v>9.1170000000000009</v>
+        <v>9.6694370999999997</v>
       </c>
       <c r="J106" s="26">
-        <v>86.555000000000007</v>
+        <v>54.297702599999994</v>
       </c>
       <c r="K106" s="19">
-        <v>6.3400000000000002E-13</v>
+        <v>5.1897725670975774E-13</v>
       </c>
       <c r="L106" s="29">
-        <v>1.2376999999999999E-16</v>
+        <v>1.2468722909704443E-16</v>
       </c>
       <c r="M106" s="31">
         <v>1097.6545295999999</v>
@@ -8972,8 +9157,22 @@
         <v>0</v>
       </c>
       <c r="R106" s="29"/>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S106" s="70">
+        <v>306.88</v>
+      </c>
+      <c r="T106" s="70">
+        <v>9.4730000000000008</v>
+      </c>
+      <c r="U106" s="67">
+        <f>S106/J106</f>
+        <v>5.6518045019459082</v>
+      </c>
+      <c r="V106" s="67">
+        <f>(S106-T106)/(J106-I106)</f>
+        <v>6.6640949781030585</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A107" s="12">
         <v>5</v>
       </c>
@@ -8993,22 +9192,22 @@
         <v>15504</v>
       </c>
       <c r="G107" s="25">
-        <v>5.5985552115583079E-2</v>
+        <v>7.3464912280701761E-2</v>
       </c>
       <c r="H107" s="26">
-        <v>58.341202270381835</v>
+        <v>51.857585139318886</v>
       </c>
       <c r="I107" s="26">
-        <v>14.630369099999999</v>
+        <v>14.715860899999999</v>
       </c>
       <c r="J107" s="26">
-        <v>118.3904395</v>
+        <v>80.945590799999991</v>
       </c>
       <c r="K107" s="19">
-        <v>2.2556661922624915E-13</v>
+        <v>5.4702027322082213E-13</v>
       </c>
       <c r="L107" s="29">
-        <v>1.2530303112920252E-16</v>
+        <v>1.2665761369070656E-16</v>
       </c>
       <c r="M107" s="31">
         <v>2305.1311283999999</v>
@@ -9022,7 +9221,7 @@
       <c r="P107" s="31"/>
       <c r="R107" s="29"/>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A108" s="12">
         <v>5</v>
       </c>
@@ -9042,29 +9241,29 @@
         <v>20349</v>
       </c>
       <c r="G108" s="25">
-        <v>5.5481841859550837E-2</v>
+        <v>7.6613101380903242E-2</v>
       </c>
       <c r="H108" s="26">
-        <v>60.457319770013271</v>
+        <v>55.399872229593591</v>
       </c>
       <c r="I108" s="26">
-        <v>22.254712000000001</v>
+        <v>22.377465300000001</v>
       </c>
       <c r="J108" s="26">
-        <v>176.19220720000001</v>
+        <v>117.491991</v>
       </c>
       <c r="K108" s="19">
-        <v>4.5253191931154844E-13</v>
+        <v>3.4433288865469058E-13</v>
       </c>
       <c r="L108" s="29">
-        <v>1.2432897067263221E-16</v>
+        <v>1.2519845719755494E-16</v>
       </c>
       <c r="M108" s="31"/>
       <c r="O108" s="29"/>
       <c r="P108" s="31"/>
       <c r="R108" s="29"/>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A109" s="20">
         <v>6</v>
       </c>
@@ -9087,19 +9286,19 @@
         <v>0</v>
       </c>
       <c r="H109" s="22">
-        <v>43.828571428571436</v>
+        <v>22.142857142857146</v>
       </c>
       <c r="I109" s="22">
-        <v>8.7413200000000003E-3</v>
+        <v>9.9852399999999994E-3</v>
       </c>
       <c r="J109" s="22">
-        <v>4.8915764999999986E-2</v>
+        <v>4.5036955000000004E-2</v>
       </c>
       <c r="K109" s="23">
-        <v>1.0923599286702165E-15</v>
+        <v>2.6522006436109976E-15</v>
       </c>
       <c r="L109" s="27">
-        <v>1.5490163297422784E-16</v>
+        <v>2.4400453471359334E-16</v>
       </c>
       <c r="M109" s="30">
         <v>0.26154030500000003</v>
@@ -9120,7 +9319,7 @@
         <v>2.6588322692823478E-15</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A110" s="20">
         <v>6</v>
       </c>
@@ -9140,22 +9339,22 @@
         <v>28</v>
       </c>
       <c r="G110" s="21">
-        <v>0</v>
+        <v>1.0714285714285714E-2</v>
       </c>
       <c r="H110" s="22">
-        <v>43.682142857142864</v>
+        <v>23.912500000000001</v>
       </c>
       <c r="I110" s="22">
-        <v>3.7696025000000008E-2</v>
+        <v>2.3968389999999999E-2</v>
       </c>
       <c r="J110" s="22">
-        <v>0.14700240000000003</v>
+        <v>0.11473232000000003</v>
       </c>
       <c r="K110" s="23">
-        <v>1.6206043888974962E-15</v>
+        <v>1.0359936184097788E-14</v>
       </c>
       <c r="L110" s="27">
-        <v>1.3172848827614632E-16</v>
+        <v>1.3255559325747014E-16</v>
       </c>
       <c r="M110" s="30">
         <v>1.0297562250000001</v>
@@ -9176,7 +9375,7 @@
         <v>5.2231039040589853E-15</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A111" s="20">
         <v>6</v>
       </c>
@@ -9196,22 +9395,22 @@
         <v>84</v>
       </c>
       <c r="G111" s="21">
-        <v>2.1428571428571429E-2</v>
+        <v>1.0714285714285714E-2</v>
       </c>
       <c r="H111" s="22">
-        <v>44.192857142857143</v>
+        <v>24.866666666666667</v>
       </c>
       <c r="I111" s="22">
-        <v>0.12162175500000001</v>
+        <v>7.8924454999999991E-2</v>
       </c>
       <c r="J111" s="22">
-        <v>0.41721945499999996</v>
+        <v>0.27964221500000008</v>
       </c>
       <c r="K111" s="23">
-        <v>2.3382105211243422E-15</v>
+        <v>1.6626630830473515E-14</v>
       </c>
       <c r="L111" s="27">
-        <v>1.3125409089103384E-16</v>
+        <v>1.33119816145033E-16</v>
       </c>
       <c r="M111" s="30">
         <v>3.0857070799999997</v>
@@ -9232,7 +9431,7 @@
         <v>1.6730608028343718E-14</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A112" s="20">
         <v>6</v>
       </c>
@@ -9252,22 +9451,22 @@
         <v>210</v>
       </c>
       <c r="G112" s="21">
-        <v>2.1904761904761903E-2</v>
+        <v>1.5952380952380954E-2</v>
       </c>
       <c r="H112" s="22">
-        <v>44.685000000000002</v>
+        <v>25.896666666666668</v>
       </c>
       <c r="I112" s="22">
-        <v>0.31338831</v>
+        <v>0.19049169999999999</v>
       </c>
       <c r="J112" s="22">
-        <v>0.97330201000000005</v>
+        <v>0.61794294500000002</v>
       </c>
       <c r="K112" s="23">
-        <v>1.6003766641405531E-14</v>
+        <v>5.5887088191209416E-14</v>
       </c>
       <c r="L112" s="27">
-        <v>1.2836608578473774E-16</v>
+        <v>1.3079149736644543E-16</v>
       </c>
       <c r="M112" s="30">
         <v>7.8288595000000001</v>
@@ -9288,7 +9487,7 @@
         <v>1.1280622335288723E-14</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A113" s="20">
         <v>6</v>
       </c>
@@ -9308,22 +9507,22 @@
         <v>462</v>
       </c>
       <c r="G113" s="21">
-        <v>2.5974025974025976E-2</v>
+        <v>1.4718614718614718E-2</v>
       </c>
       <c r="H113" s="22">
-        <v>45.636796536796538</v>
+        <v>26.348917748917746</v>
       </c>
       <c r="I113" s="22">
-        <v>0.70373210000000008</v>
+        <v>0.43905209999999995</v>
       </c>
       <c r="J113" s="22">
-        <v>2.0912460400000001</v>
+        <v>1.2429469200000001</v>
       </c>
       <c r="K113" s="23">
-        <v>1.2016961612700277E-13</v>
+        <v>1.3326703601758001E-14</v>
       </c>
       <c r="L113" s="27">
-        <v>1.2925433991094627E-16</v>
+        <v>1.3022596131231571E-16</v>
       </c>
       <c r="M113" s="30">
         <v>19.46116374</v>
@@ -9344,7 +9543,7 @@
         <v>1.5540873578954652E-14</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A114" s="20">
         <v>6</v>
       </c>
@@ -9364,22 +9563,22 @@
         <v>924</v>
       </c>
       <c r="G114" s="21">
-        <v>3.6363636363636362E-2</v>
+        <v>3.0952380952380953E-2</v>
       </c>
       <c r="H114" s="22">
-        <v>47.128787878787875</v>
+        <v>29.588528138528137</v>
       </c>
       <c r="I114" s="22">
-        <v>1.5138139399999999</v>
+        <v>1.0173983799999999</v>
       </c>
       <c r="J114" s="22">
-        <v>4.3360461200000007</v>
+        <v>2.6888829599999999</v>
       </c>
       <c r="K114" s="23">
-        <v>7.2231095284998176E-14</v>
+        <v>2.2332061816516014E-13</v>
       </c>
       <c r="L114" s="27">
-        <v>1.2736717987803491E-16</v>
+        <v>1.3068230495601532E-16</v>
       </c>
       <c r="M114" s="30">
         <v>43.666878280000006</v>
@@ -9400,7 +9599,7 @@
         <v>1.1820446670874992E-14</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A115" s="20">
         <v>6</v>
       </c>
@@ -9420,22 +9619,22 @@
         <v>1716</v>
       </c>
       <c r="G115" s="21">
-        <v>4.4988344988344989E-2</v>
+        <v>3.787878787878788E-2</v>
       </c>
       <c r="H115" s="22">
-        <v>50.096386946386943</v>
+        <v>32.369930069930071</v>
       </c>
       <c r="I115" s="22">
-        <v>3.0472979600000003</v>
+        <v>2.1504890799999998</v>
       </c>
       <c r="J115" s="22">
-        <v>9.2199360400000003</v>
+        <v>5.3917490800000003</v>
       </c>
       <c r="K115" s="23">
-        <v>1.3349996514515971E-13</v>
+        <v>1.76555805213773E-13</v>
       </c>
       <c r="L115" s="27">
-        <v>1.2648498938668725E-16</v>
+        <v>1.2825571818704477E-16</v>
       </c>
       <c r="M115" s="30">
         <v>118.44355419999999</v>
@@ -9455,8 +9654,22 @@
       <c r="R115" s="27">
         <v>2.5508350008859155E-14</v>
       </c>
-    </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S115" s="70">
+        <v>20.8325657</v>
+      </c>
+      <c r="T115" s="70">
+        <v>2.411</v>
+      </c>
+      <c r="U115" s="67">
+        <f>S115/J115</f>
+        <v>3.8637862020092371</v>
+      </c>
+      <c r="V115" s="67">
+        <f>(S115-T115)/(J115-I115)</f>
+        <v>5.6834581921845198</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A116" s="20">
         <v>6</v>
       </c>
@@ -9476,22 +9689,22 @@
         <v>3003</v>
       </c>
       <c r="G116" s="21">
-        <v>4.2357642357642361E-2</v>
+        <v>5.1171051171051168E-2</v>
       </c>
       <c r="H116" s="22">
-        <v>50.058807858807867</v>
+        <v>36.462204462204461</v>
       </c>
       <c r="I116" s="22">
-        <v>5.8062753199999992</v>
+        <v>4.4141718333333335</v>
       </c>
       <c r="J116" s="22">
-        <v>16.972541159999999</v>
+        <v>11.015139166666666</v>
       </c>
       <c r="K116" s="23">
-        <v>2.3008405060185915E-13</v>
+        <v>3.1616837461351963E-13</v>
       </c>
       <c r="L116" s="27">
-        <v>1.2503468397978249E-16</v>
+        <v>1.2624025364824506E-16</v>
       </c>
       <c r="M116" s="30">
         <v>302.59518709999998</v>
@@ -9512,7 +9725,7 @@
         <v>4.2878516110114435E-14</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A117" s="20">
         <v>6</v>
       </c>
@@ -9532,22 +9745,22 @@
         <v>5005</v>
       </c>
       <c r="G117" s="21">
-        <v>5.386613386613387E-2</v>
+        <v>5.627705627705628E-2</v>
       </c>
       <c r="H117" s="22">
-        <v>52.590169830169827</v>
+        <v>38.478654678654671</v>
       </c>
       <c r="I117" s="22">
-        <v>10.650419119999999</v>
+        <v>8.7393834333333338</v>
       </c>
       <c r="J117" s="22">
-        <v>33.834060720000004</v>
+        <v>21.323356200000003</v>
       </c>
       <c r="K117" s="23">
-        <v>2.1893243051455232E-13</v>
+        <v>5.5288575528456537E-13</v>
       </c>
       <c r="L117" s="27">
-        <v>1.2721829290026919E-16</v>
+        <v>1.2834318770514012E-16</v>
       </c>
       <c r="M117" s="30">
         <v>742.08734189999996</v>
@@ -9563,8 +9776,22 @@
       </c>
       <c r="Q117" s="23"/>
       <c r="R117" s="27"/>
-    </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S117" s="70">
+        <v>80.093980900000005</v>
+      </c>
+      <c r="T117" s="70">
+        <v>9.3544</v>
+      </c>
+      <c r="U117" s="67">
+        <f>S117/J117</f>
+        <v>3.7561620295026539</v>
+      </c>
+      <c r="V117" s="67">
+        <f>(S117-T117)/(J117-I117)</f>
+        <v>5.6214028917306695</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A118" s="20">
         <v>6</v>
       </c>
@@ -9584,22 +9811,22 @@
         <v>8008</v>
       </c>
       <c r="G118" s="21">
-        <v>6.043956043956044E-2</v>
+        <v>6.9555444555444559E-2</v>
       </c>
       <c r="H118" s="22">
-        <v>55.905219780219781</v>
+        <v>41.701798201798205</v>
       </c>
       <c r="I118" s="22">
-        <v>20.688411800000001</v>
+        <v>18.381482099999999</v>
       </c>
       <c r="J118" s="22">
-        <v>66.541065099999997</v>
+        <v>40.379703499999998</v>
       </c>
       <c r="K118" s="23">
-        <v>6.7259815530124517E-13</v>
+        <v>3.7238543221220515E-13</v>
       </c>
       <c r="L118" s="27">
-        <v>1.2860943492388659E-16</v>
+        <v>1.3060000676674515E-16</v>
       </c>
       <c r="M118" s="30">
         <v>2312.4965281999998</v>
@@ -9616,7 +9843,7 @@
       <c r="Q118" s="23"/>
       <c r="R118" s="27"/>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A119" s="12">
         <v>7</v>
       </c>
@@ -9639,19 +9866,19 @@
         <v>0</v>
       </c>
       <c r="H119" s="26">
-        <v>45.706249999999997</v>
+        <v>24.537500000000001</v>
       </c>
       <c r="I119" s="26">
-        <v>1.3620534999999998E-2</v>
+        <v>3.7806144999999999E-2</v>
       </c>
       <c r="J119" s="26">
-        <v>5.9506694999999984E-2</v>
+        <v>7.5730779999999998E-2</v>
       </c>
       <c r="K119" s="19">
-        <v>9.625919512762793E-16</v>
+        <v>5.6854775624040914E-15</v>
       </c>
       <c r="L119" s="29">
-        <v>1.6538608547142279E-16</v>
+        <v>1.6272925443105194E-16</v>
       </c>
       <c r="M119" s="31">
         <v>2.28116596</v>
@@ -9672,7 +9899,7 @@
         <v>2.1762739024720347E-15</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A120" s="12">
         <v>7</v>
       </c>
@@ -9692,22 +9919,22 @@
         <v>36</v>
       </c>
       <c r="G120" s="25">
-        <v>1.1111111111111112E-2</v>
+        <v>8.3333333333333332E-3</v>
       </c>
       <c r="H120" s="26">
-        <v>44.476388888888877</v>
+        <v>24.824999999999996</v>
       </c>
       <c r="I120" s="26">
-        <v>5.2029024999999993E-2</v>
+        <v>5.5774629999999992E-2</v>
       </c>
       <c r="J120" s="26">
-        <v>0.197268425</v>
+        <v>0.15315430000000002</v>
       </c>
       <c r="K120" s="19">
-        <v>2.1641480774581508E-15</v>
+        <v>4.8939021377378756E-15</v>
       </c>
       <c r="L120" s="29">
-        <v>1.4169626419159008E-16</v>
+        <v>1.4633551304035414E-16</v>
       </c>
       <c r="M120" s="31">
         <v>10.47226306</v>
@@ -9728,7 +9955,7 @@
         <v>3.6813657602131006E-15</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A121" s="12">
         <v>7</v>
       </c>
@@ -9748,22 +9975,22 @@
         <v>120</v>
       </c>
       <c r="G121" s="25">
-        <v>1.1666666666666665E-2</v>
+        <v>9.1666666666666667E-3</v>
       </c>
       <c r="H121" s="26">
-        <v>45.926666666666662</v>
+        <v>25.621666666666663</v>
       </c>
       <c r="I121" s="26">
-        <v>0.19992137000000004</v>
+        <v>0.18532896500000001</v>
       </c>
       <c r="J121" s="26">
-        <v>0.69836495499999995</v>
+        <v>0.44925526999999993</v>
       </c>
       <c r="K121" s="19">
-        <v>9.9175922962140197E-15</v>
+        <v>7.1332073663340674E-14</v>
       </c>
       <c r="L121" s="29">
-        <v>1.3924790189394575E-16</v>
+        <v>1.3949455290075497E-16</v>
       </c>
       <c r="M121" s="31">
         <v>35.521456920000006</v>
@@ -9784,7 +10011,7 @@
         <v>6.6476839034272828E-15</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A122" s="12">
         <v>7</v>
       </c>
@@ -9804,22 +10031,22 @@
         <v>330</v>
       </c>
       <c r="G122" s="25">
-        <v>2.8484848484848484E-2</v>
+        <v>1.4545454545454545E-2</v>
       </c>
       <c r="H122" s="26">
-        <v>47.738181818181815</v>
+        <v>28.228484848484847</v>
       </c>
       <c r="I122" s="26">
-        <v>0.59156125999999998</v>
+        <v>0.60415343999999993</v>
       </c>
       <c r="J122" s="26">
-        <v>1.79893028</v>
+        <v>1.28136454</v>
       </c>
       <c r="K122" s="19">
-        <v>1.0524418624525242E-13</v>
+        <v>2.435011097181236E-13</v>
       </c>
       <c r="L122" s="29">
-        <v>1.3684242343917633E-16</v>
+        <v>1.4088281313872886E-16</v>
       </c>
       <c r="M122" s="31">
         <v>104.9884751</v>
@@ -9840,7 +10067,7 @@
         <v>7.2565794550175886E-15</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A123" s="12">
         <v>7</v>
       </c>
@@ -9860,22 +10087,22 @@
         <v>792</v>
       </c>
       <c r="G123" s="25">
-        <v>3.2323232323232323E-2</v>
+        <v>2.5505050505050503E-2</v>
       </c>
       <c r="H123" s="26">
-        <v>47.821717171717168</v>
+        <v>28.807575757575755</v>
       </c>
       <c r="I123" s="26">
-        <v>1.7483439999999999</v>
+        <v>1.7266233800000002</v>
       </c>
       <c r="J123" s="26">
-        <v>4.8900499999999996</v>
+        <v>3.1694037799999997</v>
       </c>
       <c r="K123" s="19">
-        <v>2.5706568202481521E-14</v>
+        <v>1.6428231581282075E-13</v>
       </c>
       <c r="L123" s="29">
-        <v>1.3618269858751313E-16</v>
+        <v>1.3841915941646457E-16</v>
       </c>
       <c r="M123" s="31">
         <v>305.77434690000001</v>
@@ -9896,7 +10123,7 @@
         <v>1.6184008831862778E-14</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A124" s="12">
         <v>7</v>
       </c>
@@ -9916,22 +10143,22 @@
         <v>1716</v>
       </c>
       <c r="G124" s="25">
-        <v>4.0559440559440559E-2</v>
+        <v>3.2828282828282832E-2</v>
       </c>
       <c r="H124" s="26">
-        <v>49.129953379953385</v>
+        <v>30.93842268842269</v>
       </c>
       <c r="I124" s="26">
-        <v>4.0596699999999997</v>
+        <v>4.2290084333333331</v>
       </c>
       <c r="J124" s="26">
-        <v>10.28380114</v>
+        <v>7.5992268666666662</v>
       </c>
       <c r="K124" s="19">
-        <v>2.0991424478406782E-13</v>
+        <v>4.7049979106233423E-13</v>
       </c>
       <c r="L124" s="29">
-        <v>1.3343160903973149E-16</v>
+        <v>1.359741032635575E-16</v>
       </c>
       <c r="M124" s="31">
         <v>860.35919660000002</v>
@@ -9952,7 +10179,7 @@
         <v>2.415254560136972E-14</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A125" s="12">
         <v>7</v>
       </c>
@@ -9972,23 +10199,22 @@
         <v>3432</v>
       </c>
       <c r="G125" s="25">
-        <f>146/3432</f>
-        <v>4.2540792540792544E-2</v>
+        <v>4.6911421911421912E-2</v>
       </c>
       <c r="H125" s="26">
-        <v>51.312899999999999</v>
+        <v>34.754370629370626</v>
       </c>
       <c r="I125" s="26">
-        <v>9.552187</v>
+        <v>9.1161122999999993</v>
       </c>
       <c r="J125" s="26">
-        <v>25.052150000000001</v>
+        <v>16.7404893</v>
       </c>
       <c r="K125" s="19">
-        <v>9.24386829625933E-14</v>
+        <v>7.8991303399505828E-13</v>
       </c>
       <c r="L125" s="29">
-        <v>1.3283122277486501E-16</v>
+        <v>1.3450546966345016E-16</v>
       </c>
       <c r="M125" s="31">
         <v>3018</v>
@@ -10004,7 +10230,7 @@
         <v>6.6161160784148703E-14</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A126" s="12">
         <v>7</v>
       </c>
@@ -10024,30 +10250,29 @@
         <v>6435</v>
       </c>
       <c r="G126" s="25">
-        <f>373/6435</f>
-        <v>5.7964257964257963E-2</v>
+        <v>5.128205128205128E-2</v>
       </c>
       <c r="H126" s="26">
-        <v>52.15571095</v>
+        <v>36.861227661227659</v>
       </c>
       <c r="I126" s="26">
-        <v>17.923686400000001</v>
+        <v>17.763582799999998</v>
       </c>
       <c r="J126" s="26">
-        <v>49.949469999999998</v>
+        <v>34.003315099999995</v>
       </c>
       <c r="K126" s="19">
-        <v>0.35885524542141001</v>
+        <v>6.5630009152964791E-13</v>
       </c>
       <c r="L126" s="29">
-        <v>1.32442536009495E-16</v>
+        <v>1.3332598889186014E-16</v>
       </c>
       <c r="M126" s="31"/>
       <c r="O126" s="29"/>
       <c r="P126" s="31"/>
       <c r="R126" s="29"/>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A127" s="12">
         <v>7</v>
       </c>
@@ -10067,29 +10292,29 @@
         <v>11440</v>
       </c>
       <c r="G127" s="57">
-        <v>6.8500000000000005E-2</v>
+        <v>6.8531468531468534E-2</v>
       </c>
       <c r="H127" s="58">
-        <v>53.65</v>
+        <v>40.034090909090907</v>
       </c>
       <c r="I127" s="58">
-        <v>36.329000000000001</v>
+        <v>33.343518899999999</v>
       </c>
       <c r="J127" s="58">
-        <v>106.61</v>
+        <v>65.172876599999995</v>
       </c>
       <c r="K127" s="55">
-        <v>7.8000000000000001E-13</v>
+        <v>6.2593631582221922E-13</v>
       </c>
       <c r="L127" s="56">
-        <v>1.3413727102630461E-16</v>
+        <v>1.3669762423730614E-16</v>
       </c>
       <c r="M127" s="31"/>
       <c r="O127" s="29"/>
       <c r="P127" s="31"/>
       <c r="R127" s="29"/>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A128" s="12">
         <v>7</v>
       </c>
@@ -10109,22 +10334,22 @@
         <v>19448</v>
       </c>
       <c r="G128" s="57">
-        <v>8.0500000000000002E-2</v>
+        <v>7.3580830933772115E-2</v>
       </c>
       <c r="H128" s="58">
-        <v>56.997999999999998</v>
+        <v>43.302858905800079</v>
       </c>
       <c r="I128" s="58">
-        <v>67.97</v>
+        <v>60.663565300000002</v>
       </c>
       <c r="J128" s="58">
-        <v>225.33</v>
+        <v>121.9182672</v>
       </c>
       <c r="K128" s="55">
-        <v>7.9800000000000003E-13</v>
+        <v>6.2534367256046993E-13</v>
       </c>
       <c r="L128" s="56">
-        <v>1.2978114416206174E-16</v>
+        <v>1.3162365042648978E-16</v>
       </c>
       <c r="M128" s="31"/>
       <c r="O128" s="29"/>
@@ -10151,22 +10376,22 @@
         <v>31824</v>
       </c>
       <c r="G129" s="57">
-        <v>8.09E-2</v>
+        <v>8.1636500754147814E-2</v>
       </c>
       <c r="H129" s="58">
-        <v>56.57</v>
+        <v>45.678450226244344</v>
       </c>
       <c r="I129" s="58">
-        <v>120.39</v>
+        <v>108.4396405</v>
       </c>
       <c r="J129" s="58">
-        <v>392.16</v>
+        <v>216.4531848</v>
       </c>
       <c r="K129" s="55">
-        <v>6.1200000000000002E-13</v>
+        <v>6.3353686354549404E-13</v>
       </c>
       <c r="L129" s="56">
-        <v>1.3206929068820129E-16</v>
+        <v>1.3356555040248495E-16</v>
       </c>
       <c r="M129" s="31"/>
       <c r="O129" s="29"/>
@@ -10196,19 +10421,19 @@
         <v>0</v>
       </c>
       <c r="H130" s="22">
-        <v>50.517682000000001</v>
+        <v>24.672222222222224</v>
       </c>
       <c r="I130" s="22">
-        <v>2.054135E-2</v>
+        <v>1.62478E-2</v>
       </c>
       <c r="J130" s="22">
-        <v>8.3039160000000001E-2</v>
+        <v>6.2447779999999987E-2</v>
       </c>
       <c r="K130" s="23">
-        <v>1.4285605750923168E-15</v>
+        <v>2.2763073738001108E-15</v>
       </c>
       <c r="L130" s="27">
-        <v>1.6033599739914397E-16</v>
+        <v>1.7026884880835408E-16</v>
       </c>
       <c r="M130" s="30">
         <v>23.6435791</v>
@@ -10249,22 +10474,22 @@
         <v>45</v>
       </c>
       <c r="G131" s="21">
-        <v>0.02</v>
+        <v>4.4444444444444444E-3</v>
       </c>
       <c r="H131" s="22">
-        <v>46.800000000000004</v>
+        <v>25.182222222222222</v>
       </c>
       <c r="I131" s="22">
-        <v>8.0181370000000002E-2</v>
+        <v>7.9699215000000018E-2</v>
       </c>
       <c r="J131" s="22">
-        <v>0.30986244499999999</v>
+        <v>0.20677629</v>
       </c>
       <c r="K131" s="23">
-        <v>2.4992357438056574E-15</v>
+        <v>1.057704887574212E-14</v>
       </c>
       <c r="L131" s="27">
-        <v>1.4815035288872744E-16</v>
+        <v>1.530270217387647E-16</v>
       </c>
       <c r="M131" s="30">
         <v>118.63456050000001</v>
@@ -10305,22 +10530,22 @@
         <v>165</v>
       </c>
       <c r="G132" s="21">
-        <v>2.636363636363636E-2</v>
+        <v>9.0909090909090905E-3</v>
       </c>
       <c r="H132" s="22">
-        <v>47.20545454545455</v>
+        <v>27.092727272727274</v>
       </c>
       <c r="I132" s="22">
-        <v>0.31096959499999999</v>
+        <v>0.31296696499999999</v>
       </c>
       <c r="J132" s="22">
-        <v>0.99736371500000021</v>
+        <v>0.68351704000000002</v>
       </c>
       <c r="K132" s="23">
-        <v>3.1977376649532487E-15</v>
+        <v>8.2852415828189899E-15</v>
       </c>
       <c r="L132" s="27">
-        <v>1.4438536352269958E-16</v>
+        <v>1.4602782396610445E-16</v>
       </c>
       <c r="M132" s="30">
         <v>447.86</v>
@@ -10361,22 +10586,22 @@
         <v>495</v>
       </c>
       <c r="G133" s="21">
-        <v>2.9090909090909091E-2</v>
+        <v>2.181818181818182E-2</v>
       </c>
       <c r="H133" s="22">
-        <v>48.054141414141419</v>
+        <v>28.631111111111114</v>
       </c>
       <c r="I133" s="22">
-        <v>1.42853728</v>
+        <v>1.2718668200000001</v>
       </c>
       <c r="J133" s="22">
-        <v>3.3568599399999997</v>
+        <v>2.2601355399999998</v>
       </c>
       <c r="K133" s="23">
-        <v>3.4783952312032996E-15</v>
+        <v>7.8760019110267406E-14</v>
       </c>
       <c r="L133" s="27">
-        <v>1.4294633939642059E-16</v>
+        <v>1.4347197357095355E-16</v>
       </c>
       <c r="M133" s="30">
         <v>1452.2390227000001</v>
@@ -10417,22 +10642,22 @@
         <v>1287</v>
       </c>
       <c r="G134" s="21">
-        <v>3.8383838383838381E-2</v>
+        <v>3.2634032634032632E-2</v>
       </c>
       <c r="H134" s="22">
-        <v>50.054700854700847</v>
+        <v>31.491219891219892</v>
       </c>
       <c r="I134" s="22">
-        <v>4.3499009399999995</v>
+        <v>3.7751415400000008</v>
       </c>
       <c r="J134" s="22">
-        <v>9.8802709400000008</v>
+        <v>6.4819743799999996</v>
       </c>
       <c r="K134" s="23">
-        <v>1.8436859912558656E-13</v>
+        <v>2.2529800320736209E-13</v>
       </c>
       <c r="L134" s="27">
-        <v>1.4091157249076579E-16</v>
+        <v>1.4337196158674879E-16</v>
       </c>
       <c r="M134" s="30">
         <v>4870.7439999999997</v>
@@ -10473,23 +10698,22 @@
         <v>3003</v>
       </c>
       <c r="G135" s="21">
-        <f>146.2/3003</f>
-        <v>4.8684648684648682E-2</v>
+        <v>4.295704295704296E-2</v>
       </c>
       <c r="H135" s="22">
-        <v>50.517699999999998</v>
+        <v>34.101454101454102</v>
       </c>
       <c r="I135" s="22">
-        <v>11.03627925999</v>
+        <v>9.568009166666668</v>
       </c>
       <c r="J135" s="22">
-        <v>24.323108040000001</v>
+        <v>16.457347866666666</v>
       </c>
       <c r="K135" s="23">
-        <v>3.54876921678448E-14</v>
+        <v>2.0120539777576654E-13</v>
       </c>
       <c r="L135" s="27">
-        <v>1.36524895551352E-16</v>
+        <v>1.3640217132197329E-16</v>
       </c>
       <c r="M135" s="30"/>
       <c r="N135" s="23"/>
@@ -10524,23 +10748,22 @@
         <v>6435</v>
       </c>
       <c r="G136" s="21">
-        <f>408.3/6435</f>
-        <v>6.3449883449883449E-2</v>
+        <v>6.3869463869463863E-2</v>
       </c>
       <c r="H136" s="22">
-        <v>52.27899</v>
+        <v>37.119813519813519</v>
       </c>
       <c r="I136" s="22">
-        <v>25.613457</v>
+        <v>22.247449</v>
       </c>
       <c r="J136" s="22">
-        <v>60.166719733000001</v>
+        <v>39.216944900000001</v>
       </c>
       <c r="K136" s="23">
-        <v>2.0060517267969899E-13</v>
+        <v>2.8085836576001143E-13</v>
       </c>
       <c r="L136" s="27">
-        <v>1.39547471763416E-16</v>
+        <v>1.3979665432003479E-16</v>
       </c>
       <c r="M136" s="30"/>
       <c r="N136" s="23"/>
@@ -10560,7 +10783,7 @@
         <v>20</v>
       </c>
       <c r="D137" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" s="16">
         <v>20</v>
@@ -10572,28 +10795,28 @@
         <v>0</v>
       </c>
       <c r="H137" s="48">
-        <v>47.615000000000016</v>
+        <v>26.159999999999989</v>
       </c>
       <c r="I137" s="48">
-        <v>2.0519420000000003E-2</v>
+        <v>2.0146089999999998E-2</v>
       </c>
       <c r="J137" s="48">
-        <v>8.9840065000000024E-2</v>
+        <v>6.709292E-2</v>
       </c>
       <c r="K137" s="19">
-        <v>1.5026459727299758E-15</v>
+        <v>2.6942737726797901E-15</v>
       </c>
       <c r="L137" s="29">
-        <v>1.6517225671802399E-16</v>
+        <v>1.6673640139720562E-16</v>
       </c>
       <c r="M137" s="49">
-        <v>0</v>
+        <v>262.76</v>
       </c>
       <c r="N137" s="19">
-        <v>0</v>
+        <v>8.8272616808598999E-16</v>
       </c>
       <c r="O137" s="29">
-        <v>0</v>
+        <v>4.1198709954403898E-16</v>
       </c>
       <c r="P137" s="49">
         <v>2.1355899999999997E-2</v>
@@ -10625,22 +10848,22 @@
         <v>55</v>
       </c>
       <c r="G138" s="47">
-        <v>1.8181818181818181E-2</v>
+        <v>5.4545454545454541E-3</v>
       </c>
       <c r="H138" s="48">
-        <v>47.985454545454552</v>
+        <v>27.351818181818182</v>
       </c>
       <c r="I138" s="48">
-        <v>0.10648650500000001</v>
+        <v>0.11100401000000001</v>
       </c>
       <c r="J138" s="48">
-        <v>0.39305564000000004</v>
+        <v>0.26641277499999994</v>
       </c>
       <c r="K138" s="19">
-        <v>2.3790274088986772E-15</v>
+        <v>8.2694426505685226E-15</v>
       </c>
       <c r="L138" s="29">
-        <v>1.5581053793345391E-16</v>
+        <v>1.555432197486837E-16</v>
       </c>
       <c r="M138" s="49">
         <v>0</v>
@@ -10681,22 +10904,22 @@
         <v>220</v>
       </c>
       <c r="G139" s="47">
-        <v>1.9545454545454543E-2</v>
+        <v>8.8636363636363635E-3</v>
       </c>
       <c r="H139" s="48">
-        <v>48.272272727272735</v>
+        <v>28.218181818181819</v>
       </c>
       <c r="I139" s="48">
-        <v>0.60008791500000014</v>
+        <v>0.58622608500000006</v>
       </c>
       <c r="J139" s="48">
-        <v>1.5480788649999997</v>
+        <v>1.1054329600000004</v>
       </c>
       <c r="K139" s="19">
-        <v>5.3397020926561128E-15</v>
+        <v>8.7389955707409441E-15</v>
       </c>
       <c r="L139" s="29">
-        <v>1.5031203777596245E-16</v>
+        <v>1.5326890010715973E-16</v>
       </c>
       <c r="M139" s="49">
         <v>0</v>
@@ -10737,23 +10960,22 @@
         <v>715</v>
       </c>
       <c r="G140" s="47">
-        <f>18.4/715</f>
-        <v>2.5734265734265731E-2</v>
+        <v>1.6223776223776222E-2</v>
       </c>
       <c r="H140" s="48">
-        <v>48.542000000000002</v>
+        <v>30.224895104895108</v>
       </c>
       <c r="I140" s="48">
-        <v>2.6829999999999998</v>
+        <v>2.4864242399999998</v>
       </c>
       <c r="J140" s="48">
-        <v>5.7869000000000002</v>
+        <v>4.0314480000000001</v>
       </c>
       <c r="K140" s="19">
-        <v>3.62781480983836E-15</v>
+        <v>8.6235865927269656E-14</v>
       </c>
       <c r="L140" s="29">
-        <v>1.4587974004736401E-16</v>
+        <v>1.4710509283326004E-16</v>
       </c>
       <c r="M140" s="49"/>
       <c r="O140" s="29"/>
@@ -10787,23 +11009,22 @@
         <v>2002</v>
       </c>
       <c r="G141" s="47">
-        <f>77.8/2002</f>
-        <v>3.8861138861138858E-2</v>
+        <v>3.3633033633033632E-2</v>
       </c>
       <c r="H141" s="48">
-        <v>51.24</v>
+        <v>33.105061605061607</v>
       </c>
       <c r="I141" s="48">
-        <v>9.3321000000000005</v>
+        <v>8.0991151000000006</v>
       </c>
       <c r="J141" s="48">
-        <v>19.7408</v>
+        <v>12.6557928</v>
       </c>
       <c r="K141" s="19">
-        <v>7.1967025213862698E-14</v>
+        <v>2.3772834604430109E-13</v>
       </c>
       <c r="L141" s="29">
-        <v>1.4469895725686299E-16</v>
+        <v>1.4636468803949842E-16</v>
       </c>
       <c r="M141" s="49"/>
       <c r="O141" s="29"/>
@@ -10840,19 +11061,19 @@
         <v>0</v>
       </c>
       <c r="H142" s="22">
-        <v>48.504545454545465</v>
+        <v>25.56818181818182</v>
       </c>
       <c r="I142" s="22">
-        <v>2.4772864999999998E-2</v>
+        <v>2.6406255E-2</v>
       </c>
       <c r="J142" s="22">
-        <v>0.10475287500000001</v>
+        <v>7.6054860000000002E-2</v>
       </c>
       <c r="K142" s="23">
-        <v>2.2087525459781703E-15</v>
+        <v>2.1471402543570415E-14</v>
       </c>
       <c r="L142" s="27">
-        <v>1.7132926194353821E-16</v>
+        <v>1.7790224233587779E-16</v>
       </c>
       <c r="M142" s="30">
         <v>0</v>
@@ -10889,22 +11110,22 @@
         <v>66</v>
       </c>
       <c r="G143" s="21">
-        <v>1.9696969696969699E-2</v>
+        <v>9.0909090909090905E-3</v>
       </c>
       <c r="H143" s="22">
-        <v>49.060606060606055</v>
+        <v>28.922727272727268</v>
       </c>
       <c r="I143" s="22">
-        <v>0.14951344500000002</v>
+        <v>0.15569002500000001</v>
       </c>
       <c r="J143" s="22">
-        <v>0.50383889000000004</v>
+        <v>0.34924788499999998</v>
       </c>
       <c r="K143" s="23">
-        <v>4.2513122238059881E-14</v>
+        <v>6.799722922474496E-15</v>
       </c>
       <c r="L143" s="27">
-        <v>1.5930178779804624E-16</v>
+        <v>1.6158123147426539E-16</v>
       </c>
       <c r="M143" s="30">
         <v>0</v>
@@ -10941,22 +11162,22 @@
         <v>286</v>
       </c>
       <c r="G144" s="21">
-        <v>1.9580419580419579E-2</v>
+        <v>1.5384615384615385E-2</v>
       </c>
       <c r="H144" s="22">
-        <v>50.006993006993014</v>
+        <v>29.650349650349646</v>
       </c>
       <c r="I144" s="22">
-        <v>1.4223936199999998</v>
+        <v>1.0465489800000001</v>
       </c>
       <c r="J144" s="22">
-        <v>2.6376466600000001</v>
+        <v>1.73802514</v>
       </c>
       <c r="K144" s="23">
-        <v>3.2852517524661626E-15</v>
+        <v>1.3371668998344418E-14</v>
       </c>
       <c r="L144" s="27">
-        <v>1.5553077438236544E-16</v>
+        <v>1.5643751577831873E-16</v>
       </c>
       <c r="M144" s="30">
         <v>0</v>
@@ -10973,7 +11194,7 @@
         <v>9.0825312062756657E-15</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A145" s="20">
         <v>10</v>
       </c>
@@ -10993,22 +11214,22 @@
         <v>1001</v>
       </c>
       <c r="G145" s="21">
-        <v>2.4975024975024976E-2</v>
+        <v>2.3576423576423578E-2</v>
       </c>
       <c r="H145" s="22">
-        <v>49.759040959040959</v>
+        <v>32.218181818181819</v>
       </c>
       <c r="I145" s="22">
-        <v>5.3108877000000003</v>
+        <v>4.4841086600000004</v>
       </c>
       <c r="J145" s="22">
-        <v>9.5998409999999996</v>
+        <v>6.7989622000000001</v>
       </c>
       <c r="K145" s="23">
-        <v>6.6927769248518135E-14</v>
+        <v>2.2747080311189355E-13</v>
       </c>
       <c r="L145" s="27">
-        <v>1.5262457199677837E-16</v>
+        <v>1.546833640418733E-16</v>
       </c>
       <c r="M145" s="30">
         <v>0</v>
@@ -11025,7 +11246,7 @@
         <v>1.0429719207744357E-14</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A146" s="20">
         <v>10</v>
       </c>
@@ -11045,22 +11266,22 @@
         <v>3003</v>
       </c>
       <c r="G146" s="21">
-        <v>4.2624042624042624E-2</v>
+        <v>3.3300033300033303E-2</v>
       </c>
       <c r="H146" s="22">
-        <v>51.843556443556452</v>
+        <v>33.957375957375959</v>
       </c>
       <c r="I146" s="22">
-        <v>20.603534040000003</v>
+        <v>15.330990166666666</v>
       </c>
       <c r="J146" s="22">
-        <v>36.282285619999996</v>
+        <v>22.921736533333334</v>
       </c>
       <c r="K146" s="23">
-        <v>3.132475179145614E-13</v>
+        <v>3.7056154758004255E-13</v>
       </c>
       <c r="L146" s="27">
-        <v>1.5102813134190057E-16</v>
+        <v>1.53939850287635E-16</v>
       </c>
       <c r="M146" s="30">
         <v>0</v>
@@ -11077,11 +11298,11 @@
         <v>2.2616696280792418E-14</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A147" s="20">
         <v>10</v>
       </c>
-      <c r="B147" s="20">
+      <c r="B147" s="64">
         <v>7</v>
       </c>
       <c r="C147" s="34">
@@ -11097,23 +11318,22 @@
         <v>8008</v>
       </c>
       <c r="G147" s="21">
-        <f>465/8008</f>
-        <v>5.8066933066933064E-2</v>
+        <v>5.6818181818181816E-2</v>
       </c>
       <c r="H147" s="22">
-        <v>53.871000000000002</v>
+        <v>38.15734265734266</v>
       </c>
       <c r="I147" s="22">
-        <v>50.222418500000003</v>
+        <v>44.146962299999998</v>
       </c>
       <c r="J147" s="22">
-        <v>99.045699999999997</v>
+        <v>67.346488899999997</v>
       </c>
       <c r="K147" s="23">
-        <v>2.9689475263861E-13</v>
+        <v>5.1125671096529199E-13</v>
       </c>
       <c r="L147" s="27">
-        <v>1.48347289238091E-16</v>
+        <v>1.5018341537302159E-16</v>
       </c>
       <c r="M147" s="30"/>
       <c r="N147" s="23"/>
@@ -11122,11 +11342,11 @@
       <c r="Q147" s="23"/>
       <c r="R147" s="27"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A148" s="20">
         <v>10</v>
       </c>
-      <c r="B148" s="20">
+      <c r="B148" s="64">
         <v>8</v>
       </c>
       <c r="C148" s="34">
@@ -11142,23 +11362,22 @@
         <v>19448</v>
       </c>
       <c r="G148" s="21">
-        <f>1563/19448</f>
-        <v>8.0368161250514186E-2</v>
+        <v>7.8259975318798844E-2</v>
       </c>
       <c r="H148" s="22">
-        <v>57.183</v>
+        <v>42.684903331962154</v>
       </c>
       <c r="I148" s="22">
-        <v>138.10169239999999</v>
+        <v>118.1147433</v>
       </c>
       <c r="J148" s="22">
-        <v>330.77274190000003</v>
+        <v>184.7420821</v>
       </c>
       <c r="K148" s="23">
-        <v>5.3839583601297597E-13</v>
+        <v>8.4221942685889919E-13</v>
       </c>
       <c r="L148" s="27">
-        <v>1.4843723858875701E-16</v>
+        <v>1.5005143304844946E-16</v>
       </c>
       <c r="M148" s="30"/>
       <c r="N148" s="23"/>
@@ -11167,11 +11386,11 @@
       <c r="Q148" s="23"/>
       <c r="R148" s="27"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A149" s="20">
         <v>10</v>
       </c>
-      <c r="B149" s="20">
+      <c r="B149" s="64">
         <v>10</v>
       </c>
       <c r="C149" s="34">
@@ -11187,22 +11406,22 @@
         <v>92378</v>
       </c>
       <c r="G149" s="59">
-        <v>0.11559999999999999</v>
+        <v>0.10751477624542639</v>
       </c>
       <c r="H149" s="60">
-        <v>62.457000000000001</v>
+        <v>48.643627270562256</v>
       </c>
       <c r="I149" s="60">
-        <v>912.2</v>
+        <v>718.57001119999995</v>
       </c>
       <c r="J149" s="60">
-        <v>3189.39</v>
+        <v>1116.2019324999999</v>
       </c>
       <c r="K149" s="61">
-        <v>7.8899999999999997E-13</v>
+        <v>7.5946377547801622E-13</v>
       </c>
       <c r="L149" s="62">
-        <v>1.4739999999999999E-16</v>
+        <v>1.4883442879242569E-16</v>
       </c>
       <c r="M149" s="30"/>
       <c r="N149" s="23"/>
@@ -11210,12 +11429,26 @@
       <c r="P149" s="30"/>
       <c r="Q149" s="23"/>
       <c r="R149" s="27"/>
-    </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S149" s="70">
+        <v>4943.8862541999997</v>
+      </c>
+      <c r="T149" s="70">
+        <v>2703.3573000000001</v>
+      </c>
+      <c r="U149" s="67">
+        <f>S149/J149</f>
+        <v>4.42920417018719</v>
+      </c>
+      <c r="V149" s="67">
+        <f>(S149-T149)/(J149-I149)</f>
+        <v>5.6346808044860053</v>
+      </c>
+    </row>
+    <row r="150" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A150" s="12">
         <v>15</v>
       </c>
-      <c r="B150" s="12">
+      <c r="B150" s="65">
         <v>2</v>
       </c>
       <c r="C150">
@@ -11231,22 +11464,22 @@
         <v>16</v>
       </c>
       <c r="G150" s="47">
-        <v>6.2500000000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="H150" s="48">
-        <v>53.965625000000003</v>
+        <v>31.496874999999999</v>
       </c>
       <c r="I150" s="48">
-        <v>6.0164625000000006E-2</v>
+        <v>7.0628894999999997E-2</v>
       </c>
       <c r="J150" s="48">
-        <v>0.18416717500000002</v>
+        <v>0.15153119000000001</v>
       </c>
       <c r="K150" s="19">
-        <v>2.4743169775678135E-14</v>
+        <v>1.686123664763437E-14</v>
       </c>
       <c r="L150" s="29">
-        <v>1.945914007401514E-16</v>
+        <v>1.9559561102866872E-16</v>
       </c>
       <c r="M150" s="49">
         <v>0</v>
@@ -11262,11 +11495,11 @@
         <v>4.5957663749455702E-15</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A151" s="12">
         <v>15</v>
       </c>
-      <c r="B151" s="12">
+      <c r="B151" s="65">
         <v>3</v>
       </c>
       <c r="C151">
@@ -11282,22 +11515,22 @@
         <v>136</v>
       </c>
       <c r="G151" s="47">
-        <v>8.8235294117647058E-3</v>
+        <v>5.8823529411764705E-3</v>
       </c>
       <c r="H151" s="48">
-        <v>53.555514705882352</v>
+        <v>33.218382352941177</v>
       </c>
       <c r="I151" s="48">
-        <v>1.3612410300000002</v>
+        <v>1.4572636500000002</v>
       </c>
       <c r="J151" s="48">
-        <v>2.2030135900000003</v>
+        <v>1.9267980650000003</v>
       </c>
       <c r="K151" s="19">
-        <v>3.6880987281577654E-14</v>
+        <v>1.2702716968080462E-13</v>
       </c>
       <c r="L151" s="29">
-        <v>1.8494364927744351E-16</v>
+        <v>1.9023012387414769E-16</v>
       </c>
       <c r="M151" s="49">
         <v>0</v>
@@ -11313,7 +11546,7 @@
         <v>8.1226533092137531E-15</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A152" s="12">
         <v>15</v>
       </c>
@@ -11333,22 +11566,22 @@
         <v>816</v>
       </c>
       <c r="G152" s="47">
-        <v>2.2794117647058826E-2</v>
+        <v>1.7973856209150325E-2</v>
       </c>
       <c r="H152" s="48">
-        <v>54.439215686274508</v>
+        <v>35.584150326797385</v>
       </c>
       <c r="I152" s="48">
-        <v>7.7498982999999999</v>
+        <v>8.147148399999999</v>
       </c>
       <c r="J152" s="48">
-        <v>12.815375419999999</v>
+        <v>10.755881666666667</v>
       </c>
       <c r="K152" s="19">
-        <v>4.716599858124967E-15</v>
+        <v>1.0641761108410615E-14</v>
       </c>
       <c r="L152" s="29">
-        <v>1.7919893611094811E-16</v>
+        <v>1.8208501473401676E-16</v>
       </c>
       <c r="M152" s="49">
         <v>0</v>
@@ -11364,94 +11597,84 @@
         <v>3.8106660570468187E-14</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A153" s="20">
-        <v>20</v>
-      </c>
-      <c r="B153" s="20">
+    <row r="153" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A153" s="12">
+        <v>15</v>
+      </c>
+      <c r="B153" s="12">
+        <v>5</v>
+      </c>
+      <c r="C153" s="36">
+        <v>1</v>
+      </c>
+      <c r="D153" s="16">
+        <v>0</v>
+      </c>
+      <c r="E153" s="16">
+        <v>0</v>
+      </c>
+      <c r="F153" s="37">
+        <v>3876</v>
+      </c>
+      <c r="G153" s="47">
+        <v>3.7151000000000003E-2</v>
+      </c>
+      <c r="H153" s="48">
+        <v>39.209000000000003</v>
+      </c>
+      <c r="I153" s="48">
+        <v>44.6843</v>
+      </c>
+      <c r="J153" s="48">
+        <v>60.979700000000001</v>
+      </c>
+      <c r="K153" s="19">
+        <v>1.978E-13</v>
+      </c>
+      <c r="L153" s="29">
+        <v>1.7699999999999999E-16</v>
+      </c>
+      <c r="M153" s="49"/>
+      <c r="O153" s="29"/>
+      <c r="P153" s="49"/>
+      <c r="R153" s="29"/>
+    </row>
+    <row r="154" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A154" s="20">
+        <v>20</v>
+      </c>
+      <c r="B154" s="20">
         <v>2</v>
       </c>
-      <c r="C153" s="33">
-        <v>20</v>
-      </c>
-      <c r="D153" s="34">
-        <v>0</v>
-      </c>
-      <c r="E153" s="34">
-        <v>20</v>
-      </c>
-      <c r="F153" s="35">
+      <c r="C154" s="33">
+        <v>20</v>
+      </c>
+      <c r="D154" s="34">
+        <v>0</v>
+      </c>
+      <c r="E154" s="34">
+        <v>20</v>
+      </c>
+      <c r="F154" s="35">
         <v>21</v>
       </c>
-      <c r="G153" s="21">
-        <v>1.4285714285714285E-2</v>
-      </c>
-      <c r="H153" s="22">
-        <v>58.069047619047623</v>
-      </c>
-      <c r="I153" s="22">
-        <v>0.153629765</v>
-      </c>
-      <c r="J153" s="22">
-        <v>0.37274005999999998</v>
-      </c>
-      <c r="K153" s="23">
-        <v>2.8318444558315176E-15</v>
-      </c>
-      <c r="L153" s="27">
-        <v>2.1386335095452643E-16</v>
-      </c>
-      <c r="M153" s="30">
-        <v>0</v>
-      </c>
-      <c r="N153" s="23"/>
-      <c r="O153" s="27"/>
-      <c r="P153" s="30">
-        <v>0.18962910499999996</v>
-      </c>
-      <c r="Q153" s="23">
-        <v>4.7064330011845567E-14</v>
-      </c>
-      <c r="R153" s="27">
-        <v>5.3151656025545146E-15</v>
-      </c>
-    </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A154" s="20">
-        <v>20</v>
-      </c>
-      <c r="B154" s="20">
-        <v>3</v>
-      </c>
-      <c r="C154" s="33">
-        <v>5</v>
-      </c>
-      <c r="D154" s="34">
-        <v>0</v>
-      </c>
-      <c r="E154" s="34">
-        <v>5</v>
-      </c>
-      <c r="F154" s="35">
-        <v>231</v>
-      </c>
       <c r="G154" s="21">
-        <v>5.1948051948051948E-3</v>
+        <v>4.7619047619047623E-3</v>
       </c>
       <c r="H154" s="22">
-        <v>57.487445887445894</v>
+        <v>35.776190476190472</v>
       </c>
       <c r="I154" s="22">
-        <v>4.2725780599999998</v>
+        <v>0.19213794499999998</v>
       </c>
       <c r="J154" s="22">
-        <v>6.0817013200000005</v>
+        <v>0.31227701999999996</v>
       </c>
       <c r="K154" s="23">
-        <v>5.1931929646145647E-15</v>
+        <v>6.1717245306926428E-15</v>
       </c>
       <c r="L154" s="27">
-        <v>2.0341459493551671E-16</v>
+        <v>2.1820056065069372E-16</v>
       </c>
       <c r="M154" s="30">
         <v>0</v>
@@ -11459,21 +11682,21 @@
       <c r="N154" s="23"/>
       <c r="O154" s="27"/>
       <c r="P154" s="30">
-        <v>13.794577720000001</v>
+        <v>0.18962910499999996</v>
       </c>
       <c r="Q154" s="23">
-        <v>2.6971918739271963E-13</v>
+        <v>4.7064330011845567E-14</v>
       </c>
       <c r="R154" s="27">
-        <v>1.1676308993650923E-14</v>
-      </c>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
+        <v>5.3151656025545146E-15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A155" s="20">
         <v>20</v>
       </c>
       <c r="B155" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C155" s="33">
         <v>5</v>
@@ -11485,292 +11708,372 @@
         <v>5</v>
       </c>
       <c r="F155" s="35">
-        <v>1771</v>
+        <v>231</v>
       </c>
       <c r="G155" s="21">
-        <v>2.3602484472049687E-2</v>
+        <v>1.7316017316017316E-3</v>
       </c>
       <c r="H155" s="22">
-        <v>59.570299265951441</v>
+        <v>37.161038961038955</v>
       </c>
       <c r="I155" s="22">
-        <v>36.886945079999997</v>
+        <v>4.6199022999999997</v>
       </c>
       <c r="J155" s="22">
-        <v>52.909996999999997</v>
+        <v>5.5634209600000002</v>
       </c>
       <c r="K155" s="23">
-        <v>5.4417498778419909E-13</v>
+        <v>1.1416262439651864E-14</v>
       </c>
       <c r="L155" s="27">
-        <v>1.996864150496776E-16</v>
+        <v>2.0703831061008342E-16</v>
       </c>
       <c r="M155" s="30">
         <v>0</v>
       </c>
       <c r="N155" s="23"/>
       <c r="O155" s="27"/>
-      <c r="P155" s="32">
+      <c r="P155" s="30">
+        <v>13.794577720000001</v>
+      </c>
+      <c r="Q155" s="23">
+        <v>2.6971918739271963E-13</v>
+      </c>
+      <c r="R155" s="27">
+        <v>1.1676308993650923E-14</v>
+      </c>
+      <c r="S155" s="69">
+        <v>14.95542</v>
+      </c>
+      <c r="T155" s="69">
+        <v>9.9762000000000004</v>
+      </c>
+      <c r="U155" s="67">
+        <f>S155/J155</f>
+        <v>2.688169762368656</v>
+      </c>
+      <c r="V155" s="67">
+        <f>(S155-T155)/(J155-I155)</f>
+        <v>5.2772883156333092</v>
+      </c>
+    </row>
+    <row r="156" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A156" s="20">
+        <v>20</v>
+      </c>
+      <c r="B156" s="20">
+        <v>4</v>
+      </c>
+      <c r="C156" s="33">
+        <v>5</v>
+      </c>
+      <c r="D156" s="34">
+        <v>0</v>
+      </c>
+      <c r="E156" s="34">
+        <v>5</v>
+      </c>
+      <c r="F156" s="35">
+        <v>1771</v>
+      </c>
+      <c r="G156" s="21">
+        <v>2.4468285337850556E-2</v>
+      </c>
+      <c r="H156" s="22">
+        <v>41.130623000188216</v>
+      </c>
+      <c r="I156" s="22">
+        <v>36.979266966666671</v>
+      </c>
+      <c r="J156" s="22">
+        <v>45.140964266666664</v>
+      </c>
+      <c r="K156" s="23">
+        <v>2.3796102523966171E-13</v>
+      </c>
+      <c r="L156" s="27">
+        <v>2.0511338980134735E-16</v>
+      </c>
+      <c r="M156" s="30">
+        <v>0</v>
+      </c>
+      <c r="N156" s="23"/>
+      <c r="O156" s="27"/>
+      <c r="P156" s="32">
         <v>18.9506771</v>
       </c>
-      <c r="Q155" s="24">
-        <v>0</v>
-      </c>
-      <c r="R155" s="28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A156" s="12">
+      <c r="Q156" s="24">
+        <v>0</v>
+      </c>
+      <c r="R156" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A157" s="12">
         <v>30</v>
       </c>
-      <c r="B156" s="12">
+      <c r="B157" s="12">
         <v>2</v>
       </c>
-      <c r="C156" s="36">
-        <v>20</v>
-      </c>
-      <c r="D156" s="16">
-        <v>0</v>
-      </c>
-      <c r="E156" s="16">
-        <v>20</v>
-      </c>
-      <c r="F156" s="37">
+      <c r="C157" s="36">
+        <v>20</v>
+      </c>
+      <c r="D157" s="16">
+        <v>0</v>
+      </c>
+      <c r="E157" s="16">
+        <v>20</v>
+      </c>
+      <c r="F157" s="37">
         <v>31</v>
       </c>
-      <c r="G156" s="47">
-        <v>6.4516129032258064E-3</v>
-      </c>
-      <c r="H156" s="48">
-        <v>63.47258064516128</v>
-      </c>
-      <c r="I156" s="48">
-        <v>0.86756881000000008</v>
-      </c>
-      <c r="J156" s="48">
-        <v>1.30644432</v>
-      </c>
-      <c r="K156" s="19">
-        <v>7.4625012168464069E-15</v>
-      </c>
-      <c r="L156" s="29">
-        <v>2.4652082294233389E-16</v>
-      </c>
-      <c r="M156" s="49">
-        <v>0</v>
-      </c>
-      <c r="O156" s="29"/>
-      <c r="P156" s="49">
+      <c r="G157" s="47">
+        <v>0</v>
+      </c>
+      <c r="H157" s="48">
+        <v>41.612903225806448</v>
+      </c>
+      <c r="I157" s="48">
+        <v>1.0210149850000003</v>
+      </c>
+      <c r="J157" s="48">
+        <v>1.2597854550000001</v>
+      </c>
+      <c r="K157" s="19">
+        <v>8.5582296734420292E-15</v>
+      </c>
+      <c r="L157" s="29">
+        <v>2.518069272681986E-16</v>
+      </c>
+      <c r="M157" s="49">
+        <v>0</v>
+      </c>
+      <c r="O157" s="29"/>
+      <c r="P157" s="49">
         <v>1.2790287900000001</v>
       </c>
-      <c r="Q156" s="19">
+      <c r="Q157" s="19">
         <v>2.9179799648931526E-13</v>
       </c>
-      <c r="R156" s="29">
+      <c r="R157" s="29">
         <v>6.5689768415600145E-15</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A157" s="20">
+    <row r="158" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A158" s="20">
         <v>40</v>
       </c>
-      <c r="B157" s="20">
+      <c r="B158" s="20">
         <v>2</v>
       </c>
-      <c r="C157" s="33">
-        <v>5</v>
-      </c>
-      <c r="D157" s="34">
-        <v>0</v>
-      </c>
-      <c r="E157" s="34">
-        <v>5</v>
-      </c>
-      <c r="F157" s="35">
+      <c r="C158" s="33">
+        <v>5</v>
+      </c>
+      <c r="D158" s="34">
+        <v>0</v>
+      </c>
+      <c r="E158" s="34">
+        <v>5</v>
+      </c>
+      <c r="F158" s="35">
         <v>41</v>
       </c>
-      <c r="G157" s="21">
+      <c r="G158" s="21">
         <v>9.7560975609756097E-3</v>
       </c>
-      <c r="H157" s="22">
-        <v>70.731707317073159</v>
-      </c>
-      <c r="I157" s="22">
-        <v>2.2014087400000002</v>
-      </c>
-      <c r="J157" s="22">
-        <v>3.02475366</v>
-      </c>
-      <c r="K157" s="23">
-        <v>4.3776762553396366E-15</v>
-      </c>
-      <c r="L157" s="27">
-        <v>2.742734855217869E-16</v>
-      </c>
-      <c r="M157" s="30">
-        <v>0</v>
-      </c>
-      <c r="N157" s="23"/>
-      <c r="O157" s="27"/>
-      <c r="P157" s="30">
+      <c r="H158" s="22">
+        <v>48.556097560975601</v>
+      </c>
+      <c r="I158" s="22">
+        <v>2.3820981400000001</v>
+      </c>
+      <c r="J158" s="22">
+        <v>2.8433841800000001</v>
+      </c>
+      <c r="K158" s="23">
+        <v>7.3951646897169031E-15</v>
+      </c>
+      <c r="L158" s="27">
+        <v>2.7664237750967958E-16</v>
+      </c>
+      <c r="M158" s="30">
+        <v>0</v>
+      </c>
+      <c r="N158" s="23"/>
+      <c r="O158" s="27"/>
+      <c r="P158" s="30">
         <v>6.3138266199999995</v>
       </c>
-      <c r="Q157" s="23">
+      <c r="Q158" s="23">
         <v>9.3527313112655728E-14</v>
       </c>
-      <c r="R157" s="27">
+      <c r="R158" s="27">
         <v>7.1300527475026733E-15</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A158" s="12">
+    <row r="159" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A159" s="12">
         <v>50</v>
       </c>
-      <c r="B158" s="12">
+      <c r="B159" s="12">
         <v>2</v>
       </c>
-      <c r="C158" s="36">
-        <v>5</v>
-      </c>
-      <c r="D158" s="16">
-        <v>0</v>
-      </c>
-      <c r="E158" s="16">
-        <v>5</v>
-      </c>
-      <c r="F158" s="37">
+      <c r="C159" s="36">
+        <v>5</v>
+      </c>
+      <c r="D159" s="16">
+        <v>0</v>
+      </c>
+      <c r="E159" s="16">
+        <v>5</v>
+      </c>
+      <c r="F159" s="37">
         <v>51</v>
       </c>
-      <c r="G158" s="47">
-        <v>0</v>
-      </c>
-      <c r="H158" s="48">
-        <v>73.917647058823519</v>
-      </c>
-      <c r="I158" s="48">
-        <v>4.2932302199999999</v>
-      </c>
-      <c r="J158" s="48">
-        <v>5.5251610400000004</v>
-      </c>
-      <c r="K158" s="19">
-        <v>7.6129738399634801E-15</v>
-      </c>
-      <c r="L158" s="29">
-        <v>2.9903040808198097E-16</v>
-      </c>
-      <c r="M158" s="49">
-        <v>0</v>
-      </c>
-      <c r="O158" s="29"/>
-      <c r="P158" s="49">
+      <c r="G159" s="47">
+        <v>7.8431372549019607E-3</v>
+      </c>
+      <c r="H159" s="48">
+        <v>52.482352941176465</v>
+      </c>
+      <c r="I159" s="48">
+        <v>4.4790898000000006</v>
+      </c>
+      <c r="J159" s="48">
+        <v>5.1876860799999998</v>
+      </c>
+      <c r="K159" s="19">
+        <v>1.5124330514439133E-14</v>
+      </c>
+      <c r="L159" s="29">
+        <v>3.0654247787110837E-16</v>
+      </c>
+      <c r="M159" s="49">
+        <v>0</v>
+      </c>
+      <c r="O159" s="29"/>
+      <c r="P159" s="49">
         <v>21.992981719999996</v>
       </c>
-      <c r="Q158" s="19">
+      <c r="Q159" s="19">
         <v>2.0222888077500663E-13</v>
       </c>
-      <c r="R158" s="29">
+      <c r="R159" s="29">
         <v>9.3758240873329806E-15</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A159" s="20">
+    <row r="160" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A160" s="20">
         <v>60</v>
       </c>
-      <c r="B159" s="20">
+      <c r="B160" s="20">
         <v>2</v>
       </c>
-      <c r="C159" s="33">
-        <v>5</v>
-      </c>
-      <c r="D159" s="34">
-        <v>0</v>
-      </c>
-      <c r="E159" s="34">
-        <v>5</v>
-      </c>
-      <c r="F159" s="35">
+      <c r="C160" s="33">
+        <v>5</v>
+      </c>
+      <c r="D160" s="34">
+        <v>0</v>
+      </c>
+      <c r="E160" s="34">
+        <v>5</v>
+      </c>
+      <c r="F160" s="35">
         <v>61</v>
       </c>
-      <c r="G159" s="21">
-        <v>6.5573770491803279E-3</v>
-      </c>
-      <c r="H159" s="22">
-        <v>79.436065573770492</v>
-      </c>
-      <c r="I159" s="22">
-        <v>11.96833852</v>
-      </c>
-      <c r="J159" s="22">
-        <v>14.187293360000002</v>
-      </c>
-      <c r="K159" s="23">
-        <v>6.5727706591326052E-15</v>
-      </c>
-      <c r="L159" s="27">
-        <v>3.2040951682034663E-16</v>
-      </c>
-      <c r="M159" s="30">
-        <v>0</v>
-      </c>
-      <c r="N159" s="23"/>
-      <c r="O159" s="27"/>
-      <c r="P159" s="30">
+      <c r="G160" s="21">
+        <v>0</v>
+      </c>
+      <c r="H160" s="22">
+        <v>56.009836065573765</v>
+      </c>
+      <c r="I160" s="22">
+        <v>7.5207874399999994</v>
+      </c>
+      <c r="J160" s="22">
+        <v>8.5283140599999996</v>
+      </c>
+      <c r="K160" s="23">
+        <v>1.651343759813488E-14</v>
+      </c>
+      <c r="L160" s="27">
+        <v>3.2130858892875223E-16</v>
+      </c>
+      <c r="M160" s="30">
+        <v>0</v>
+      </c>
+      <c r="N160" s="23"/>
+      <c r="O160" s="27"/>
+      <c r="P160" s="30">
         <v>64.626304340000004</v>
       </c>
-      <c r="Q159" s="23">
+      <c r="Q160" s="23">
         <v>3.2534728724153973E-14</v>
       </c>
-      <c r="R159" s="27">
+      <c r="R160" s="27">
         <v>7.9329691390372562E-15</v>
       </c>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A160" s="12">
+      <c r="S160" s="69">
+        <v>36.792900000000003</v>
+      </c>
+      <c r="T160" s="69">
+        <v>31.407540000000001</v>
+      </c>
+      <c r="U160" s="67">
+        <f>S160/J160</f>
+        <v>4.3142055676125048</v>
+      </c>
+      <c r="V160" s="67">
+        <f>(S160-T160)/(J160-I160)</f>
+        <v>5.3451292433345348</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A161" s="12">
         <v>100</v>
       </c>
-      <c r="B160" s="12">
+      <c r="B161" s="12">
         <v>2</v>
       </c>
-      <c r="C160" s="36">
+      <c r="C161" s="36">
         <v>1</v>
       </c>
-      <c r="D160" s="16">
-        <v>0</v>
-      </c>
-      <c r="E160" s="16">
-        <v>0</v>
-      </c>
-      <c r="F160" s="37">
+      <c r="D161" s="16">
+        <v>0</v>
+      </c>
+      <c r="E161" s="16">
+        <v>0</v>
+      </c>
+      <c r="F161" s="37">
         <v>101</v>
       </c>
-      <c r="G160" s="47">
-        <v>0</v>
-      </c>
-      <c r="H160" s="48">
-        <v>92.841584158415841</v>
-      </c>
-      <c r="I160" s="48">
-        <v>40.335313300000003</v>
-      </c>
-      <c r="J160" s="48">
-        <v>48.8238226</v>
-      </c>
-      <c r="K160" s="19">
-        <v>8.2046709664132521E-15</v>
-      </c>
-      <c r="L160" s="29">
-        <v>3.9130857912949214E-16</v>
-      </c>
-      <c r="M160" s="49">
-        <v>0</v>
-      </c>
-      <c r="O160" s="29"/>
-      <c r="P160" s="49">
-        <v>0</v>
-      </c>
-      <c r="R160" s="29"/>
+      <c r="G161" s="47">
+        <v>0</v>
+      </c>
+      <c r="H161" s="48">
+        <v>73.56435643564356</v>
+      </c>
+      <c r="I161" s="48">
+        <v>34.633054600000001</v>
+      </c>
+      <c r="J161" s="48">
+        <v>38.690378299999999</v>
+      </c>
+      <c r="K161" s="19">
+        <v>2.3909098509220518E-13</v>
+      </c>
+      <c r="L161" s="29">
+        <v>3.9287786047432685E-16</v>
+      </c>
+      <c r="M161" s="49">
+        <v>0</v>
+      </c>
+      <c r="O161" s="29"/>
+      <c r="P161" s="49">
+        <v>0</v>
+      </c>
+      <c r="R161" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
